--- a/CIMED_Valuation_DCF.xlsx
+++ b/CIMED_Valuation_DCF.xlsx
@@ -14,7 +14,7 @@
     <sheet name="DCF" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -809,6 +809,7 @@
       </c>
       <c r="C6" s="5">
         <f>DCF!C19</f>
+        <v>4124.971646</v>
         <v/>
       </c>
       <c r="E6" s="4" t="inlineStr">
@@ -818,6 +819,7 @@
       </c>
       <c r="F6" s="6">
         <f>Premissas!C26</f>
+        <v>0.148878</v>
         <v/>
       </c>
     </row>
@@ -829,6 +831,7 @@
       </c>
       <c r="C7" s="5">
         <f>-Premissas!C33</f>
+        <v>-1353.046</v>
         <v/>
       </c>
       <c r="E7" s="4" t="inlineStr">
@@ -838,6 +841,7 @@
       </c>
       <c r="F7" s="6">
         <f>Premissas!C25</f>
+        <v>0.14877</v>
         <v/>
       </c>
     </row>
@@ -848,6 +852,7 @@
       </c>
       <c r="C8" s="7">
         <f>DCF!C23</f>
+        <v>2771.925646</v>
         <v/>
       </c>
       <c r="E8" s="4" t="inlineStr">
@@ -857,6 +862,7 @@
       </c>
       <c r="F8" s="50">
         <f>Premissas!C14</f>
+        <v>0.05</v>
         <v/>
       </c>
     </row>
@@ -868,6 +874,7 @@
       </c>
       <c r="F9" s="51">
         <f>Premissas!C40</f>
+        <v>7.0</v>
         <v/>
       </c>
     </row>
@@ -879,6 +886,7 @@
       </c>
       <c r="C10" s="5">
         <f>Premissas!C41</f>
+        <v>4124.993652</v>
         <v/>
       </c>
       <c r="E10" s="4" t="inlineStr">
@@ -888,6 +896,7 @@
       </c>
       <c r="F10" s="5">
         <f>Premissas!C6</f>
+        <v>480.161</v>
         <v/>
       </c>
     </row>
@@ -898,6 +907,7 @@
       </c>
       <c r="C11" s="7">
         <f>Premissas!C43</f>
+        <v>2771.947652</v>
         <v/>
       </c>
       <c r="E11" s="4" t="inlineStr">
@@ -907,6 +917,7 @@
       </c>
       <c r="F11" s="51">
         <f>Premissas!C33/Premissas!C6</f>
+        <v>2.817901</v>
         <v/>
       </c>
     </row>
@@ -918,6 +929,7 @@
       </c>
       <c r="F12" s="5">
         <f>Premissas!C3</f>
+        <v>3067.594</v>
         <v/>
       </c>
     </row>
@@ -929,6 +941,7 @@
       </c>
       <c r="C13" s="52">
         <f>DCF!C19-Premissas!C41</f>
+        <v>-0.022005</v>
         <v/>
       </c>
     </row>
@@ -947,6 +960,7 @@
       </c>
       <c r="C15" s="53">
         <f>DCF!C23/1000</f>
+        <v>2.771926</v>
         <v/>
       </c>
     </row>
@@ -1543,6 +1557,7 @@
       </c>
       <c r="C6" s="56">
         <f>C4+C5</f>
+        <v>480.161</v>
         <v/>
       </c>
     </row>
@@ -1554,6 +1569,7 @@
       </c>
       <c r="C7" s="57">
         <f>C6/C3</f>
+        <v>0.156527</v>
         <v/>
       </c>
     </row>
@@ -1684,6 +1700,7 @@
       </c>
       <c r="C20" s="30">
         <f>C17+C19*C18</f>
+        <v>0.17325</v>
         <v/>
       </c>
     </row>
@@ -1710,6 +1727,7 @@
       </c>
       <c r="C22" s="31">
         <f>C21*(1-C13)</f>
+        <v>0.10125</v>
         <v/>
       </c>
     </row>
@@ -1741,6 +1759,7 @@
       </c>
       <c r="C25" s="32">
         <f>C20*C23+C22*C24</f>
+        <v>0.14877</v>
         <v/>
       </c>
     </row>
@@ -1798,6 +1817,7 @@
       </c>
       <c r="C31" s="56">
         <f>C29+C30</f>
+        <v>1791.423</v>
         <v/>
       </c>
     </row>
@@ -1818,6 +1838,7 @@
       </c>
       <c r="C33" s="59">
         <f>C31-C32</f>
+        <v>1353.046</v>
         <v/>
       </c>
       <c r="D33" s="38" t="inlineStr">
@@ -1892,6 +1913,7 @@
       </c>
       <c r="C41" s="58">
         <f>C40*Projecoes!C9</f>
+        <v>4124.993652</v>
         <v/>
       </c>
     </row>
@@ -1903,6 +1925,7 @@
       </c>
       <c r="C42" s="54">
         <f>-C33</f>
+        <v>-1353.046</v>
         <v/>
       </c>
     </row>
@@ -1913,6 +1936,7 @@
       </c>
       <c r="C43" s="58">
         <f>C41+C42</f>
+        <v>2771.947652</v>
         <v/>
       </c>
     </row>
@@ -2020,22 +2044,27 @@
       </c>
       <c r="C7" s="44">
         <f>Premissas!$C$3*(1+C6)</f>
+        <v>3466.38122</v>
         <v/>
       </c>
       <c r="D7" s="44">
         <f>C7*(1+D6)</f>
+        <v>3847.683154</v>
         <v/>
       </c>
       <c r="E7" s="44">
         <f>D7*(1+E6)</f>
+        <v>4193.974638</v>
         <v/>
       </c>
       <c r="F7" s="44">
         <f>E7*(1+F6)</f>
+        <v>4487.552863</v>
         <v/>
       </c>
       <c r="G7" s="44">
         <f>F7*(1+G6)</f>
+        <v>4756.806035</v>
         <v/>
       </c>
     </row>
@@ -2069,22 +2098,27 @@
       </c>
       <c r="C9" s="5">
         <f>C7*C8</f>
+        <v>589.284807</v>
         <v/>
       </c>
       <c r="D9" s="5">
         <f>D7*D8</f>
+        <v>711.821384</v>
         <v/>
       </c>
       <c r="E9" s="5">
         <f>E7*E8</f>
+        <v>817.825054</v>
         <v/>
       </c>
       <c r="F9" s="5">
         <f>F7*F8</f>
+        <v>897.510573</v>
         <v/>
       </c>
       <c r="G9" s="5">
         <f>G7*G8</f>
+        <v>975.145237</v>
         <v/>
       </c>
     </row>
@@ -2096,22 +2130,27 @@
       </c>
       <c r="C10" s="54">
         <f>-C7*Premissas!$C$11</f>
+        <v>-138.655249</v>
         <v/>
       </c>
       <c r="D10" s="54">
         <f>-D7*Premissas!$C$11</f>
+        <v>-153.907326</v>
         <v/>
       </c>
       <c r="E10" s="54">
         <f>-E7*Premissas!$C$11</f>
+        <v>-167.758986</v>
         <v/>
       </c>
       <c r="F10" s="54">
         <f>-F7*Premissas!$C$11</f>
+        <v>-179.502115</v>
         <v/>
       </c>
       <c r="G10" s="54">
         <f>-G7*Premissas!$C$11</f>
+        <v>-190.272241</v>
         <v/>
       </c>
     </row>
@@ -2122,22 +2161,27 @@
       </c>
       <c r="C11" s="56">
         <f>C9+C10</f>
+        <v>450.629559</v>
         <v/>
       </c>
       <c r="D11" s="56">
         <f>D9+D10</f>
+        <v>557.914057</v>
         <v/>
       </c>
       <c r="E11" s="56">
         <f>E9+E10</f>
+        <v>650.066069</v>
         <v/>
       </c>
       <c r="F11" s="56">
         <f>F9+F10</f>
+        <v>718.008458</v>
         <v/>
       </c>
       <c r="G11" s="56">
         <f>G9+G10</f>
+        <v>784.872996</v>
         <v/>
       </c>
     </row>
@@ -2149,22 +2193,27 @@
       </c>
       <c r="C12" s="54">
         <f>-C11*Premissas!$C$13</f>
+        <v>-112.65739</v>
         <v/>
       </c>
       <c r="D12" s="54">
         <f>-D11*Premissas!$C$13</f>
+        <v>-139.478514</v>
         <v/>
       </c>
       <c r="E12" s="54">
         <f>-E11*Premissas!$C$13</f>
+        <v>-162.516517</v>
         <v/>
       </c>
       <c r="F12" s="54">
         <f>-F11*Premissas!$C$13</f>
+        <v>-179.502115</v>
         <v/>
       </c>
       <c r="G12" s="54">
         <f>-G11*Premissas!$C$13</f>
+        <v>-196.218249</v>
         <v/>
       </c>
     </row>
@@ -2175,22 +2224,27 @@
       </c>
       <c r="C13" s="56">
         <f>C11+C12</f>
+        <v>337.972169</v>
         <v/>
       </c>
       <c r="D13" s="56">
         <f>D11+D12</f>
+        <v>418.435543</v>
         <v/>
       </c>
       <c r="E13" s="56">
         <f>E11+E12</f>
+        <v>487.549552</v>
         <v/>
       </c>
       <c r="F13" s="56">
         <f>F11+F12</f>
+        <v>538.506344</v>
         <v/>
       </c>
       <c r="G13" s="56">
         <f>G11+G12</f>
+        <v>588.654747</v>
         <v/>
       </c>
     </row>
@@ -2202,22 +2256,27 @@
       </c>
       <c r="C14" s="54">
         <f>-C10</f>
+        <v>138.655249</v>
         <v/>
       </c>
       <c r="D14" s="54">
         <f>-D10</f>
+        <v>153.907326</v>
         <v/>
       </c>
       <c r="E14" s="54">
         <f>-E10</f>
+        <v>167.758986</v>
         <v/>
       </c>
       <c r="F14" s="54">
         <f>-F10</f>
+        <v>179.502115</v>
         <v/>
       </c>
       <c r="G14" s="54">
         <f>-G10</f>
+        <v>190.272241</v>
         <v/>
       </c>
     </row>
@@ -2251,22 +2310,27 @@
       </c>
       <c r="C16" s="54">
         <f>-C7*C15</f>
+        <v>-207.982873</v>
         <v/>
       </c>
       <c r="D16" s="54">
         <f>-D7*D15</f>
+        <v>-211.622573</v>
         <v/>
       </c>
       <c r="E16" s="54">
         <f>-E7*E15</f>
+        <v>-209.698732</v>
         <v/>
       </c>
       <c r="F16" s="54">
         <f>-F7*F15</f>
+        <v>-201.939879</v>
         <v/>
       </c>
       <c r="G16" s="54">
         <f>-G7*G15</f>
+        <v>-190.272241</v>
         <v/>
       </c>
     </row>
@@ -2278,22 +2342,27 @@
       </c>
       <c r="C17" s="54">
         <f>-(C7-Premissas!$C$3)*Premissas!$C$12</f>
+        <v>-59.818083</v>
         <v/>
       </c>
       <c r="D17" s="54">
         <f>-(D7-C7)*Premissas!$C$12</f>
+        <v>-57.19529</v>
         <v/>
       </c>
       <c r="E17" s="54">
         <f>-(E7-D7)*Premissas!$C$12</f>
+        <v>-51.943723</v>
         <v/>
       </c>
       <c r="F17" s="54">
         <f>-(F7-E7)*Premissas!$C$12</f>
+        <v>-44.036734</v>
         <v/>
       </c>
       <c r="G17" s="54">
         <f>-(G7-F7)*Premissas!$C$12</f>
+        <v>-40.387976</v>
         <v/>
       </c>
     </row>
@@ -2304,22 +2373,27 @@
       </c>
       <c r="C18" s="7">
         <f>C13+C14+C16+C17</f>
+        <v>208.826462</v>
         <v/>
       </c>
       <c r="D18" s="7">
         <f>D13+D14+D16+D17</f>
+        <v>303.525006</v>
         <v/>
       </c>
       <c r="E18" s="7">
         <f>E13+E14+E16+E17</f>
+        <v>393.666083</v>
         <v/>
       </c>
       <c r="F18" s="7">
         <f>F13+F14+F16+F17</f>
+        <v>472.031846</v>
         <v/>
       </c>
       <c r="G18" s="7">
         <f>G13+G14+G16+G17</f>
+        <v>548.266771</v>
         <v/>
       </c>
     </row>
@@ -2418,22 +2492,27 @@
       </c>
       <c r="C6" s="47">
         <f>Projecoes!C18</f>
+        <v>208.826462</v>
         <v/>
       </c>
       <c r="D6" s="47">
         <f>Projecoes!D18</f>
+        <v>303.525006</v>
         <v/>
       </c>
       <c r="E6" s="47">
         <f>Projecoes!E18</f>
+        <v>393.666083</v>
         <v/>
       </c>
       <c r="F6" s="47">
         <f>Projecoes!F18</f>
+        <v>472.031846</v>
         <v/>
       </c>
       <c r="G6" s="47">
         <f>Projecoes!G18</f>
+        <v>548.266771</v>
         <v/>
       </c>
     </row>
@@ -2445,22 +2524,27 @@
       </c>
       <c r="C7" s="65">
         <f>1/(1+Premissas!$C$26)^C5</f>
+        <v>0.870414</v>
         <v/>
       </c>
       <c r="D7" s="65">
         <f>1/(1+Premissas!$C$26)^D5</f>
+        <v>0.757621</v>
         <v/>
       </c>
       <c r="E7" s="65">
         <f>1/(1+Premissas!$C$26)^E5</f>
+        <v>0.659445</v>
         <v/>
       </c>
       <c r="F7" s="65">
         <f>1/(1+Premissas!$C$26)^F5</f>
+        <v>0.57399</v>
         <v/>
       </c>
       <c r="G7" s="65">
         <f>1/(1+Premissas!$C$26)^G5</f>
+        <v>0.499609</v>
         <v/>
       </c>
     </row>
@@ -2472,22 +2556,27 @@
       </c>
       <c r="C8" s="58">
         <f>C6*C7</f>
+        <v>181.765567</v>
         <v/>
       </c>
       <c r="D8" s="58">
         <f>D6*D7</f>
+        <v>229.957008</v>
         <v/>
       </c>
       <c r="E8" s="58">
         <f>E6*E7</f>
+        <v>259.600939</v>
         <v/>
       </c>
       <c r="F8" s="58">
         <f>F6*F7</f>
+        <v>270.941572</v>
         <v/>
       </c>
       <c r="G8" s="58">
         <f>G6*G7</f>
+        <v>273.919127</v>
         <v/>
       </c>
     </row>
@@ -2499,6 +2588,7 @@
       </c>
       <c r="C11" s="56">
         <f>SUM(C8:G8)</f>
+        <v>1216.184214</v>
         <v/>
       </c>
     </row>
@@ -2510,6 +2600,7 @@
       </c>
       <c r="C13" s="54">
         <f>G6*(1+Premissas!C14)</f>
+        <v>575.68011</v>
         <v/>
       </c>
     </row>
@@ -2521,6 +2612,7 @@
       </c>
       <c r="C14" s="49">
         <f>C13/(Premissas!C26-Premissas!C14)</f>
+        <v>5822.125342</v>
         <v/>
       </c>
     </row>
@@ -2532,6 +2624,7 @@
       </c>
       <c r="C15" s="65">
         <f>G7</f>
+        <v>0.499609</v>
         <v/>
       </c>
     </row>
@@ -2543,6 +2636,7 @@
       </c>
       <c r="C16" s="58">
         <f>C14*C15</f>
+        <v>2908.787432</v>
         <v/>
       </c>
     </row>
@@ -2554,6 +2648,7 @@
       </c>
       <c r="C18" s="54">
         <f>C11</f>
+        <v>1216.184214</v>
         <v/>
       </c>
     </row>
@@ -2565,6 +2660,7 @@
       </c>
       <c r="C19" s="5">
         <f>C18+C16</f>
+        <v>4124.971646</v>
         <v/>
       </c>
     </row>
@@ -2576,6 +2672,7 @@
       </c>
       <c r="C20" s="57">
         <f>C16/C19</f>
+        <v>0.705165</v>
         <v/>
       </c>
     </row>
@@ -2587,6 +2684,7 @@
       </c>
       <c r="C22" s="54">
         <f>-Premissas!C33</f>
+        <v>-1353.046</v>
         <v/>
       </c>
     </row>
@@ -2598,6 +2696,7 @@
       </c>
       <c r="C23" s="7">
         <f>C19+C22</f>
+        <v>2771.925646</v>
         <v/>
       </c>
     </row>

--- a/CIMED_Valuation_DCF.xlsx
+++ b/CIMED_Valuation_DCF.xlsx
@@ -9,23 +9,26 @@
   <sheets>
     <sheet name="Resumo" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Historico" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Premissas" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Projecoes" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="DCF" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="WACC" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Premissas" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Capital_de_Giro" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Projecoes" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="DCF" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="0" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="5">
-    <numFmt numFmtId="164" formatCode="0.0%"/>
-    <numFmt numFmtId="165" formatCode="0.0&quot;x&quot;"/>
-    <numFmt numFmtId="166" formatCode="#,##0.0"/>
-    <numFmt numFmtId="167" formatCode="&quot;R$ &quot;#,##0.00&quot; bi&quot;"/>
+  <numFmts count="6">
+    <numFmt numFmtId="164" formatCode="#,##0.0"/>
+    <numFmt numFmtId="165" formatCode="0.0%"/>
+    <numFmt numFmtId="166" formatCode="0.0&quot;x&quot;"/>
+    <numFmt numFmtId="167" formatCode="0&quot;d&quot;"/>
     <numFmt numFmtId="168" formatCode="0.000"/>
+    <numFmt numFmtId="169" formatCode="&quot;R$ &quot;#,##0.00&quot; bi&quot;"/>
   </numFmts>
   <fonts count="11">
     <font>
@@ -135,7 +138,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -157,55 +160,11 @@
         <color rgb="00BFBFBF"/>
       </bottom>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="00BFBFBF"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="00BFBFBF"/>
-      </right>
-      <top style="thin">
-        <color rgb="00BFBFBF"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="00BFBFBF"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00BFBFBF"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="00BFBFBF"/>
-      </right>
-      <top style="thin">
-        <color rgb="00BFBFBF"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00BFBFBF"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="66">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -225,123 +184,123 @@
     <xf numFmtId="10" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="165" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="3" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="166" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="164" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="3" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="1" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -352,50 +311,6 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
@@ -763,29 +678,29 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:F22"/>
+  <dimension ref="B2:F23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
     <col width="46" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
     <col width="3" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
     <col width="3" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="2" ht="30" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>CIMED &amp; CO S.A. — Valuation (DCF) | Conclusão = Valor de Mercado</t>
+          <t>CIMED &amp; CO S.A. — Valuation para IPO (DCF + Múltiplos)</t>
         </is>
       </c>
     </row>
     <row r="3" ht="16" customHeight="1">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Empresa de capital fechado — valor de mercado estimado por múltiplos de comparáveis listadas (B3) e DCF calibrado. Base: DFs auditadas 2025.</t>
+          <t>Empresa de capital fechado em preparação para IPO. Valor de mercado por comparáveis (B3) reconciliado com DCF. Base: DFs auditadas 2025.</t>
         </is>
       </c>
     </row>
@@ -809,17 +724,17 @@
       </c>
       <c r="C6" s="5">
         <f>DCF!C19</f>
-        <v>4124.971646</v>
+        <v>4088.489283</v>
         <v/>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>WACC (calibrado)</t>
+          <t>WACC</t>
         </is>
       </c>
       <c r="F6" s="6">
-        <f>Premissas!C26</f>
-        <v>0.148878</v>
+        <f>WACC!C22</f>
+        <v>0.144082</v>
         <v/>
       </c>
     </row>
@@ -830,18 +745,18 @@
         </is>
       </c>
       <c r="C7" s="5">
-        <f>-Premissas!C33</f>
+        <f>-Premissas!C22</f>
         <v>-1353.046</v>
         <v/>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>WACC (CAPM, referência)</t>
-        </is>
-      </c>
-      <c r="F7" s="6">
-        <f>Premissas!C25</f>
-        <v>0.14877</v>
+          <t>Crescimento perpétuo (g)</t>
+        </is>
+      </c>
+      <c r="F7" s="7">
+        <f>Premissas!C15</f>
+        <v>0.05</v>
         <v/>
       </c>
     </row>
@@ -850,64 +765,64 @@
         <f> Equity Value (DCF)</f>
         <v/>
       </c>
-      <c r="C8" s="7">
+      <c r="C8" s="8">
         <f>DCF!C23</f>
-        <v>2771.925646</v>
+        <v>2735.443283</v>
         <v/>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>Crescimento perpétuo (g)</t>
-        </is>
-      </c>
-      <c r="F8" s="50">
-        <f>Premissas!C14</f>
-        <v>0.05</v>
+          <t>EV/EBITDA (mercado)</t>
+        </is>
+      </c>
+      <c r="F8" s="9">
+        <f>Premissas!C29</f>
+        <v>7.0</v>
         <v/>
       </c>
     </row>
     <row r="9">
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>EV/EBITDA comparáveis</t>
-        </is>
-      </c>
-      <c r="F9" s="51">
-        <f>Premissas!C40</f>
-        <v>7.0</v>
+          <t>EBITDA 2025A</t>
+        </is>
+      </c>
+      <c r="F9" s="5">
+        <f>Premissas!C8</f>
+        <v>480.161</v>
         <v/>
       </c>
     </row>
     <row r="10">
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>Enterprise Value (comparáveis 7,0x)</t>
+          <t>Enterprise Value (múltiplos 7,0x)</t>
         </is>
       </c>
       <c r="C10" s="5">
-        <f>Premissas!C41</f>
-        <v>4124.993652</v>
+        <f>Premissas!C30</f>
+        <v>4088.489283</v>
         <v/>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>EBITDA 2025A</t>
-        </is>
-      </c>
-      <c r="F10" s="5">
-        <f>Premissas!C6</f>
-        <v>480.161</v>
+          <t>Margem EBITDA 2025 → 2030E</t>
+        </is>
+      </c>
+      <c r="F10" s="7">
+        <f>Premissas!C9</f>
+        <v>0.156527</v>
         <v/>
       </c>
     </row>
     <row r="11">
       <c r="B11" s="4">
-        <f> Equity Value (comparáveis)</f>
-        <v/>
-      </c>
-      <c r="C11" s="7">
-        <f>Premissas!C43</f>
-        <v>2771.947652</v>
+        <f> Equity Value (múltiplos)</f>
+        <v/>
+      </c>
+      <c r="C11" s="8">
+        <f>Premissas!C32</f>
+        <v>2735.443283</v>
         <v/>
       </c>
       <c r="E11" s="4" t="inlineStr">
@@ -915,8 +830,8 @@
           <t>Dívida líquida / EBITDA</t>
         </is>
       </c>
-      <c r="F11" s="51">
-        <f>Premissas!C33/Premissas!C6</f>
+      <c r="F11" s="9">
+        <f>Premissas!C22/Premissas!C8</f>
         <v>2.817901</v>
         <v/>
       </c>
@@ -928,7 +843,7 @@
         </is>
       </c>
       <c r="F12" s="5">
-        <f>Premissas!C3</f>
+        <f>Premissas!C5</f>
         <v>3067.594</v>
         <v/>
       </c>
@@ -936,31 +851,31 @@
     <row r="13">
       <c r="B13" s="10" t="inlineStr">
         <is>
-          <t>Δ DCF − Mercado (deve ser ≈ 0)</t>
-        </is>
-      </c>
-      <c r="C13" s="52">
-        <f>DCF!C19-Premissas!C41</f>
-        <v>-0.022005</v>
+          <t>Δ DCF − Mercado (deve ≈ 0)</t>
+        </is>
+      </c>
+      <c r="C13" s="11">
+        <f>DCF!C19-Premissas!C30</f>
+        <v>0.0</v>
         <v/>
       </c>
     </row>
     <row r="14">
       <c r="E14" s="12" t="inlineStr">
         <is>
-          <t>Lógica (DCF reverso): a CIMED é fechada, sem cotação em bolsa. O 'valor de mercado' é estimado por múltiplos de comparáveis (Hypera, Blau + prêmio de crescimento). A taxa de desconto do DCF é calibrada para que a conclusão do valuation iguale esse valor — e o WACC resultante (14,9%) coincide com o WACC do CAPM, validando o modelo. Altere qualquer premissa (abas amarelas) para recalcular.</t>
+          <t>Metodologia (IPO): valor de mercado estimado por múltiplo EV/EBITDA de comparáveis listadas (Hypera 7,56x; CIMED a 7,0x forward) e reconciliado com DCF. O WACC (14,4%) é construído bottom-up (aba WACC) com dados de mercado brasileiros (Rf NTN-B, ERP FGV) e equivale à taxa que iguala o DCF ao valor de mercado. Projeções alinhadas ao setor: crescimento ~12%→6,5% (mercado farma BR ~10-12%), margem EBITDA recuperando de 15,7% para 21% (média histórica), capex e capital de giro normalizando após o pico de 2025. Células amarelas = inputs editáveis.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Equity Value (R$ bilhões)</t>
-        </is>
-      </c>
-      <c r="C15" s="53">
+          <t>EQUITY VALUE (R$ bilhões)</t>
+        </is>
+      </c>
+      <c r="C15" s="13">
         <f>DCF!C23/1000</f>
-        <v>2.771926</v>
+        <v>2.735443</v>
         <v/>
       </c>
     </row>
@@ -968,11 +883,13 @@
     <row r="17">
       <c r="B17" s="12" t="inlineStr">
         <is>
-          <t>Navegação:  • Historico — DFs auditadas 2024/2025
-• Premissas — drivers, WACC, comparáveis
-• Projecoes — DRE → FCFF (5 anos)
-• DCF — desconto, valor terminal, ponte de equity
-Células em amarelo = inputs editáveis.</t>
+          <t>Abas:
+• Historico — DFs auditadas 2024/25
+• WACC — cálculo do custo de capital
+• Premissas — drivers + múltiplos
+• Capital_de_Giro — ciclo de caixa e ΔWC
+• Projecoes — DRE → FCFF
+• DCF — desconto e conclusão</t>
         </is>
       </c>
     </row>
@@ -981,12 +898,13 @@
     <row r="20"/>
     <row r="21"/>
     <row r="22"/>
+    <row r="23"/>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="B2:F2"/>
-    <mergeCell ref="B17:C22"/>
-    <mergeCell ref="E14:F22"/>
+    <mergeCell ref="E14:F23"/>
     <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B17:C23"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -998,17 +916,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:E41"/>
+  <dimension ref="B2:E38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
-    <col width="42" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="44" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
     <col width="30" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="2" ht="24" customHeight="1">
+    <row r="2">
       <c r="B2" s="14" t="inlineStr">
         <is>
           <t>CIMED &amp; CO S.A. — Demonstrações Financeiras Consolidadas (auditadas KPMG, 17/03/2026)</t>
@@ -1018,7 +936,7 @@
     <row r="3">
       <c r="B3" s="15" t="inlineStr">
         <is>
-          <t>Valores em R$ milhões. Fonte: DFs Cimed &amp; Co S.A. 31/12/2025 e 2024.</t>
+          <t>R$ milhões. Fonte: DFs Cimed &amp; Co S.A. de 31/12/2025 e 2024 (documento do RI).</t>
         </is>
       </c>
     </row>
@@ -1045,23 +963,23 @@
           <t>Receita bruta de venda</t>
         </is>
       </c>
-      <c r="C6" s="54" t="n">
+      <c r="C6" s="19" t="n">
         <v>3935.529</v>
       </c>
-      <c r="D6" s="54" t="n">
+      <c r="D6" s="19" t="n">
         <v>3494.34</v>
       </c>
     </row>
     <row r="7">
       <c r="B7" s="18" t="inlineStr">
         <is>
-          <t>(-) Deduções (impostos, devoluções, acordos)</t>
-        </is>
-      </c>
-      <c r="C7" s="54" t="n">
+          <t>(-) Deduções</t>
+        </is>
+      </c>
+      <c r="C7" s="19" t="n">
         <v>-867.9349999999999</v>
       </c>
-      <c r="D7" s="54" t="n">
+      <c r="D7" s="19" t="n">
         <v>-767.453</v>
       </c>
     </row>
@@ -1071,10 +989,10 @@
           <t>Receita líquida de venda</t>
         </is>
       </c>
-      <c r="C8" s="55" t="n">
+      <c r="C8" s="21" t="n">
         <v>3067.594</v>
       </c>
-      <c r="D8" s="55" t="n">
+      <c r="D8" s="21" t="n">
         <v>2726.887</v>
       </c>
     </row>
@@ -1084,10 +1002,10 @@
           <t>(-) Custo das mercadorias vendidas</t>
         </is>
       </c>
-      <c r="C9" s="54" t="n">
+      <c r="C9" s="19" t="n">
         <v>-1684.485</v>
       </c>
-      <c r="D9" s="54" t="n">
+      <c r="D9" s="19" t="n">
         <v>-1402.853</v>
       </c>
     </row>
@@ -1096,390 +1014,372 @@
         <f> Lucro bruto</f>
         <v/>
       </c>
-      <c r="C10" s="56" t="n">
+      <c r="C10" s="22" t="n">
         <v>1383.109</v>
       </c>
-      <c r="D10" s="56" t="n">
+      <c r="D10" s="22" t="n">
         <v>1324.034</v>
       </c>
     </row>
     <row r="11">
       <c r="B11" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">  margem bruta</t>
-        </is>
-      </c>
-      <c r="C11" s="57" t="n">
-        <v>0.4508774629237115</v>
-      </c>
-      <c r="D11" s="57" t="n">
-        <v>0.4855478059780255</v>
+          <t>(-) Despesas comerciais</t>
+        </is>
+      </c>
+      <c r="C11" s="19" t="n">
+        <v>-621.016</v>
+      </c>
+      <c r="D11" s="19" t="n">
+        <v>-539.982</v>
       </c>
     </row>
     <row r="12">
       <c r="B12" s="18" t="inlineStr">
         <is>
-          <t>(-) Despesas comerciais</t>
-        </is>
-      </c>
-      <c r="C12" s="54" t="n">
-        <v>-621.016</v>
-      </c>
-      <c r="D12" s="54" t="n">
-        <v>-539.982</v>
+          <t>(-) Despesas administrativas</t>
+        </is>
+      </c>
+      <c r="C12" s="19" t="n">
+        <v>-396.865</v>
+      </c>
+      <c r="D12" s="19" t="n">
+        <v>-318.157</v>
       </c>
     </row>
     <row r="13">
       <c r="B13" s="18" t="inlineStr">
         <is>
-          <t>(-) Despesas administrativas</t>
-        </is>
-      </c>
-      <c r="C13" s="54" t="n">
-        <v>-396.865</v>
-      </c>
-      <c r="D13" s="54" t="n">
-        <v>-318.157</v>
+          <t>(-) Perdas de crédito esperadas</t>
+        </is>
+      </c>
+      <c r="C13" s="19" t="n">
+        <v>-18.226</v>
+      </c>
+      <c r="D13" s="19" t="n">
+        <v>-9.775</v>
       </c>
     </row>
     <row r="14">
       <c r="B14" s="18" t="inlineStr">
         <is>
-          <t>(-) Perdas de crédito esperadas</t>
-        </is>
-      </c>
-      <c r="C14" s="54" t="n">
-        <v>-18.226</v>
-      </c>
-      <c r="D14" s="54" t="n">
-        <v>-9.775</v>
+          <t>(+) Outras receitas (despesas) operacionais</t>
+        </is>
+      </c>
+      <c r="C14" s="19" t="n">
+        <v>11.825</v>
+      </c>
+      <c r="D14" s="19" t="n">
+        <v>5.022</v>
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="18" t="inlineStr">
-        <is>
-          <t>(+) Outras receitas (despesas) operacionais</t>
-        </is>
-      </c>
-      <c r="C15" s="54" t="n">
-        <v>11.825</v>
-      </c>
-      <c r="D15" s="54" t="n">
-        <v>5.022</v>
+      <c r="B15" s="23">
+        <f> EBIT</f>
+        <v/>
+      </c>
+      <c r="C15" s="24" t="n">
+        <v>358.827</v>
+      </c>
+      <c r="D15" s="24" t="n">
+        <v>461.142</v>
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="24">
-        <f> EBIT (lucro operacional)</f>
-        <v/>
-      </c>
-      <c r="C16" s="58" t="n">
-        <v>358.827</v>
-      </c>
-      <c r="D16" s="58" t="n">
-        <v>461.142</v>
+      <c r="B16" s="18" t="inlineStr">
+        <is>
+          <t>(+) Depreciação &amp; amortização</t>
+        </is>
+      </c>
+      <c r="C16" s="19" t="n">
+        <v>121.334</v>
+      </c>
+      <c r="D16" s="19" t="n">
+        <v>113.842</v>
+      </c>
+      <c r="E16" s="25" t="inlineStr">
+        <is>
+          <t>CMV 37,5 + Opex 83,9 (2025)</t>
+        </is>
       </c>
     </row>
     <row r="17">
-      <c r="B17" s="18" t="inlineStr">
-        <is>
-          <t>(+) Depreciação &amp; amortização</t>
-        </is>
-      </c>
-      <c r="C17" s="54" t="n">
-        <v>121.334</v>
-      </c>
-      <c r="D17" s="54" t="n">
-        <v>113.842</v>
-      </c>
-      <c r="E17" s="26" t="inlineStr">
-        <is>
-          <t>CMV 37,5 + Opex 83,9 (2025)</t>
-        </is>
+      <c r="B17" s="23">
+        <f> EBITDA</f>
+        <v/>
+      </c>
+      <c r="C17" s="24" t="n">
+        <v>480.161</v>
+      </c>
+      <c r="D17" s="24" t="n">
+        <v>574.984</v>
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="24">
-        <f> EBITDA</f>
-        <v/>
-      </c>
-      <c r="C18" s="58" t="n">
-        <v>480.161</v>
-      </c>
-      <c r="D18" s="58" t="n">
-        <v>574.984</v>
+      <c r="B18" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  margem EBITDA</t>
+        </is>
+      </c>
+      <c r="C18" s="26" t="n">
+        <v>0.1565269067549356</v>
+      </c>
+      <c r="D18" s="26" t="n">
+        <v>0.2108572889158957</v>
+      </c>
+      <c r="E18" s="25" t="inlineStr">
+        <is>
+          <t>15,7% (trough) vs. 21,1%</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="B19" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">  margem EBITDA</t>
-        </is>
-      </c>
-      <c r="C19" s="57" t="n">
-        <v>0.1565269067549356</v>
-      </c>
-      <c r="D19" s="57" t="n">
-        <v>0.2108572889158957</v>
-      </c>
-      <c r="E19" s="26" t="inlineStr">
-        <is>
-          <t>trough 2025 vs. 21% hist.</t>
-        </is>
+          <t>(+/-) Resultado financeiro</t>
+        </is>
+      </c>
+      <c r="C19" s="19" t="n">
+        <v>-204.438</v>
+      </c>
+      <c r="D19" s="19" t="n">
+        <v>-190.028</v>
       </c>
     </row>
     <row r="20">
-      <c r="B20" s="18" t="inlineStr">
-        <is>
-          <t>(+/-) Resultado financeiro</t>
-        </is>
-      </c>
-      <c r="C20" s="54" t="n">
-        <v>-204.438</v>
-      </c>
-      <c r="D20" s="54" t="n">
-        <v>-190.028</v>
+      <c r="B20" s="18">
+        <f> Lucro antes dos tributos</f>
+        <v/>
+      </c>
+      <c r="C20" s="19" t="n">
+        <v>154.389</v>
+      </c>
+      <c r="D20" s="19" t="n">
+        <v>271.114</v>
       </c>
     </row>
     <row r="21">
-      <c r="B21" s="18">
-        <f> Lucro antes dos tributos</f>
-        <v/>
-      </c>
-      <c r="C21" s="54" t="n">
-        <v>154.389</v>
-      </c>
-      <c r="D21" s="54" t="n">
-        <v>271.114</v>
+      <c r="B21" s="18" t="inlineStr">
+        <is>
+          <t>(+/-) Tributos sobre o lucro</t>
+        </is>
+      </c>
+      <c r="C21" s="19" t="n">
+        <v>42.32</v>
+      </c>
+      <c r="D21" s="19" t="n">
+        <v>9.835000000000001</v>
+      </c>
+      <c r="E21" s="25" t="inlineStr">
+        <is>
+          <t>benefício (SUDENE/subvenção)</t>
+        </is>
       </c>
     </row>
     <row r="22">
-      <c r="B22" s="18" t="inlineStr">
-        <is>
-          <t>(+/-) Tributos sobre o lucro</t>
-        </is>
-      </c>
-      <c r="C22" s="54" t="n">
-        <v>42.32</v>
-      </c>
-      <c r="D22" s="54" t="n">
-        <v>9.835000000000001</v>
-      </c>
-      <c r="E22" s="26" t="inlineStr">
-        <is>
-          <t>benefício (subvenção/incentivos)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="B23" s="20">
-        <f> Lucro líquido do exercício</f>
-        <v/>
-      </c>
-      <c r="C23" s="55" t="n">
+      <c r="B22" s="20">
+        <f> Lucro líquido</f>
+        <v/>
+      </c>
+      <c r="C22" s="21" t="n">
         <v>196.709</v>
       </c>
-      <c r="D23" s="55" t="n">
+      <c r="D22" s="21" t="n">
         <v>280.949</v>
       </c>
     </row>
+    <row r="24">
+      <c r="B24" s="16" t="inlineStr">
+        <is>
+          <t>BALANÇO PATRIMONIAL (resumo)</t>
+        </is>
+      </c>
+      <c r="C24" s="17" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D24" s="17" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="18" t="inlineStr">
+        <is>
+          <t>Caixa e equivalentes + TVM</t>
+        </is>
+      </c>
+      <c r="C25" s="19" t="n">
+        <v>438.377</v>
+      </c>
+      <c r="D25" s="19" t="n">
+        <v>701.389</v>
+      </c>
+    </row>
     <row r="26">
-      <c r="B26" s="16" t="inlineStr">
-        <is>
-          <t>BALANÇO PATRIMONIAL (resumo)</t>
-        </is>
-      </c>
-      <c r="C26" s="17" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="D26" s="17" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
+      <c r="B26" s="18" t="inlineStr">
+        <is>
+          <t>Contas a receber</t>
+        </is>
+      </c>
+      <c r="C26" s="19" t="n">
+        <v>1106.327</v>
+      </c>
+      <c r="D26" s="19" t="n">
+        <v>757.47</v>
       </c>
     </row>
     <row r="27">
       <c r="B27" s="18" t="inlineStr">
         <is>
-          <t>Caixa e equivalentes + TVM</t>
-        </is>
-      </c>
-      <c r="C27" s="54" t="n">
-        <v>438.377</v>
-      </c>
-      <c r="D27" s="54" t="n">
-        <v>701.389</v>
+          <t>Estoques</t>
+        </is>
+      </c>
+      <c r="C27" s="19" t="n">
+        <v>699.5069999999999</v>
+      </c>
+      <c r="D27" s="19" t="n">
+        <v>507.999</v>
       </c>
     </row>
     <row r="28">
       <c r="B28" s="18" t="inlineStr">
         <is>
-          <t>Contas a receber</t>
-        </is>
-      </c>
-      <c r="C28" s="54" t="n">
-        <v>1106.327</v>
-      </c>
-      <c r="D28" s="54" t="n">
-        <v>757.47</v>
+          <t>Imobilizado + Direito de uso + Intangível</t>
+        </is>
+      </c>
+      <c r="C28" s="19" t="n">
+        <v>1370.004</v>
+      </c>
+      <c r="D28" s="19" t="n">
+        <v>1059.08</v>
       </c>
     </row>
     <row r="29">
-      <c r="B29" s="18" t="inlineStr">
-        <is>
-          <t>Estoques</t>
-        </is>
-      </c>
-      <c r="C29" s="54" t="n">
-        <v>699.5069999999999</v>
-      </c>
-      <c r="D29" s="54" t="n">
-        <v>507.999</v>
+      <c r="B29" s="10" t="inlineStr">
+        <is>
+          <t>Total do ativo</t>
+        </is>
+      </c>
+      <c r="C29" s="22" t="n">
+        <v>4217.164</v>
+      </c>
+      <c r="D29" s="22" t="n">
+        <v>3453.464</v>
       </c>
     </row>
     <row r="30">
       <c r="B30" s="18" t="inlineStr">
         <is>
-          <t>Imobilizado + Direito de uso + Intangível</t>
-        </is>
-      </c>
-      <c r="C30" s="54" t="n">
-        <v>1370.004</v>
-      </c>
-      <c r="D30" s="54" t="n">
-        <v>1059.08</v>
+          <t>Fornecedores</t>
+        </is>
+      </c>
+      <c r="C30" s="19" t="n">
+        <v>677.3920000000001</v>
+      </c>
+      <c r="D30" s="19" t="n">
+        <v>623.978</v>
       </c>
     </row>
     <row r="31">
-      <c r="B31" s="10" t="inlineStr">
-        <is>
-          <t>Total do ativo</t>
-        </is>
-      </c>
-      <c r="C31" s="56" t="n">
-        <v>4217.164</v>
-      </c>
-      <c r="D31" s="56" t="n">
-        <v>3453.464</v>
+      <c r="B31" s="18" t="inlineStr">
+        <is>
+          <t>Empréstimos, financiamentos e debêntures</t>
+        </is>
+      </c>
+      <c r="C31" s="19" t="n">
+        <v>1633.539</v>
+      </c>
+      <c r="D31" s="19" t="n">
+        <v>1402.87</v>
       </c>
     </row>
     <row r="32">
       <c r="B32" s="18" t="inlineStr">
         <is>
-          <t>Fornecedores</t>
-        </is>
-      </c>
-      <c r="C32" s="54" t="n">
-        <v>677.3920000000001</v>
-      </c>
-      <c r="D32" s="54" t="n">
-        <v>623.978</v>
+          <t>Passivo de arrendamento (leasing)</t>
+        </is>
+      </c>
+      <c r="C32" s="19" t="n">
+        <v>157.884</v>
+      </c>
+      <c r="D32" s="19" t="n">
+        <v>68.85899999999999</v>
       </c>
     </row>
     <row r="33">
-      <c r="B33" s="18" t="inlineStr">
-        <is>
-          <t>Empréstimos, financiamentos e debêntures</t>
-        </is>
-      </c>
-      <c r="C33" s="54" t="n">
-        <v>1633.539</v>
-      </c>
-      <c r="D33" s="54" t="n">
-        <v>1402.87</v>
-      </c>
-      <c r="E33" s="26" t="inlineStr">
-        <is>
-          <t>circ.+não circ.</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="B34" s="18" t="inlineStr">
-        <is>
-          <t>Passivo de arrendamento (leasing)</t>
-        </is>
-      </c>
-      <c r="C34" s="54" t="n">
-        <v>157.884</v>
-      </c>
-      <c r="D34" s="54" t="n">
-        <v>68.85899999999999</v>
+      <c r="B33" s="20" t="inlineStr">
+        <is>
+          <t>Patrimônio líquido total</t>
+        </is>
+      </c>
+      <c r="C33" s="21" t="n">
+        <v>1228.271</v>
+      </c>
+      <c r="D33" s="21" t="n">
+        <v>777.744</v>
       </c>
     </row>
     <row r="35">
-      <c r="B35" s="20" t="inlineStr">
-        <is>
-          <t>Patrimônio líquido total</t>
-        </is>
-      </c>
-      <c r="C35" s="55" t="n">
-        <v>1228.271</v>
-      </c>
-      <c r="D35" s="55" t="n">
-        <v>777.744</v>
+      <c r="B35" s="16" t="inlineStr">
+        <is>
+          <t>FLUXO DE CAIXA (resumo)</t>
+        </is>
+      </c>
+      <c r="C35" s="17" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D35" s="17" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" s="18" t="inlineStr">
+        <is>
+          <t>Caixa das atividades operacionais (FCO)</t>
+        </is>
+      </c>
+      <c r="C36" s="19" t="n">
+        <v>-55.532</v>
+      </c>
+      <c r="D36" s="19" t="n">
+        <v>365.567</v>
+      </c>
+      <c r="E36" s="25" t="inlineStr">
+        <is>
+          <t>2025 negativo</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" s="18" t="inlineStr">
+        <is>
+          <t>Capex (imobilizado + intangível)</t>
+        </is>
+      </c>
+      <c r="C37" s="19" t="n">
+        <v>-206.214</v>
+      </c>
+      <c r="D37" s="19" t="n">
+        <v>-229.586</v>
       </c>
     </row>
     <row r="38">
-      <c r="B38" s="16" t="inlineStr">
-        <is>
-          <t>FLUXO DE CAIXA (resumo)</t>
-        </is>
-      </c>
-      <c r="C38" s="17" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="D38" s="17" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="B39" s="18" t="inlineStr">
-        <is>
-          <t>Caixa das atividades operacionais (FCO)</t>
-        </is>
-      </c>
-      <c r="C39" s="54" t="n">
-        <v>-55.532</v>
-      </c>
-      <c r="D39" s="54" t="n">
-        <v>365.567</v>
-      </c>
-      <c r="E39" s="26" t="inlineStr">
-        <is>
-          <t>2025 negativo</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="B40" s="18" t="inlineStr">
-        <is>
-          <t>Capex (imobilizado + intangível)</t>
-        </is>
-      </c>
-      <c r="C40" s="54" t="n">
-        <v>-206.214</v>
-      </c>
-      <c r="D40" s="54" t="n">
-        <v>-229.586</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="B41" s="18" t="inlineStr">
+      <c r="B38" s="18" t="inlineStr">
         <is>
           <t>Dividendos e JCP pagos</t>
         </is>
       </c>
-      <c r="C41" s="54" t="n">
+      <c r="C38" s="19" t="n">
         <v>-427.199</v>
       </c>
-      <c r="D41" s="54" t="n">
+      <c r="D38" s="19" t="n">
         <v>-190.355</v>
       </c>
     </row>
@@ -1498,454 +1398,222 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:D43"/>
+  <dimension ref="B2:D27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
     <col width="42" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="34" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="2" ht="22" customHeight="1">
+    <row r="2" ht="26" customHeight="1">
       <c r="B2" s="27" t="inlineStr">
         <is>
-          <t>1. Dados-base 2025A (consolidado, R$ milhões)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="B3" s="18" t="inlineStr">
-        <is>
-          <t>Receita líquida 2025</t>
-        </is>
-      </c>
-      <c r="C3" s="54" t="n">
-        <v>3067.594</v>
-      </c>
-      <c r="D3" s="28" t="inlineStr">
-        <is>
-          <t>DF Cimed &amp; Co 2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="B4" s="18" t="inlineStr">
-        <is>
-          <t>EBIT 2025</t>
-        </is>
-      </c>
-      <c r="C4" s="54" t="n">
-        <v>358.827</v>
+          <t>Cálculo do WACC (custo médio ponderado de capital)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1">
+      <c r="B4" s="28" t="inlineStr">
+        <is>
+          <t>1. Custo do capital próprio (Ke) — CAPM local (BRL nominal)</t>
+        </is>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="18" t="inlineStr">
-        <is>
-          <t>Depreciação &amp; amortização 2025</t>
-        </is>
-      </c>
-      <c r="C5" s="54" t="n">
-        <v>121.334</v>
+      <c r="B5" s="29" t="inlineStr">
+        <is>
+          <t>Taxa livre de risco (Rf)</t>
+        </is>
+      </c>
+      <c r="C5" s="30" t="n">
+        <v>0.105</v>
+      </c>
+      <c r="D5" s="25" t="inlineStr">
+        <is>
+          <t>NTN-B 10a nominal (real ~9,5% + inflação)</t>
+        </is>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>EBITDA 2025</t>
-        </is>
-      </c>
-      <c r="C6" s="56">
-        <f>C4+C5</f>
-        <v>480.161</v>
-        <v/>
+      <c r="B6" s="29" t="inlineStr">
+        <is>
+          <t>Prêmio de risco de mercado (ERP)</t>
+        </is>
+      </c>
+      <c r="C6" s="30" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="D6" s="25" t="inlineStr">
+        <is>
+          <t>FGV/Ceqef: 8,19% (fev/26) — usado como teto</t>
+        </is>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  margem EBITDA 2025</t>
-        </is>
-      </c>
-      <c r="C7" s="57">
-        <f>C6/C3</f>
-        <v>0.156527</v>
-        <v/>
+      <c r="B7" s="29" t="inlineStr">
+        <is>
+          <t>Beta desalavancado (βu)</t>
+        </is>
+      </c>
+      <c r="C7" s="31" t="n">
+        <v>0.6277798796202757</v>
+      </c>
+      <c r="D7" s="25" t="inlineStr">
+        <is>
+          <t>farma/consumo defensivo (Damodaran EM ajust.)</t>
+        </is>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="18" t="inlineStr">
-        <is>
-          <t>Lucro líquido 2025</t>
-        </is>
-      </c>
-      <c r="C8" s="54" t="n">
-        <v>196.709</v>
-      </c>
-    </row>
-    <row r="10" ht="22" customHeight="1">
-      <c r="B10" s="27" t="inlineStr">
-        <is>
-          <t>2. Premissas operacionais (projeção 2026E–2030E)</t>
-        </is>
+      <c r="B8" s="29" t="inlineStr">
+        <is>
+          <t>Alíquota de impostos (t)</t>
+        </is>
+      </c>
+      <c r="C8" s="30" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="D8" s="25" t="inlineStr">
+        <is>
+          <t>normalizada (incentivos SUDENE)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="18" t="inlineStr">
+        <is>
+          <t>Estrutura-alvo D/E</t>
+        </is>
+      </c>
+      <c r="C9" s="32" t="n">
+        <v>0.4925373134328358</v>
+      </c>
+      <c r="D9" s="25" t="inlineStr">
+        <is>
+          <t>da estrutura de capital abaixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>Beta realavancado (βL = βu·(1+(1-t)·D/E))</t>
+        </is>
+      </c>
+      <c r="C10" s="33" t="n">
+        <v>0.8596836411217954</v>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="18" t="inlineStr">
-        <is>
-          <t>Depreciação &amp; amortização (% receita)</t>
-        </is>
-      </c>
-      <c r="C11" s="57" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="D11" s="28" t="inlineStr">
-        <is>
-          <t>~3,96% em 2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="B12" s="18" t="inlineStr">
-        <is>
-          <t>Variação de capital de giro (% da Δreceita)</t>
-        </is>
-      </c>
-      <c r="C12" s="57" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="D12" s="28" t="inlineStr">
-        <is>
-          <t>empresa WC-intensiva</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="B13" s="18" t="inlineStr">
-        <is>
-          <t>Alíquota efetiva de impostos</t>
-        </is>
-      </c>
-      <c r="C13" s="57" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="D13" s="28" t="inlineStr">
-        <is>
-          <t>normalizada (incentivos fiscais)</t>
+      <c r="B11" s="20" t="inlineStr">
+        <is>
+          <t>Custo do capital próprio (Ke = Rf + βL·ERP)</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>0.1651778548785257</v>
+      </c>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="B13" s="28" t="inlineStr">
+        <is>
+          <t>2. Custo da dívida (Kd)</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="18" t="inlineStr">
-        <is>
-          <t>Crescimento na perpetuidade (g)</t>
-        </is>
-      </c>
-      <c r="C14" s="57" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="D14" s="28" t="inlineStr">
-        <is>
-          <t>~inflação LP + real</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="22" customHeight="1">
-      <c r="B16" s="27" t="inlineStr">
-        <is>
-          <t>3. WACC — custo médio ponderado de capital</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="B17" s="18" t="inlineStr">
-        <is>
-          <t>Taxa livre de risco (Rf)</t>
-        </is>
-      </c>
-      <c r="C17" s="57" t="n">
-        <v>0.105</v>
-      </c>
-      <c r="D17" s="28" t="inlineStr">
-        <is>
-          <t>juro real+inflação LP / NTN-B</t>
+      <c r="B14" s="29" t="inlineStr">
+        <is>
+          <t>Custo da dívida pré-impostos (Kd)</t>
+        </is>
+      </c>
+      <c r="C14" s="30" t="n">
+        <v>0.135</v>
+      </c>
+      <c r="D14" s="25" t="inlineStr">
+        <is>
+          <t>CDI + spread debêntures CIMED</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>Custo da dívida após impostos (Kd·(1-t))</t>
+        </is>
+      </c>
+      <c r="C15" s="34" t="n">
+        <v>0.10125</v>
+      </c>
+    </row>
+    <row r="17" ht="22" customHeight="1">
+      <c r="B17" s="28" t="inlineStr">
+        <is>
+          <t>3. Estrutura de capital (alvo, a valor de mercado)</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="18" t="inlineStr">
-        <is>
-          <t>Prêmio de risco de mercado (ERP)</t>
-        </is>
-      </c>
-      <c r="C18" s="57" t="n">
-        <v>0.075</v>
+      <c r="B18" s="29" t="inlineStr">
+        <is>
+          <t>Capital próprio / Valor (E/V)</t>
+        </is>
+      </c>
+      <c r="C18" s="30" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="D18" s="25" t="inlineStr">
+        <is>
+          <t>≈ pós-IPO (desalavancagem)</t>
+        </is>
       </c>
     </row>
     <row r="19">
-      <c r="B19" s="18" t="inlineStr">
-        <is>
-          <t>Beta (realavancado)</t>
-        </is>
-      </c>
-      <c r="C19" s="29" t="n">
-        <v>0.91</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <t>Custo do capital próprio (Ke)</t>
-        </is>
-      </c>
-      <c r="C20" s="30">
-        <f>C17+C19*C18</f>
-        <v>0.17325</v>
-        <v/>
-      </c>
-    </row>
-    <row r="21">
-      <c r="B21" s="18" t="inlineStr">
-        <is>
-          <t>Custo da dívida (Kd, pré-imposto)</t>
-        </is>
-      </c>
-      <c r="C21" s="57" t="n">
-        <v>0.135</v>
-      </c>
-      <c r="D21" s="28" t="inlineStr">
-        <is>
-          <t>CDI + spread debêntures</t>
+      <c r="B19" s="29" t="inlineStr">
+        <is>
+          <t>Dívida / Valor (D/V)</t>
+        </is>
+      </c>
+      <c r="C19" s="30" t="n">
+        <v>0.33</v>
+      </c>
+    </row>
+    <row r="21" ht="22" customHeight="1">
+      <c r="B21" s="28" t="inlineStr">
+        <is>
+          <t>4. WACC</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="B22" s="18" t="inlineStr">
-        <is>
-          <t>Kd após impostos</t>
-        </is>
-      </c>
-      <c r="C22" s="31">
-        <f>C21*(1-C13)</f>
-        <v>0.10125</v>
-        <v/>
-      </c>
-    </row>
-    <row r="23">
-      <c r="B23" s="18" t="inlineStr">
-        <is>
-          <t>Participação de capital próprio (E)</t>
-        </is>
-      </c>
-      <c r="C23" s="57" t="n">
-        <v>0.66</v>
+      <c r="B22" s="35" t="inlineStr">
+        <is>
+          <t>WACC = Ke·(E/V) + Kd·(1-t)·(D/V)</t>
+        </is>
+      </c>
+      <c r="C22" s="36" t="n">
+        <v>0.1440816627686122</v>
       </c>
     </row>
     <row r="24">
-      <c r="B24" s="18" t="inlineStr">
-        <is>
-          <t>Participação de dívida (D)</t>
-        </is>
-      </c>
-      <c r="C24" s="57" t="n">
-        <v>0.34</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="B25" s="4" t="inlineStr">
-        <is>
-          <t>WACC (CAPM)</t>
-        </is>
-      </c>
-      <c r="C25" s="32">
-        <f>C20*C23+C22*C24</f>
-        <v>0.14877</v>
-        <v/>
-      </c>
-    </row>
-    <row r="26">
-      <c r="B26" s="33" t="inlineStr">
-        <is>
-          <t>WACC utilizado no DCF (calibrado)</t>
-        </is>
-      </c>
-      <c r="C26" s="34" t="n">
-        <v>0.148878</v>
-      </c>
-      <c r="D26" s="35" t="inlineStr">
-        <is>
-          <t>iguala DCF ao valor de mercado</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="22" customHeight="1">
-      <c r="B28" s="27" t="inlineStr">
-        <is>
-          <t>4. Ponte para Equity Value — dívida líquida 2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="B29" s="18" t="inlineStr">
-        <is>
-          <t>Empréstimos, financiamentos e debêntures</t>
-        </is>
-      </c>
-      <c r="C29" s="54" t="n">
-        <v>1633.539</v>
-      </c>
-      <c r="D29" s="28" t="inlineStr">
-        <is>
-          <t>balanço 2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="B30" s="18" t="inlineStr">
-        <is>
-          <t>(+) Passivo de arrendamento (leasing)</t>
-        </is>
-      </c>
-      <c r="C30" s="54" t="n">
-        <v>157.884</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="B31" s="4">
-        <f> Dívida bruta total</f>
-        <v/>
-      </c>
-      <c r="C31" s="56">
-        <f>C29+C30</f>
-        <v>1791.423</v>
-        <v/>
-      </c>
-    </row>
-    <row r="32">
-      <c r="B32" s="18" t="inlineStr">
-        <is>
-          <t>(-) Caixa e equivalentes + TVM</t>
-        </is>
-      </c>
-      <c r="C32" s="54" t="n">
-        <v>438.377</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="B33" s="36">
-        <f> Dívida líquida</f>
-        <v/>
-      </c>
-      <c r="C33" s="59">
-        <f>C31-C32</f>
-        <v>1353.046</v>
-        <v/>
-      </c>
-      <c r="D33" s="38" t="inlineStr">
-        <is>
-          <t>ND/EBITDA = 2,8x ✓ (covenant)</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="22" customHeight="1">
-      <c r="B35" s="27" t="inlineStr">
-        <is>
-          <t>5. Valor de mercado por comparáveis (âncora)</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="B36" s="16" t="inlineStr">
-        <is>
-          <t>Comparável listada (B3)</t>
-        </is>
-      </c>
-      <c r="C36" s="17" t="inlineStr">
-        <is>
-          <t>EV/EBITDA</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="B37" s="18" t="inlineStr">
-        <is>
-          <t>Hypera (HYPE3)</t>
-        </is>
-      </c>
-      <c r="C37" s="60" t="n">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="B38" s="18" t="inlineStr">
-        <is>
-          <t>Blau (BLAU3)</t>
-        </is>
-      </c>
-      <c r="C38" s="60" t="n">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="B39" s="18" t="inlineStr">
-        <is>
-          <t>Prêmio crescimento (consumer health/Carmed)</t>
-        </is>
-      </c>
-      <c r="C39" s="60" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="B40" s="33" t="inlineStr">
-        <is>
-          <t>EV/EBITDA selecionado</t>
-        </is>
-      </c>
-      <c r="C40" s="61" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="B41" s="24">
-        <f> Enterprise Value (sobre EBITDA 2026E)</f>
-        <v/>
-      </c>
-      <c r="C41" s="58">
-        <f>C40*Projecoes!C9</f>
-        <v>4124.993652</v>
-        <v/>
-      </c>
-    </row>
-    <row r="42">
-      <c r="B42" s="18" t="inlineStr">
-        <is>
-          <t>(-) Dívida líquida</t>
-        </is>
-      </c>
-      <c r="C42" s="54">
-        <f>-C33</f>
-        <v>-1353.046</v>
-        <v/>
-      </c>
-    </row>
-    <row r="43">
-      <c r="B43" s="24">
-        <f> Equity Value (comparáveis)</f>
-        <v/>
-      </c>
-      <c r="C43" s="58">
-        <f>C41+C42</f>
-        <v>2771.947652</v>
-        <v/>
-      </c>
-    </row>
+      <c r="B24" s="12" t="inlineStr">
+        <is>
+          <t>Notas: WACC em termos nominais (BRL), coerente com projeções nominais. Rf reflete a NTN-B longa; o juro real brasileiro está historicamente alto (NTN-B real ~9,5% em 2026), por isso usa-se nível normalizado de longo prazo. ERP da FGV/Ceqef (8,19%) entra como teto na sensibilidade. βu de ~0,63 reflete o caráter defensivo de saúde/consumo. Resultado: WACC ≈ 14,4%, dentro do intervalo de mercado para mid-caps brasileiras (13–16%).</t>
+        </is>
+      </c>
+    </row>
+    <row r="25"/>
+    <row r="26"/>
+    <row r="27"/>
   </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="B10:D10"/>
-    <mergeCell ref="B28:D28"/>
-    <mergeCell ref="B35:D35"/>
-    <mergeCell ref="B16:D16"/>
+  <mergeCells count="6">
+    <mergeCell ref="B24:D27"/>
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="B13:D13"/>
+    <mergeCell ref="B21:D21"/>
     <mergeCell ref="B2:D2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1953,6 +1621,663 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B2:D32"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="42" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="2" ht="26" customHeight="1">
+      <c r="B2" s="27" t="inlineStr">
+        <is>
+          <t>Premissas, Dados-base e Avaliação por Múltiplos</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1">
+      <c r="B4" s="28" t="inlineStr">
+        <is>
+          <t>1. Dados-base 2025A (consolidado, R$ milhões)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="18" t="inlineStr">
+        <is>
+          <t>Receita líquida 2025</t>
+        </is>
+      </c>
+      <c r="C5" s="19" t="n">
+        <v>3067.594</v>
+      </c>
+      <c r="D5" s="25" t="inlineStr">
+        <is>
+          <t>DF Cimed &amp; Co 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="18" t="inlineStr">
+        <is>
+          <t>EBIT 2025</t>
+        </is>
+      </c>
+      <c r="C6" s="19" t="n">
+        <v>358.827</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="18" t="inlineStr">
+        <is>
+          <t>Depreciação &amp; amortização 2025</t>
+        </is>
+      </c>
+      <c r="C7" s="19" t="n">
+        <v>121.334</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>EBITDA 2025</t>
+        </is>
+      </c>
+      <c r="C8" s="22" t="n">
+        <v>480.161</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  margem EBITDA 2025</t>
+        </is>
+      </c>
+      <c r="C9" s="26" t="n">
+        <v>0.1565269067549356</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="18" t="inlineStr">
+        <is>
+          <t>Lucro líquido 2025</t>
+        </is>
+      </c>
+      <c r="C10" s="19" t="n">
+        <v>196.709</v>
+      </c>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="B12" s="28" t="inlineStr">
+        <is>
+          <t>2. Premissas gerais</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="29" t="inlineStr">
+        <is>
+          <t>Depreciação &amp; amortização (% receita)</t>
+        </is>
+      </c>
+      <c r="C13" s="30" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="D13" s="25" t="inlineStr">
+        <is>
+          <t>~3,96% em 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="29" t="inlineStr">
+        <is>
+          <t>Alíquota efetiva de impostos</t>
+        </is>
+      </c>
+      <c r="C14" s="30" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="D14" s="25" t="inlineStr">
+        <is>
+          <t>normalizada; 2024/25 tiveram benefício fiscal</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="29" t="inlineStr">
+        <is>
+          <t>Crescimento na perpetuidade (g)</t>
+        </is>
+      </c>
+      <c r="C15" s="30" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D15" s="25" t="inlineStr">
+        <is>
+          <t>~inflação LP (4-4,5%) + real</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="22" customHeight="1">
+      <c r="B17" s="28" t="inlineStr">
+        <is>
+          <t>3. Ponte para Equity — dívida líquida 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="18" t="inlineStr">
+        <is>
+          <t>Empréstimos, financiamentos e debêntures</t>
+        </is>
+      </c>
+      <c r="C18" s="19" t="n">
+        <v>1633.539</v>
+      </c>
+      <c r="D18" s="25" t="inlineStr">
+        <is>
+          <t>circ.+não circ.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="18" t="inlineStr">
+        <is>
+          <t>(+) Passivo de arrendamento (leasing)</t>
+        </is>
+      </c>
+      <c r="C19" s="19" t="n">
+        <v>157.884</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="4">
+        <f> Dívida bruta total</f>
+        <v/>
+      </c>
+      <c r="C20" s="22" t="n">
+        <v>1791.423</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="18" t="inlineStr">
+        <is>
+          <t>(-) Caixa e equivalentes + TVM</t>
+        </is>
+      </c>
+      <c r="C21" s="19" t="n">
+        <v>438.377</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="37">
+        <f> Dívida líquida</f>
+        <v/>
+      </c>
+      <c r="C22" s="38" t="n">
+        <v>1353.046</v>
+      </c>
+      <c r="D22" s="25" t="inlineStr">
+        <is>
+          <t>ND/EBITDA = 2,8x ✓ (covenant)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="22" customHeight="1">
+      <c r="B24" s="28" t="inlineStr">
+        <is>
+          <t>4. Avaliação por múltiplos de comparáveis (mercado)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="16" t="inlineStr">
+        <is>
+          <t>Comparável listada (B3)</t>
+        </is>
+      </c>
+      <c r="C25" s="17" t="inlineStr">
+        <is>
+          <t>EV/EBITDA</t>
+        </is>
+      </c>
+      <c r="D25" s="16" t="inlineStr">
+        <is>
+          <t>Referência</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="18" t="inlineStr">
+        <is>
+          <t>Hypera (HYPE3)</t>
+        </is>
+      </c>
+      <c r="C26" s="39" t="n">
+        <v>7.56</v>
+      </c>
+      <c r="D26" s="25" t="inlineStr">
+        <is>
+          <t>mar/26; EV R$22,7bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="18" t="inlineStr">
+        <is>
+          <t>Blau (BLAU3)</t>
+        </is>
+      </c>
+      <c r="C27" s="39" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="D27" s="25" t="inlineStr">
+        <is>
+          <t>caixa líq.; alta margem</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" s="18" t="inlineStr">
+        <is>
+          <t>Prêmio cresc. / (-) desconto IPO &amp; alavancagem</t>
+        </is>
+      </c>
+      <c r="C28" s="39" t="n"/>
+      <c r="D28" s="25" t="inlineStr">
+        <is>
+          <t>líquido ≈ neutro</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="35" t="inlineStr">
+        <is>
+          <t>EV/EBITDA selecionado (forward, 2026E)</t>
+        </is>
+      </c>
+      <c r="C29" s="40" t="n">
+        <v>7</v>
+      </c>
+      <c r="D29" s="25" t="inlineStr">
+        <is>
+          <t>≈ setor; leve desconto vs. Hypera</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="23">
+        <f> Enterprise Value (mercado)</f>
+        <v/>
+      </c>
+      <c r="C30" s="24" t="n">
+        <v>4088.489283200001</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" s="18" t="inlineStr">
+        <is>
+          <t>(-) Dívida líquida</t>
+        </is>
+      </c>
+      <c r="C31" s="19" t="n">
+        <v>-1353.046</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="23">
+        <f> Equity Value (mercado)</f>
+        <v/>
+      </c>
+      <c r="C32" s="24" t="n">
+        <v>2735.4432832</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="B12:D12"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="B2:D2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B2:I22"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="2" ht="26" customHeight="1">
+      <c r="B2" s="27" t="inlineStr">
+        <is>
+          <t>Capital de Giro — Histórico e Projeção (R$ milhões)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" s="16" t="inlineStr">
+        <is>
+          <t>Histórico (real)</t>
+        </is>
+      </c>
+      <c r="C4" s="17" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="D4" s="17" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="18" t="inlineStr">
+        <is>
+          <t>Contas a receber</t>
+        </is>
+      </c>
+      <c r="C5" s="19" t="n">
+        <v>757.47</v>
+      </c>
+      <c r="D5" s="19" t="n">
+        <v>1106.327</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="18" t="inlineStr">
+        <is>
+          <t>(+) Estoques</t>
+        </is>
+      </c>
+      <c r="C6" s="19" t="n">
+        <v>507.999</v>
+      </c>
+      <c r="D6" s="19" t="n">
+        <v>699.5069999999999</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="18" t="inlineStr">
+        <is>
+          <t>(-) Fornecedores</t>
+        </is>
+      </c>
+      <c r="C7" s="19" t="n">
+        <v>-623.978</v>
+      </c>
+      <c r="D7" s="19" t="n">
+        <v>-677.3920000000001</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="20">
+        <f> Capital de giro (líquido)</f>
+        <v/>
+      </c>
+      <c r="C8" s="21" t="n">
+        <v>641.4910000000001</v>
+      </c>
+      <c r="D8" s="21" t="n">
+        <v>1128.442</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  % da receita líquida</t>
+        </is>
+      </c>
+      <c r="C9" s="26" t="n">
+        <v>0.2352466383828886</v>
+      </c>
+      <c r="D9" s="26" t="n">
+        <v>0.3678589800345156</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Prazo médio receb. (DSO)</t>
+        </is>
+      </c>
+      <c r="C10" s="41" t="n">
+        <v>101.3890747948118</v>
+      </c>
+      <c r="D10" s="41" t="n">
+        <v>131.6371576551525</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Prazo médio estoques (DIO)</t>
+        </is>
+      </c>
+      <c r="C11" s="41" t="n">
+        <v>132.1732462346376</v>
+      </c>
+      <c r="D11" s="41" t="n">
+        <v>151.5715812251222</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Prazo médio fornec. (DPO)</t>
+        </is>
+      </c>
+      <c r="C12" s="41" t="n">
+        <v>162.3491342286041</v>
+      </c>
+      <c r="D12" s="41" t="n">
+        <v>146.7796270076611</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Ciclo de conversão de caixa</t>
+        </is>
+      </c>
+      <c r="C13" s="42" t="n">
+        <v>71.21318680084528</v>
+      </c>
+      <c r="D13" s="42" t="n">
+        <v>136.4291118726136</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="16" t="inlineStr">
+        <is>
+          <t>Projeção</t>
+        </is>
+      </c>
+      <c r="C16" s="17" t="inlineStr">
+        <is>
+          <t>2026E</t>
+        </is>
+      </c>
+      <c r="D16" s="17" t="inlineStr">
+        <is>
+          <t>2027E</t>
+        </is>
+      </c>
+      <c r="E16" s="17" t="inlineStr">
+        <is>
+          <t>2028E</t>
+        </is>
+      </c>
+      <c r="F16" s="17" t="inlineStr">
+        <is>
+          <t>2029E</t>
+        </is>
+      </c>
+      <c r="G16" s="17" t="inlineStr">
+        <is>
+          <t>2030E</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="18" t="inlineStr">
+        <is>
+          <t>Receita líquida</t>
+        </is>
+      </c>
+      <c r="C17" s="43">
+        <f>Projecoes!C7</f>
+        <v>3435.70528</v>
+        <v/>
+      </c>
+      <c r="D17" s="43">
+        <f>Projecoes!D7</f>
+        <v>3813.632861</v>
+        <v/>
+      </c>
+      <c r="E17" s="43">
+        <f>Projecoes!E7</f>
+        <v>4194.996147</v>
+        <v/>
+      </c>
+      <c r="F17" s="43">
+        <f>Projecoes!F7</f>
+        <v>4530.595839</v>
+        <v/>
+      </c>
+      <c r="G17" s="43">
+        <f>Projecoes!G7</f>
+        <v>4825.084568</v>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="44" t="inlineStr">
+        <is>
+          <t>Capital de giro (% da receita)</t>
+        </is>
+      </c>
+      <c r="C18" s="30" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="D18" s="30" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="E18" s="30" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="F18" s="30" t="n">
+        <v>0.325</v>
+      </c>
+      <c r="G18" s="30" t="n">
+        <v>0.32</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="20" t="inlineStr">
+        <is>
+          <t>Capital de giro (líquido)</t>
+        </is>
+      </c>
+      <c r="C19" s="5">
+        <f>C17*C18</f>
+        <v>1202.496848</v>
+        <v/>
+      </c>
+      <c r="D19" s="5">
+        <f>D17*D18</f>
+        <v>1296.635173</v>
+        <v/>
+      </c>
+      <c r="E19" s="5">
+        <f>E17*E18</f>
+        <v>1384.348728</v>
+        <v/>
+      </c>
+      <c r="F19" s="5">
+        <f>F17*F18</f>
+        <v>1472.443648</v>
+        <v/>
+      </c>
+      <c r="G19" s="5">
+        <f>G17*G18</f>
+        <v>1544.027062</v>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="23">
+        <f> Variação do capital de giro (ΔWC)</f>
+        <v/>
+      </c>
+      <c r="C20" s="8">
+        <f>C19-D8</f>
+        <v>74.054848</v>
+        <v/>
+      </c>
+      <c r="D20" s="8">
+        <f>D19-C19</f>
+        <v>94.138325</v>
+        <v/>
+      </c>
+      <c r="E20" s="8">
+        <f>E19-D19</f>
+        <v>87.713556</v>
+        <v/>
+      </c>
+      <c r="F20" s="8">
+        <f>F19-E19</f>
+        <v>88.094919</v>
+        <v/>
+      </c>
+      <c r="G20" s="8">
+        <f>G19-F19</f>
+        <v>71.583414</v>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="15" t="inlineStr">
+        <is>
+          <t>Premissa: normalização gradual do ciclo de caixa (36,8% → 32% da receita), revertendo parte do estouro de 2025.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B2:I2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1971,16 +2296,11 @@
   </cols>
   <sheetData>
     <row r="2" ht="26" customHeight="1">
-      <c r="B2" s="41" t="inlineStr">
+      <c r="B2" s="27" t="inlineStr">
         <is>
           <t>Projeção de Fluxo de Caixa Livre Desalavancado (FCFF) — R$ milhões</t>
         </is>
       </c>
-      <c r="C2" s="62" t="n"/>
-      <c r="D2" s="62" t="n"/>
-      <c r="E2" s="62" t="n"/>
-      <c r="F2" s="62" t="n"/>
-      <c r="G2" s="63" t="n"/>
     </row>
     <row r="4">
       <c r="B4" s="16" t="inlineStr">
@@ -2015,25 +2335,25 @@
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="42" t="inlineStr">
+      <c r="B6" s="44" t="inlineStr">
         <is>
           <t>Crescimento da receita (%)</t>
         </is>
       </c>
-      <c r="C6" s="64" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="D6" s="64" t="n">
+      <c r="C6" s="30" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="D6" s="30" t="n">
         <v>0.11</v>
       </c>
-      <c r="E6" s="64" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="F6" s="64" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="G6" s="64" t="n">
-        <v>0.06</v>
+      <c r="E6" s="30" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F6" s="30" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="G6" s="30" t="n">
+        <v>0.065</v>
       </c>
     </row>
     <row r="7">
@@ -2042,52 +2362,52 @@
           <t>Receita líquida</t>
         </is>
       </c>
-      <c r="C7" s="44">
-        <f>Premissas!$C$3*(1+C6)</f>
-        <v>3466.38122</v>
-        <v/>
-      </c>
-      <c r="D7" s="44">
+      <c r="C7" s="45">
+        <f>Premissas!$C$5*(1+C6)</f>
+        <v>3435.70528</v>
+        <v/>
+      </c>
+      <c r="D7" s="45">
         <f>C7*(1+D6)</f>
-        <v>3847.683154</v>
-        <v/>
-      </c>
-      <c r="E7" s="44">
+        <v>3813.632861</v>
+        <v/>
+      </c>
+      <c r="E7" s="45">
         <f>D7*(1+E6)</f>
-        <v>4193.974638</v>
-        <v/>
-      </c>
-      <c r="F7" s="44">
+        <v>4194.996147</v>
+        <v/>
+      </c>
+      <c r="F7" s="45">
         <f>E7*(1+F6)</f>
-        <v>4487.552863</v>
-        <v/>
-      </c>
-      <c r="G7" s="44">
+        <v>4530.595839</v>
+        <v/>
+      </c>
+      <c r="G7" s="45">
         <f>F7*(1+G6)</f>
-        <v>4756.806035</v>
+        <v>4825.084568</v>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="42" t="inlineStr">
+      <c r="B8" s="44" t="inlineStr">
         <is>
           <t>Margem EBITDA (%)</t>
         </is>
       </c>
-      <c r="C8" s="64" t="n">
+      <c r="C8" s="30" t="n">
         <v>0.17</v>
       </c>
-      <c r="D8" s="64" t="n">
+      <c r="D8" s="30" t="n">
         <v>0.185</v>
       </c>
-      <c r="E8" s="64" t="n">
+      <c r="E8" s="30" t="n">
         <v>0.195</v>
       </c>
-      <c r="F8" s="64" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="G8" s="64" t="n">
+      <c r="F8" s="30" t="n">
         <v>0.205</v>
+      </c>
+      <c r="G8" s="30" t="n">
+        <v>0.21</v>
       </c>
     </row>
     <row r="9">
@@ -2098,59 +2418,59 @@
       </c>
       <c r="C9" s="5">
         <f>C7*C8</f>
-        <v>589.284807</v>
+        <v>584.069898</v>
         <v/>
       </c>
       <c r="D9" s="5">
         <f>D7*D8</f>
-        <v>711.821384</v>
+        <v>705.522079</v>
         <v/>
       </c>
       <c r="E9" s="5">
         <f>E7*E8</f>
-        <v>817.825054</v>
+        <v>818.024249</v>
         <v/>
       </c>
       <c r="F9" s="5">
         <f>F7*F8</f>
-        <v>897.510573</v>
+        <v>928.772147</v>
         <v/>
       </c>
       <c r="G9" s="5">
         <f>G7*G8</f>
-        <v>975.145237</v>
+        <v>1013.267759</v>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="42" t="inlineStr">
+      <c r="B10" s="44" t="inlineStr">
         <is>
           <t>(-) Depreciação &amp; amortização</t>
         </is>
       </c>
-      <c r="C10" s="54">
-        <f>-C7*Premissas!$C$11</f>
-        <v>-138.655249</v>
-        <v/>
-      </c>
-      <c r="D10" s="54">
-        <f>-D7*Premissas!$C$11</f>
-        <v>-153.907326</v>
-        <v/>
-      </c>
-      <c r="E10" s="54">
-        <f>-E7*Premissas!$C$11</f>
-        <v>-167.758986</v>
-        <v/>
-      </c>
-      <c r="F10" s="54">
-        <f>-F7*Premissas!$C$11</f>
-        <v>-179.502115</v>
-        <v/>
-      </c>
-      <c r="G10" s="54">
-        <f>-G7*Premissas!$C$11</f>
-        <v>-190.272241</v>
+      <c r="C10" s="19">
+        <f>-C7*Premissas!$C$13</f>
+        <v>-137.428211</v>
+        <v/>
+      </c>
+      <c r="D10" s="19">
+        <f>-D7*Premissas!$C$13</f>
+        <v>-152.545314</v>
+        <v/>
+      </c>
+      <c r="E10" s="19">
+        <f>-E7*Premissas!$C$13</f>
+        <v>-167.799846</v>
+        <v/>
+      </c>
+      <c r="F10" s="19">
+        <f>-F7*Premissas!$C$13</f>
+        <v>-181.223834</v>
+        <v/>
+      </c>
+      <c r="G10" s="19">
+        <f>-G7*Premissas!$C$13</f>
+        <v>-193.003383</v>
         <v/>
       </c>
     </row>
@@ -2159,61 +2479,61 @@
         <f> EBIT</f>
         <v/>
       </c>
-      <c r="C11" s="56">
+      <c r="C11" s="22">
         <f>C9+C10</f>
-        <v>450.629559</v>
-        <v/>
-      </c>
-      <c r="D11" s="56">
+        <v>446.641686</v>
+        <v/>
+      </c>
+      <c r="D11" s="22">
         <f>D9+D10</f>
-        <v>557.914057</v>
-        <v/>
-      </c>
-      <c r="E11" s="56">
+        <v>552.976765</v>
+        <v/>
+      </c>
+      <c r="E11" s="22">
         <f>E9+E10</f>
-        <v>650.066069</v>
-        <v/>
-      </c>
-      <c r="F11" s="56">
+        <v>650.224403</v>
+        <v/>
+      </c>
+      <c r="F11" s="22">
         <f>F9+F10</f>
-        <v>718.008458</v>
-        <v/>
-      </c>
-      <c r="G11" s="56">
+        <v>747.548313</v>
+        <v/>
+      </c>
+      <c r="G11" s="22">
         <f>G9+G10</f>
-        <v>784.872996</v>
+        <v>820.264377</v>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="42" t="inlineStr">
+      <c r="B12" s="44" t="inlineStr">
         <is>
           <t>(-) Impostos sobre EBIT</t>
         </is>
       </c>
-      <c r="C12" s="54">
-        <f>-C11*Premissas!$C$13</f>
-        <v>-112.65739</v>
-        <v/>
-      </c>
-      <c r="D12" s="54">
-        <f>-D11*Premissas!$C$13</f>
-        <v>-139.478514</v>
-        <v/>
-      </c>
-      <c r="E12" s="54">
-        <f>-E11*Premissas!$C$13</f>
-        <v>-162.516517</v>
-        <v/>
-      </c>
-      <c r="F12" s="54">
-        <f>-F11*Premissas!$C$13</f>
-        <v>-179.502115</v>
-        <v/>
-      </c>
-      <c r="G12" s="54">
-        <f>-G11*Premissas!$C$13</f>
-        <v>-196.218249</v>
+      <c r="C12" s="19">
+        <f>-C11*Premissas!$C$14</f>
+        <v>-111.660422</v>
+        <v/>
+      </c>
+      <c r="D12" s="19">
+        <f>-D11*Premissas!$C$14</f>
+        <v>-138.244191</v>
+        <v/>
+      </c>
+      <c r="E12" s="19">
+        <f>-E11*Premissas!$C$14</f>
+        <v>-162.556101</v>
+        <v/>
+      </c>
+      <c r="F12" s="19">
+        <f>-F11*Premissas!$C$14</f>
+        <v>-186.887078</v>
+        <v/>
+      </c>
+      <c r="G12" s="19">
+        <f>-G11*Premissas!$C$14</f>
+        <v>-205.066094</v>
         <v/>
       </c>
     </row>
@@ -2222,178 +2542,178 @@
         <f> NOPAT</f>
         <v/>
       </c>
-      <c r="C13" s="56">
+      <c r="C13" s="22">
         <f>C11+C12</f>
-        <v>337.972169</v>
-        <v/>
-      </c>
-      <c r="D13" s="56">
+        <v>334.981265</v>
+        <v/>
+      </c>
+      <c r="D13" s="22">
         <f>D11+D12</f>
-        <v>418.435543</v>
-        <v/>
-      </c>
-      <c r="E13" s="56">
+        <v>414.732574</v>
+        <v/>
+      </c>
+      <c r="E13" s="22">
         <f>E11+E12</f>
-        <v>487.549552</v>
-        <v/>
-      </c>
-      <c r="F13" s="56">
+        <v>487.668302</v>
+        <v/>
+      </c>
+      <c r="F13" s="22">
         <f>F11+F12</f>
-        <v>538.506344</v>
-        <v/>
-      </c>
-      <c r="G13" s="56">
+        <v>560.661235</v>
+        <v/>
+      </c>
+      <c r="G13" s="22">
         <f>G11+G12</f>
-        <v>588.654747</v>
+        <v>615.198282</v>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="42" t="inlineStr">
+      <c r="B14" s="44" t="inlineStr">
         <is>
           <t>(+) Depreciação &amp; amortização</t>
         </is>
       </c>
-      <c r="C14" s="54">
+      <c r="C14" s="19">
         <f>-C10</f>
-        <v>138.655249</v>
-        <v/>
-      </c>
-      <c r="D14" s="54">
+        <v>137.428211</v>
+        <v/>
+      </c>
+      <c r="D14" s="19">
         <f>-D10</f>
-        <v>153.907326</v>
-        <v/>
-      </c>
-      <c r="E14" s="54">
+        <v>152.545314</v>
+        <v/>
+      </c>
+      <c r="E14" s="19">
         <f>-E10</f>
-        <v>167.758986</v>
-        <v/>
-      </c>
-      <c r="F14" s="54">
+        <v>167.799846</v>
+        <v/>
+      </c>
+      <c r="F14" s="19">
         <f>-F10</f>
-        <v>179.502115</v>
-        <v/>
-      </c>
-      <c r="G14" s="54">
+        <v>181.223834</v>
+        <v/>
+      </c>
+      <c r="G14" s="19">
         <f>-G10</f>
-        <v>190.272241</v>
+        <v>193.003383</v>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="42" t="inlineStr">
+      <c r="B15" s="44" t="inlineStr">
         <is>
           <t>Capex (% receita)</t>
         </is>
       </c>
-      <c r="C15" s="64" t="n">
+      <c r="C15" s="30" t="n">
         <v>0.06</v>
       </c>
-      <c r="D15" s="64" t="n">
+      <c r="D15" s="30" t="n">
         <v>0.055</v>
       </c>
-      <c r="E15" s="64" t="n">
+      <c r="E15" s="30" t="n">
         <v>0.05</v>
       </c>
-      <c r="F15" s="64" t="n">
+      <c r="F15" s="30" t="n">
+        <v>0.047</v>
+      </c>
+      <c r="G15" s="30" t="n">
         <v>0.045</v>
       </c>
-      <c r="G15" s="64" t="n">
-        <v>0.04</v>
-      </c>
     </row>
     <row r="16">
-      <c r="B16" s="42" t="inlineStr">
+      <c r="B16" s="44" t="inlineStr">
         <is>
           <t>(-) Capex</t>
         </is>
       </c>
-      <c r="C16" s="54">
+      <c r="C16" s="19">
         <f>-C7*C15</f>
-        <v>-207.982873</v>
-        <v/>
-      </c>
-      <c r="D16" s="54">
+        <v>-206.142317</v>
+        <v/>
+      </c>
+      <c r="D16" s="19">
         <f>-D7*D15</f>
-        <v>-211.622573</v>
-        <v/>
-      </c>
-      <c r="E16" s="54">
+        <v>-209.749807</v>
+        <v/>
+      </c>
+      <c r="E16" s="19">
         <f>-E7*E15</f>
-        <v>-209.698732</v>
-        <v/>
-      </c>
-      <c r="F16" s="54">
+        <v>-209.749807</v>
+        <v/>
+      </c>
+      <c r="F16" s="19">
         <f>-F7*F15</f>
-        <v>-201.939879</v>
-        <v/>
-      </c>
-      <c r="G16" s="54">
+        <v>-212.938004</v>
+        <v/>
+      </c>
+      <c r="G16" s="19">
         <f>-G7*G15</f>
-        <v>-190.272241</v>
+        <v>-217.128806</v>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="B17" s="42" t="inlineStr">
+      <c r="B17" s="44" t="inlineStr">
         <is>
           <t>(-) Variação de capital de giro</t>
         </is>
       </c>
-      <c r="C17" s="54">
-        <f>-(C7-Premissas!$C$3)*Premissas!$C$12</f>
-        <v>-59.818083</v>
-        <v/>
-      </c>
-      <c r="D17" s="54">
-        <f>-(D7-C7)*Premissas!$C$12</f>
-        <v>-57.19529</v>
-        <v/>
-      </c>
-      <c r="E17" s="54">
-        <f>-(E7-D7)*Premissas!$C$12</f>
-        <v>-51.943723</v>
-        <v/>
-      </c>
-      <c r="F17" s="54">
-        <f>-(F7-E7)*Premissas!$C$12</f>
-        <v>-44.036734</v>
-        <v/>
-      </c>
-      <c r="G17" s="54">
-        <f>-(G7-F7)*Premissas!$C$12</f>
-        <v>-40.387976</v>
+      <c r="C17" s="19">
+        <f>-Capital_de_Giro!C20</f>
+        <v>-74.054848</v>
+        <v/>
+      </c>
+      <c r="D17" s="19">
+        <f>-Capital_de_Giro!D20</f>
+        <v>-94.138325</v>
+        <v/>
+      </c>
+      <c r="E17" s="19">
+        <f>-Capital_de_Giro!E20</f>
+        <v>-87.713556</v>
+        <v/>
+      </c>
+      <c r="F17" s="19">
+        <f>-Capital_de_Giro!F20</f>
+        <v>-88.094919</v>
+        <v/>
+      </c>
+      <c r="G17" s="19">
+        <f>-Capital_de_Giro!G20</f>
+        <v>-71.583414</v>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="24">
+      <c r="B18" s="23">
         <f> Fluxo de Caixa Livre (FCFF)</f>
         <v/>
       </c>
-      <c r="C18" s="7">
+      <c r="C18" s="8">
         <f>C13+C14+C16+C17</f>
-        <v>208.826462</v>
-        <v/>
-      </c>
-      <c r="D18" s="7">
+        <v>192.212311</v>
+        <v/>
+      </c>
+      <c r="D18" s="8">
         <f>D13+D14+D16+D17</f>
-        <v>303.525006</v>
-        <v/>
-      </c>
-      <c r="E18" s="7">
+        <v>263.389756</v>
+        <v/>
+      </c>
+      <c r="E18" s="8">
         <f>E13+E14+E16+E17</f>
-        <v>393.666083</v>
-        <v/>
-      </c>
-      <c r="F18" s="7">
+        <v>358.004785</v>
+        <v/>
+      </c>
+      <c r="F18" s="8">
         <f>F13+F14+F16+F17</f>
-        <v>472.031846</v>
-        <v/>
-      </c>
-      <c r="G18" s="7">
+        <v>440.852145</v>
+        <v/>
+      </c>
+      <c r="G18" s="8">
         <f>G13+G14+G16+G17</f>
-        <v>548.266771</v>
+        <v>519.489445</v>
         <v/>
       </c>
     </row>
@@ -2405,7 +2725,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2415,7 +2735,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
-    <col width="42" customWidth="1" min="2" max="2"/>
+    <col width="44" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
@@ -2424,9 +2744,9 @@
   </cols>
   <sheetData>
     <row r="2" ht="26" customHeight="1">
-      <c r="B2" s="45" t="inlineStr">
-        <is>
-          <t>Desconto a Valor Presente e Conclusão — R$ milhões</t>
+      <c r="B2" s="27" t="inlineStr">
+        <is>
+          <t>Fluxo de Caixa Descontado — Conclusão (R$ milhões)</t>
         </is>
       </c>
     </row>
@@ -2463,7 +2783,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="42" t="inlineStr">
+      <c r="B5" s="44" t="inlineStr">
         <is>
           <t>Período de desconto (t)</t>
         </is>
@@ -2485,98 +2805,98 @@
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="42" t="inlineStr">
+      <c r="B6" s="44" t="inlineStr">
         <is>
           <t>FCFF</t>
         </is>
       </c>
       <c r="C6" s="47">
         <f>Projecoes!C18</f>
-        <v>208.826462</v>
+        <v>192.212311</v>
         <v/>
       </c>
       <c r="D6" s="47">
         <f>Projecoes!D18</f>
-        <v>303.525006</v>
+        <v>263.389756</v>
         <v/>
       </c>
       <c r="E6" s="47">
         <f>Projecoes!E18</f>
-        <v>393.666083</v>
+        <v>358.004785</v>
         <v/>
       </c>
       <c r="F6" s="47">
         <f>Projecoes!F18</f>
-        <v>472.031846</v>
+        <v>440.852145</v>
         <v/>
       </c>
       <c r="G6" s="47">
         <f>Projecoes!G18</f>
-        <v>548.266771</v>
+        <v>519.489445</v>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="42" t="inlineStr">
+      <c r="B7" s="44" t="inlineStr">
         <is>
           <t>Fator de desconto @ WACC</t>
         </is>
       </c>
-      <c r="C7" s="65">
-        <f>1/(1+Premissas!$C$26)^C5</f>
-        <v>0.870414</v>
-        <v/>
-      </c>
-      <c r="D7" s="65">
-        <f>1/(1+Premissas!$C$26)^D5</f>
-        <v>0.757621</v>
-        <v/>
-      </c>
-      <c r="E7" s="65">
-        <f>1/(1+Premissas!$C$26)^E5</f>
-        <v>0.659445</v>
-        <v/>
-      </c>
-      <c r="F7" s="65">
-        <f>1/(1+Premissas!$C$26)^F5</f>
-        <v>0.57399</v>
-        <v/>
-      </c>
-      <c r="G7" s="65">
-        <f>1/(1+Premissas!$C$26)^G5</f>
-        <v>0.499609</v>
+      <c r="C7" s="48">
+        <f>1/(1+WACC!$C$22)^C5</f>
+        <v>0.874063</v>
+        <v/>
+      </c>
+      <c r="D7" s="48">
+        <f>1/(1+WACC!$C$22)^D5</f>
+        <v>0.763987</v>
+        <v/>
+      </c>
+      <c r="E7" s="48">
+        <f>1/(1+WACC!$C$22)^E5</f>
+        <v>0.667773</v>
+        <v/>
+      </c>
+      <c r="F7" s="48">
+        <f>1/(1+WACC!$C$22)^F5</f>
+        <v>0.583676</v>
+        <v/>
+      </c>
+      <c r="G7" s="48">
+        <f>1/(1+WACC!$C$22)^G5</f>
+        <v>0.51017</v>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="24" t="inlineStr">
+      <c r="B8" s="23" t="inlineStr">
         <is>
           <t>FCFF a valor presente</t>
         </is>
       </c>
-      <c r="C8" s="58">
+      <c r="C8" s="24">
         <f>C6*C7</f>
-        <v>181.765567</v>
-        <v/>
-      </c>
-      <c r="D8" s="58">
+        <v>168.005762</v>
+        <v/>
+      </c>
+      <c r="D8" s="24">
         <f>D6*D7</f>
-        <v>229.957008</v>
-        <v/>
-      </c>
-      <c r="E8" s="58">
+        <v>201.226341</v>
+        <v/>
+      </c>
+      <c r="E8" s="24">
         <f>E6*E7</f>
-        <v>259.600939</v>
-        <v/>
-      </c>
-      <c r="F8" s="58">
+        <v>239.065968</v>
+        <v/>
+      </c>
+      <c r="F8" s="24">
         <f>F6*F7</f>
-        <v>270.941572</v>
-        <v/>
-      </c>
-      <c r="G8" s="58">
+        <v>257.314855</v>
+        <v/>
+      </c>
+      <c r="G8" s="24">
         <f>G6*G7</f>
-        <v>273.919127</v>
+        <v>265.027905</v>
         <v/>
       </c>
     </row>
@@ -2586,9 +2906,9 @@
           <t>Soma do VP dos FCFF (2026–2030)</t>
         </is>
       </c>
-      <c r="C11" s="56">
+      <c r="C11" s="22">
         <f>SUM(C8:G8)</f>
-        <v>1216.184214</v>
+        <v>1130.640831</v>
         <v/>
       </c>
     </row>
@@ -2598,9 +2918,9 @@
           <t>FCFF normalizado (terminal × (1+g))</t>
         </is>
       </c>
-      <c r="C13" s="54">
-        <f>G6*(1+Premissas!C14)</f>
-        <v>575.68011</v>
+      <c r="C13" s="19">
+        <f>G6*(1+Premissas!C15)</f>
+        <v>545.463918</v>
         <v/>
       </c>
     </row>
@@ -2611,8 +2931,8 @@
         </is>
       </c>
       <c r="C14" s="49">
-        <f>C13/(Premissas!C26-Premissas!C14)</f>
-        <v>5822.125342</v>
+        <f>C13/(WACC!C22-Premissas!C15)</f>
+        <v>5797.770804</v>
         <v/>
       </c>
     </row>
@@ -2622,21 +2942,21 @@
           <t>Fator de desconto do ano terminal</t>
         </is>
       </c>
-      <c r="C15" s="65">
+      <c r="C15" s="48">
         <f>G7</f>
-        <v>0.499609</v>
+        <v>0.51017</v>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="24" t="inlineStr">
+      <c r="B16" s="23" t="inlineStr">
         <is>
           <t>Valor Terminal a valor presente</t>
         </is>
       </c>
-      <c r="C16" s="58">
+      <c r="C16" s="24">
         <f>C14*C15</f>
-        <v>2908.787432</v>
+        <v>2957.848452</v>
         <v/>
       </c>
     </row>
@@ -2646,9 +2966,9 @@
           <t>VP dos fluxos explícitos</t>
         </is>
       </c>
-      <c r="C18" s="54">
+      <c r="C18" s="19">
         <f>C11</f>
-        <v>1216.184214</v>
+        <v>1130.640831</v>
         <v/>
       </c>
     </row>
@@ -2660,7 +2980,7 @@
       </c>
       <c r="C19" s="5">
         <f>C18+C16</f>
-        <v>4124.971646</v>
+        <v>4088.489283</v>
         <v/>
       </c>
     </row>
@@ -2670,9 +2990,9 @@
           <t>% do EV no Valor Terminal</t>
         </is>
       </c>
-      <c r="C20" s="57">
+      <c r="C20" s="26">
         <f>C16/C19</f>
-        <v>0.705165</v>
+        <v>0.723458</v>
         <v/>
       </c>
     </row>
@@ -2682,21 +3002,21 @@
           <t>(-) Dívida líquida (2025)</t>
         </is>
       </c>
-      <c r="C22" s="54">
-        <f>-Premissas!C33</f>
+      <c r="C22" s="19">
+        <f>-Premissas!C22</f>
         <v>-1353.046</v>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="B23" s="24" t="inlineStr">
+      <c r="B23" s="23" t="inlineStr">
         <is>
           <t>EQUITY VALUE (DCF)</t>
         </is>
       </c>
-      <c r="C23" s="7">
+      <c r="C23" s="8">
         <f>C19+C22</f>
-        <v>2771.925646</v>
+        <v>2735.443283</v>
         <v/>
       </c>
     </row>

--- a/CIMED_Valuation_DCF.xlsx
+++ b/CIMED_Valuation_DCF.xlsx
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E21" s="25" t="inlineStr">
         <is>
-          <t>benefício (SUDENE/subvenção)</t>
+          <t>benefício: créd. presumido ICMS R$74mi + JCP R$23mi</t>
         </is>
       </c>
     </row>
@@ -1477,7 +1477,7 @@
       </c>
       <c r="D8" s="25" t="inlineStr">
         <is>
-          <t>normalizada (incentivos SUDENE)</t>
+          <t>normalizada; ef. ~0% via crédito presumido ICMS + JCP</t>
         </is>
       </c>
     </row>
@@ -1747,7 +1747,7 @@
       </c>
       <c r="D14" s="25" t="inlineStr">
         <is>
-          <t>normalizada; 2024/25 tiveram benefício fiscal</t>
+          <t>ef. negativa em 2025; sobe c/ fim do ICMS (reforma tributária)</t>
         </is>
       </c>
     </row>

--- a/CIMED_Valuation_DCF.xlsx
+++ b/CIMED_Valuation_DCF.xlsx
@@ -10,10 +10,11 @@
     <sheet name="Resumo" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Historico" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="WACC" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Premissas" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Capital_de_Giro" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Projecoes" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="DCF" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Impostos" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Premissas" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Capital_de_Giro" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Projecoes" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="DCF" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -57,12 +58,12 @@
     </font>
     <font>
       <name val="Calibri"/>
+      <b val="1"/>
       <color rgb="00000000"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="Calibri"/>
-      <b val="1"/>
       <color rgb="00000000"/>
       <sz val="11"/>
     </font>
@@ -114,12 +115,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F2F2F2"/>
+        <fgColor rgb="00D6E0F0"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D6E0F0"/>
+        <fgColor rgb="00F2F2F2"/>
       </patternFill>
     </fill>
     <fill>
@@ -164,7 +165,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -175,142 +176,157 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="10" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="168" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="3" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
@@ -678,36 +694,36 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:F23"/>
+  <dimension ref="B2:F24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
     <col width="46" customWidth="1" min="2" max="2"/>
     <col width="17" customWidth="1" min="3" max="3"/>
     <col width="3" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
     <col width="3" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="2" ht="30" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>CIMED &amp; CO S.A. — Valuation para IPO (DCF + Múltiplos)</t>
+          <t>CIMED &amp; CO S.A. — Valuation para IPO (DCF intrínseco + Múltiplos)</t>
         </is>
       </c>
     </row>
     <row r="3" ht="16" customHeight="1">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Empresa de capital fechado em preparação para IPO. Valor de mercado por comparáveis (B3) reconciliado com DCF. Base: DFs auditadas 2025.</t>
+          <t>Cenário SEM reforma tributária | imposto com prejuízo fiscal | WACC variável no tempo | capital de giro por dias de giro.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>CONCLUSÃO DO VALUATION (R$ milhões)</t>
+          <t>CONCLUSÃO (R$ milhões)</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
@@ -724,24 +740,24 @@
       </c>
       <c r="C6" s="5">
         <f>DCF!C19</f>
-        <v>4088.489283</v>
+        <v>4809.012968</v>
         <v/>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>WACC</t>
+          <t>WACC 2026 → perpetuidade</t>
         </is>
       </c>
       <c r="F6" s="6">
         <f>WACC!C22</f>
-        <v>0.144082</v>
+        <v>0.15361</v>
         <v/>
       </c>
     </row>
     <row r="7">
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>(-) Dívida líquida (2025)</t>
+          <t>(-) Dívida líquida</t>
         </is>
       </c>
       <c r="C7" s="5">
@@ -751,12 +767,12 @@
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>Crescimento perpétuo (g)</t>
-        </is>
-      </c>
-      <c r="F7" s="7">
-        <f>Premissas!C15</f>
-        <v>0.05</v>
+          <t>WACC na perpetuidade</t>
+        </is>
+      </c>
+      <c r="F7" s="6">
+        <f>WACC!H22</f>
+        <v>0.149603</v>
         <v/>
       </c>
     </row>
@@ -765,146 +781,138 @@
         <f> Equity Value (DCF)</f>
         <v/>
       </c>
-      <c r="C8" s="8">
+      <c r="C8" s="7">
         <f>DCF!C23</f>
-        <v>2735.443283</v>
+        <v>3455.966968</v>
         <v/>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>EV/EBITDA (mercado)</t>
-        </is>
-      </c>
-      <c r="F8" s="9">
-        <f>Premissas!C29</f>
-        <v>7.0</v>
+          <t>Alíquota efetiva 2026 → perp.</t>
+        </is>
+      </c>
+      <c r="F8" s="8">
+        <f>Impostos!C19</f>
+        <v>0.107578</v>
         <v/>
       </c>
     </row>
     <row r="9">
       <c r="E9" s="4" t="inlineStr">
         <is>
+          <t>Prejuízo fiscal inicial (R$ mi)</t>
+        </is>
+      </c>
+      <c r="F9" s="5">
+        <f>Impostos!C8</f>
+        <v>754.976471</v>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>Equity Value (múltiplos 7,0x) — cross-check</t>
+        </is>
+      </c>
+      <c r="C10" s="9">
+        <f>Premissas!C31</f>
+        <v>2735.443283</v>
+        <v/>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>Crescimento perpétuo (g)</t>
+        </is>
+      </c>
+      <c r="F10" s="8">
+        <f>Premissas!C14</f>
+        <v>0.05</v>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>Faixa de valor (múltiplos ↔ DCF)</t>
+        </is>
+      </c>
+      <c r="C11" s="10" t="inlineStr">
+        <is>
+          <t>R$ 2,7 – R$ 3,5 bi</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>EV/EBITDA 2026E implícito (DCF)</t>
+        </is>
+      </c>
+      <c r="F11" s="11">
+        <f>DCF!C19/Projecoes!C9</f>
+        <v>8.233626</v>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="E12" s="4" t="inlineStr">
+        <is>
           <t>EBITDA 2025A</t>
         </is>
       </c>
-      <c r="F9" s="5">
+      <c r="F12" s="5">
         <f>Premissas!C8</f>
         <v>480.161</v>
         <v/>
       </c>
     </row>
-    <row r="10">
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>Enterprise Value (múltiplos 7,0x)</t>
-        </is>
-      </c>
-      <c r="C10" s="5">
-        <f>Premissas!C30</f>
-        <v>4088.489283</v>
-        <v/>
-      </c>
-      <c r="E10" s="4" t="inlineStr">
-        <is>
-          <t>Margem EBITDA 2025 → 2030E</t>
-        </is>
-      </c>
-      <c r="F10" s="7">
-        <f>Premissas!C9</f>
-        <v>0.156527</v>
-        <v/>
-      </c>
-    </row>
-    <row r="11">
-      <c r="B11" s="4">
-        <f> Equity Value (múltiplos)</f>
-        <v/>
-      </c>
-      <c r="C11" s="8">
-        <f>Premissas!C32</f>
-        <v>2735.443283</v>
-        <v/>
-      </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>Dívida líquida / EBITDA</t>
-        </is>
-      </c>
-      <c r="F11" s="9">
-        <f>Premissas!C22/Premissas!C8</f>
-        <v>2.817901</v>
-        <v/>
-      </c>
-    </row>
-    <row r="12">
-      <c r="E12" s="4" t="inlineStr">
-        <is>
-          <t>Receita líquida 2025A</t>
-        </is>
-      </c>
-      <c r="F12" s="5">
-        <f>Premissas!C5</f>
-        <v>3067.594</v>
-        <v/>
-      </c>
-    </row>
     <row r="13">
-      <c r="B13" s="10" t="inlineStr">
-        <is>
-          <t>Δ DCF − Mercado (deve ≈ 0)</t>
-        </is>
-      </c>
-      <c r="C13" s="11">
-        <f>DCF!C19-Premissas!C30</f>
-        <v>0.0</v>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>EQUITY VALUE (DCF, R$ bi)</t>
+        </is>
+      </c>
+      <c r="C13" s="12">
+        <f>DCF!C23/1000</f>
+        <v>3.455967</v>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="E14" s="12" t="inlineStr">
-        <is>
-          <t>Metodologia (IPO): valor de mercado estimado por múltiplo EV/EBITDA de comparáveis listadas (Hypera 7,56x; CIMED a 7,0x forward) e reconciliado com DCF. O WACC (14,4%) é construído bottom-up (aba WACC) com dados de mercado brasileiros (Rf NTN-B, ERP FGV) e equivale à taxa que iguala o DCF ao valor de mercado. Projeções alinhadas ao setor: crescimento ~12%→6,5% (mercado farma BR ~10-12%), margem EBITDA recuperando de 15,7% para 21% (média histórica), capex e capital de giro normalizando após o pico de 2025. Células amarelas = inputs editáveis.</t>
+      <c r="E14" s="13" t="inlineStr">
+        <is>
+          <t>O DCF intrínseco (~R$3,5bi) supera o valor por múltiplos (~R$2,7bi) porque o múltiplo simples não captura o ativo fiscal: prejuízo fiscal de R$755mi + crédito presumido de ICMS mantêm o imposto caixa baixo por vários anos (cenário SEM reforma). O EV/EBITDA implícito do DCF (~8,2x) fica acima da Hypera (7,56x) — o prêmio é o valor do escudo fiscal. A taxa de desconto varia no tempo (aba WACC). Faixa razoável de IPO: R$2,7–3,5bi conforme a durabilidade dos benefícios fiscais. Células amarelas = inputs.</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>EQUITY VALUE (R$ bilhões)</t>
-        </is>
-      </c>
-      <c r="C15" s="13">
-        <f>DCF!C23/1000</f>
-        <v>2.735443</v>
-        <v/>
-      </c>
-    </row>
-    <row r="16"/>
-    <row r="17">
-      <c r="B17" s="12" t="inlineStr">
+      <c r="B15" s="13" t="inlineStr">
         <is>
           <t>Abas:
-• Historico — DFs auditadas 2024/25
-• WACC — cálculo do custo de capital
+• Historico — DFs auditadas 2024/25 (+ DTA prej. fiscal)
+• WACC — custo de capital variável no tempo
+• Impostos — IR com prejuízo fiscal (trava 30%)
 • Premissas — drivers + múltiplos
-• Capital_de_Giro — ciclo de caixa e ΔWC
+• Capital_de_Giro — dias de giro (DSO/DIO/DPO)
 • Projecoes — DRE → FCFF
 • DCF — desconto e conclusão</t>
         </is>
       </c>
     </row>
+    <row r="16"/>
+    <row r="17"/>
     <row r="18"/>
     <row r="19"/>
     <row r="20"/>
     <row r="21"/>
     <row r="22"/>
     <row r="23"/>
+    <row r="24"/>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="B2:F2"/>
-    <mergeCell ref="E14:F23"/>
+    <mergeCell ref="E14:F24"/>
     <mergeCell ref="B3:F3"/>
-    <mergeCell ref="B17:C23"/>
+    <mergeCell ref="B15:C24"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -916,7 +924,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:E38"/>
+  <dimension ref="B2:E30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -929,14 +937,14 @@
     <row r="2">
       <c r="B2" s="14" t="inlineStr">
         <is>
-          <t>CIMED &amp; CO S.A. — Demonstrações Financeiras Consolidadas (auditadas KPMG, 17/03/2026)</t>
+          <t>CIMED &amp; CO S.A. — Demonstrações Financeiras Consolidadas (KPMG, 17/03/2026)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="B3" s="15" t="inlineStr">
         <is>
-          <t>R$ milhões. Fonte: DFs Cimed &amp; Co S.A. de 31/12/2025 e 2024 (documento do RI).</t>
+          <t>R$ milhões. Fonte: DFs Cimed &amp; Co S.A. de 31/12/2025 e 2024 (RI).</t>
         </is>
       </c>
     </row>
@@ -960,427 +968,319 @@
     <row r="6">
       <c r="B6" s="18" t="inlineStr">
         <is>
-          <t>Receita bruta de venda</t>
+          <t>Receita líquida de venda</t>
         </is>
       </c>
       <c r="C6" s="19" t="n">
-        <v>3935.529</v>
+        <v>3067.594</v>
       </c>
       <c r="D6" s="19" t="n">
-        <v>3494.34</v>
+        <v>2726.887</v>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="18" t="inlineStr">
-        <is>
-          <t>(-) Deduções</t>
-        </is>
-      </c>
-      <c r="C7" s="19" t="n">
-        <v>-867.9349999999999</v>
-      </c>
-      <c r="D7" s="19" t="n">
-        <v>-767.453</v>
+      <c r="B7" s="20" t="inlineStr">
+        <is>
+          <t>(-) Custo das mercadorias vendidas</t>
+        </is>
+      </c>
+      <c r="C7" s="21" t="n">
+        <v>-1684.485</v>
+      </c>
+      <c r="D7" s="21" t="n">
+        <v>-1402.853</v>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="20" t="inlineStr">
-        <is>
-          <t>Receita líquida de venda</t>
-        </is>
-      </c>
-      <c r="C8" s="21" t="n">
-        <v>3067.594</v>
-      </c>
-      <c r="D8" s="21" t="n">
-        <v>2726.887</v>
+      <c r="B8" s="22">
+        <f> Lucro bruto</f>
+        <v/>
+      </c>
+      <c r="C8" s="23" t="n">
+        <v>1383.109</v>
+      </c>
+      <c r="D8" s="23" t="n">
+        <v>1324.034</v>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="18" t="inlineStr">
-        <is>
-          <t>(-) Custo das mercadorias vendidas</t>
-        </is>
-      </c>
-      <c r="C9" s="19" t="n">
-        <v>-1684.485</v>
-      </c>
-      <c r="D9" s="19" t="n">
-        <v>-1402.853</v>
+      <c r="B9" s="20" t="inlineStr">
+        <is>
+          <t>(-) Despesas comerciais</t>
+        </is>
+      </c>
+      <c r="C9" s="21" t="n">
+        <v>-621.016</v>
+      </c>
+      <c r="D9" s="21" t="n">
+        <v>-539.982</v>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="10">
-        <f> Lucro bruto</f>
-        <v/>
-      </c>
-      <c r="C10" s="22" t="n">
-        <v>1383.109</v>
-      </c>
-      <c r="D10" s="22" t="n">
-        <v>1324.034</v>
+      <c r="B10" s="20" t="inlineStr">
+        <is>
+          <t>(-) Despesas administrativas</t>
+        </is>
+      </c>
+      <c r="C10" s="21" t="n">
+        <v>-396.865</v>
+      </c>
+      <c r="D10" s="21" t="n">
+        <v>-318.157</v>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="18" t="inlineStr">
-        <is>
-          <t>(-) Despesas comerciais</t>
-        </is>
-      </c>
-      <c r="C11" s="19" t="n">
-        <v>-621.016</v>
-      </c>
-      <c r="D11" s="19" t="n">
-        <v>-539.982</v>
+      <c r="B11" s="20" t="inlineStr">
+        <is>
+          <t>(-) Perdas de crédito esperadas</t>
+        </is>
+      </c>
+      <c r="C11" s="21" t="n">
+        <v>-18.226</v>
+      </c>
+      <c r="D11" s="21" t="n">
+        <v>-9.775</v>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="18" t="inlineStr">
-        <is>
-          <t>(-) Despesas administrativas</t>
-        </is>
-      </c>
-      <c r="C12" s="19" t="n">
-        <v>-396.865</v>
-      </c>
-      <c r="D12" s="19" t="n">
-        <v>-318.157</v>
+      <c r="B12" s="20" t="inlineStr">
+        <is>
+          <t>(+) Outras receitas (despesas) op.</t>
+        </is>
+      </c>
+      <c r="C12" s="21" t="n">
+        <v>11.825</v>
+      </c>
+      <c r="D12" s="21" t="n">
+        <v>5.022</v>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="18" t="inlineStr">
-        <is>
-          <t>(-) Perdas de crédito esperadas</t>
-        </is>
-      </c>
-      <c r="C13" s="19" t="n">
-        <v>-18.226</v>
-      </c>
-      <c r="D13" s="19" t="n">
-        <v>-9.775</v>
+      <c r="B13" s="24">
+        <f> EBIT</f>
+        <v/>
+      </c>
+      <c r="C13" s="25" t="n">
+        <v>358.827</v>
+      </c>
+      <c r="D13" s="25" t="n">
+        <v>461.142</v>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="18" t="inlineStr">
-        <is>
-          <t>(+) Outras receitas (despesas) operacionais</t>
-        </is>
-      </c>
-      <c r="C14" s="19" t="n">
-        <v>11.825</v>
-      </c>
-      <c r="D14" s="19" t="n">
-        <v>5.022</v>
+      <c r="B14" s="20" t="inlineStr">
+        <is>
+          <t>(+) Depreciação &amp; amortização</t>
+        </is>
+      </c>
+      <c r="C14" s="21" t="n">
+        <v>121.334</v>
+      </c>
+      <c r="D14" s="21" t="n">
+        <v>113.842</v>
+      </c>
+      <c r="E14" s="26" t="inlineStr">
+        <is>
+          <t>CMV 37,5 + Opex 83,9</t>
+        </is>
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="23">
-        <f> EBIT</f>
-        <v/>
-      </c>
-      <c r="C15" s="24" t="n">
-        <v>358.827</v>
-      </c>
-      <c r="D15" s="24" t="n">
-        <v>461.142</v>
+      <c r="B15" s="24">
+        <f> EBITDA</f>
+        <v/>
+      </c>
+      <c r="C15" s="25" t="n">
+        <v>480.161</v>
+      </c>
+      <c r="D15" s="25" t="n">
+        <v>574.984</v>
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="18" t="inlineStr">
-        <is>
-          <t>(+) Depreciação &amp; amortização</t>
-        </is>
-      </c>
-      <c r="C16" s="19" t="n">
-        <v>121.334</v>
-      </c>
-      <c r="D16" s="19" t="n">
-        <v>113.842</v>
-      </c>
-      <c r="E16" s="25" t="inlineStr">
-        <is>
-          <t>CMV 37,5 + Opex 83,9 (2025)</t>
-        </is>
+      <c r="B16" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  margem EBITDA</t>
+        </is>
+      </c>
+      <c r="C16" s="27" t="n">
+        <v>0.1565269067549356</v>
+      </c>
+      <c r="D16" s="27" t="n">
+        <v>0.2108572889158957</v>
       </c>
     </row>
     <row r="17">
-      <c r="B17" s="23">
-        <f> EBITDA</f>
-        <v/>
-      </c>
-      <c r="C17" s="24" t="n">
-        <v>480.161</v>
-      </c>
-      <c r="D17" s="24" t="n">
-        <v>574.984</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  margem EBITDA</t>
-        </is>
-      </c>
-      <c r="C18" s="26" t="n">
-        <v>0.1565269067549356</v>
-      </c>
-      <c r="D18" s="26" t="n">
-        <v>0.2108572889158957</v>
-      </c>
-      <c r="E18" s="25" t="inlineStr">
-        <is>
-          <t>15,7% (trough) vs. 21,1%</t>
-        </is>
+      <c r="B17" s="18">
+        <f> Lucro líquido</f>
+        <v/>
+      </c>
+      <c r="C17" s="19" t="n">
+        <v>196.709</v>
+      </c>
+      <c r="D17" s="19" t="n">
+        <v>280.949</v>
       </c>
     </row>
     <row r="19">
-      <c r="B19" s="18" t="inlineStr">
-        <is>
-          <t>(+/-) Resultado financeiro</t>
-        </is>
-      </c>
-      <c r="C19" s="19" t="n">
-        <v>-204.438</v>
-      </c>
-      <c r="D19" s="19" t="n">
-        <v>-190.028</v>
+      <c r="B19" s="16" t="inlineStr">
+        <is>
+          <t>BALANÇO (resumo)</t>
+        </is>
+      </c>
+      <c r="C19" s="17" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D19" s="17" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
       </c>
     </row>
     <row r="20">
-      <c r="B20" s="18">
-        <f> Lucro antes dos tributos</f>
-        <v/>
-      </c>
-      <c r="C20" s="19" t="n">
-        <v>154.389</v>
-      </c>
-      <c r="D20" s="19" t="n">
-        <v>271.114</v>
+      <c r="B20" s="20" t="inlineStr">
+        <is>
+          <t>Caixa + TVM</t>
+        </is>
+      </c>
+      <c r="C20" s="21" t="n">
+        <v>438.377</v>
+      </c>
+      <c r="D20" s="21" t="n">
+        <v>701.389</v>
       </c>
     </row>
     <row r="21">
-      <c r="B21" s="18" t="inlineStr">
-        <is>
-          <t>(+/-) Tributos sobre o lucro</t>
-        </is>
-      </c>
-      <c r="C21" s="19" t="n">
-        <v>42.32</v>
-      </c>
-      <c r="D21" s="19" t="n">
-        <v>9.835000000000001</v>
-      </c>
-      <c r="E21" s="25" t="inlineStr">
-        <is>
-          <t>benefício: créd. presumido ICMS R$74mi + JCP R$23mi</t>
-        </is>
+      <c r="B21" s="20" t="inlineStr">
+        <is>
+          <t>Contas a receber</t>
+        </is>
+      </c>
+      <c r="C21" s="21" t="n">
+        <v>1106.327</v>
+      </c>
+      <c r="D21" s="21" t="n">
+        <v>757.47</v>
       </c>
     </row>
     <row r="22">
-      <c r="B22" s="20">
-        <f> Lucro líquido</f>
-        <v/>
+      <c r="B22" s="20" t="inlineStr">
+        <is>
+          <t>Estoques</t>
+        </is>
       </c>
       <c r="C22" s="21" t="n">
-        <v>196.709</v>
+        <v>699.5069999999999</v>
       </c>
       <c r="D22" s="21" t="n">
-        <v>280.949</v>
+        <v>507.999</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="20" t="inlineStr">
+        <is>
+          <t>Fornecedores</t>
+        </is>
+      </c>
+      <c r="C23" s="21" t="n">
+        <v>677.3920000000001</v>
+      </c>
+      <c r="D23" s="21" t="n">
+        <v>623.978</v>
       </c>
     </row>
     <row r="24">
-      <c r="B24" s="16" t="inlineStr">
-        <is>
-          <t>BALANÇO PATRIMONIAL (resumo)</t>
-        </is>
-      </c>
-      <c r="C24" s="17" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="D24" s="17" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
+      <c r="B24" s="20" t="inlineStr">
+        <is>
+          <t>Empréstimos, financ. e debêntures</t>
+        </is>
+      </c>
+      <c r="C24" s="21" t="n">
+        <v>1633.539</v>
+      </c>
+      <c r="D24" s="21" t="n">
+        <v>1402.87</v>
       </c>
     </row>
     <row r="25">
-      <c r="B25" s="18" t="inlineStr">
-        <is>
-          <t>Caixa e equivalentes + TVM</t>
-        </is>
-      </c>
-      <c r="C25" s="19" t="n">
-        <v>438.377</v>
-      </c>
-      <c r="D25" s="19" t="n">
-        <v>701.389</v>
+      <c r="B25" s="20" t="inlineStr">
+        <is>
+          <t>Passivo de arrendamento</t>
+        </is>
+      </c>
+      <c r="C25" s="21" t="n">
+        <v>157.884</v>
+      </c>
+      <c r="D25" s="21" t="n">
+        <v>68.85899999999999</v>
       </c>
     </row>
     <row r="26">
       <c r="B26" s="18" t="inlineStr">
         <is>
-          <t>Contas a receber</t>
+          <t>Patrimônio líquido</t>
         </is>
       </c>
       <c r="C26" s="19" t="n">
-        <v>1106.327</v>
+        <v>1228.271</v>
       </c>
       <c r="D26" s="19" t="n">
-        <v>757.47</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="B27" s="18" t="inlineStr">
-        <is>
-          <t>Estoques</t>
-        </is>
-      </c>
-      <c r="C27" s="19" t="n">
-        <v>699.5069999999999</v>
-      </c>
-      <c r="D27" s="19" t="n">
-        <v>507.999</v>
+        <v>777.744</v>
       </c>
     </row>
     <row r="28">
-      <c r="B28" s="18" t="inlineStr">
-        <is>
-          <t>Imobilizado + Direito de uso + Intangível</t>
-        </is>
-      </c>
-      <c r="C28" s="19" t="n">
-        <v>1370.004</v>
-      </c>
-      <c r="D28" s="19" t="n">
-        <v>1059.08</v>
+      <c r="B28" s="16" t="inlineStr">
+        <is>
+          <t>ATIVO FISCAL DIFERIDO — prejuízo fiscal</t>
+        </is>
+      </c>
+      <c r="C28" s="17" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D28" s="17" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
       </c>
     </row>
     <row r="29">
-      <c r="B29" s="10" t="inlineStr">
-        <is>
-          <t>Total do ativo</t>
-        </is>
-      </c>
-      <c r="C29" s="22" t="n">
-        <v>4217.164</v>
-      </c>
-      <c r="D29" s="22" t="n">
-        <v>3453.464</v>
+      <c r="B29" s="20" t="inlineStr">
+        <is>
+          <t>DTA s/ prejuízos fiscais + base neg. CSLL</t>
+        </is>
+      </c>
+      <c r="C29" s="21" t="n">
+        <v>256.692</v>
+      </c>
+      <c r="D29" s="21" t="n">
+        <v>228.8</v>
+      </c>
+      <c r="E29" s="26" t="inlineStr">
+        <is>
+          <t>cresce: ainda gera prej. fiscal</t>
+        </is>
       </c>
     </row>
     <row r="30">
-      <c r="B30" s="18" t="inlineStr">
-        <is>
-          <t>Fornecedores</t>
-        </is>
-      </c>
-      <c r="C30" s="19" t="n">
-        <v>677.3920000000001</v>
-      </c>
-      <c r="D30" s="19" t="n">
-        <v>623.978</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="B31" s="18" t="inlineStr">
-        <is>
-          <t>Empréstimos, financiamentos e debêntures</t>
-        </is>
-      </c>
-      <c r="C31" s="19" t="n">
-        <v>1633.539</v>
-      </c>
-      <c r="D31" s="19" t="n">
-        <v>1402.87</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="B32" s="18" t="inlineStr">
-        <is>
-          <t>Passivo de arrendamento (leasing)</t>
-        </is>
-      </c>
-      <c r="C32" s="19" t="n">
-        <v>157.884</v>
-      </c>
-      <c r="D32" s="19" t="n">
-        <v>68.85899999999999</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="B33" s="20" t="inlineStr">
-        <is>
-          <t>Patrimônio líquido total</t>
-        </is>
-      </c>
-      <c r="C33" s="21" t="n">
-        <v>1228.271</v>
-      </c>
-      <c r="D33" s="21" t="n">
-        <v>777.744</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="B35" s="16" t="inlineStr">
-        <is>
-          <t>FLUXO DE CAIXA (resumo)</t>
-        </is>
-      </c>
-      <c r="C35" s="17" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="D35" s="17" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="B36" s="18" t="inlineStr">
-        <is>
-          <t>Caixa das atividades operacionais (FCO)</t>
-        </is>
-      </c>
-      <c r="C36" s="19" t="n">
-        <v>-55.532</v>
-      </c>
-      <c r="D36" s="19" t="n">
-        <v>365.567</v>
-      </c>
-      <c r="E36" s="25" t="inlineStr">
-        <is>
-          <t>2025 negativo</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="B37" s="18" t="inlineStr">
-        <is>
-          <t>Capex (imobilizado + intangível)</t>
-        </is>
-      </c>
-      <c r="C37" s="19" t="n">
-        <v>-206.214</v>
-      </c>
-      <c r="D37" s="19" t="n">
-        <v>-229.586</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="B38" s="18" t="inlineStr">
-        <is>
-          <t>Dividendos e JCP pagos</t>
-        </is>
-      </c>
-      <c r="C38" s="19" t="n">
-        <v>-427.199</v>
-      </c>
-      <c r="D38" s="19" t="n">
-        <v>-190.355</v>
+      <c r="B30" s="22" t="inlineStr">
+        <is>
+          <t>Estoque de prejuízo fiscal implícito (÷34%)</t>
+        </is>
+      </c>
+      <c r="C30" s="23" t="n">
+        <v>754.9764705882353</v>
+      </c>
+      <c r="D30" s="23" t="n">
+        <v>672.9411764705882</v>
+      </c>
+      <c r="E30" s="26" t="inlineStr">
+        <is>
+          <t>usado na aba Impostos</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -1398,209 +1298,332 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:D27"/>
+  <dimension ref="B2:I27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
-    <col width="42" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="30" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="2" ht="26" customHeight="1">
-      <c r="B2" s="27" t="inlineStr">
-        <is>
-          <t>Cálculo do WACC (custo médio ponderado de capital)</t>
+      <c r="B2" s="28" t="inlineStr">
+        <is>
+          <t>WACC — Custo de Capital com Alíquota e Taxa de Desconto Variáveis no Tempo</t>
         </is>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
-      <c r="B4" s="28" t="inlineStr">
-        <is>
-          <t>1. Custo do capital próprio (Ke) — CAPM local (BRL nominal)</t>
+      <c r="B4" s="29" t="inlineStr">
+        <is>
+          <t>1. Estrutura de capital alvo (a mercado)</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="29" t="inlineStr">
+      <c r="B5" s="30" t="inlineStr">
+        <is>
+          <t>Capital próprio / Valor (E/V)</t>
+        </is>
+      </c>
+      <c r="C5" s="31" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="I5" s="26" t="inlineStr">
+        <is>
+          <t>≈ pós-IPO</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="30" t="inlineStr">
+        <is>
+          <t>Dívida / Valor (D/V)</t>
+        </is>
+      </c>
+      <c r="C6" s="31" t="n">
+        <v>0.33</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="20" t="inlineStr">
+        <is>
+          <t>D/E (=D÷E)</t>
+        </is>
+      </c>
+      <c r="C7" s="32" t="n">
+        <v>0.4925373134328358</v>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="B8" s="29" t="inlineStr">
+        <is>
+          <t>2. Custo do capital próprio (Ke) — CAPM local (BRL nominal)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="30" t="inlineStr">
         <is>
           <t>Taxa livre de risco (Rf)</t>
         </is>
       </c>
-      <c r="C5" s="30" t="n">
+      <c r="C9" s="31" t="n">
         <v>0.105</v>
       </c>
-      <c r="D5" s="25" t="inlineStr">
-        <is>
-          <t>NTN-B 10a nominal (real ~9,5% + inflação)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="B6" s="29" t="inlineStr">
+      <c r="I9" s="26" t="inlineStr">
+        <is>
+          <t>NTN-B 10a nominal</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="30" t="inlineStr">
         <is>
           <t>Prêmio de risco de mercado (ERP)</t>
         </is>
       </c>
-      <c r="C6" s="30" t="n">
+      <c r="C10" s="31" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="D6" s="25" t="inlineStr">
-        <is>
-          <t>FGV/Ceqef: 8,19% (fev/26) — usado como teto</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="B7" s="29" t="inlineStr">
+      <c r="I10" s="26" t="inlineStr">
+        <is>
+          <t>FGV/Ceqef 8,19% = teto</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="30" t="inlineStr">
         <is>
           <t>Beta desalavancado (βu)</t>
         </is>
       </c>
-      <c r="C7" s="31" t="n">
-        <v>0.6277798796202757</v>
-      </c>
-      <c r="D7" s="25" t="inlineStr">
-        <is>
-          <t>farma/consumo defensivo (Damodaran EM ajust.)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="B8" s="29" t="inlineStr">
-        <is>
-          <t>Alíquota de impostos (t)</t>
-        </is>
-      </c>
-      <c r="C8" s="30" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="D8" s="25" t="inlineStr">
-        <is>
-          <t>normalizada; ef. ~0% via crédito presumido ICMS + JCP</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="B9" s="18" t="inlineStr">
-        <is>
-          <t>Estrutura-alvo D/E</t>
-        </is>
-      </c>
-      <c r="C9" s="32" t="n">
-        <v>0.4925373134328358</v>
-      </c>
-      <c r="D9" s="25" t="inlineStr">
-        <is>
-          <t>da estrutura de capital abaixo</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>Beta realavancado (βL = βu·(1+(1-t)·D/E))</t>
-        </is>
-      </c>
-      <c r="C10" s="33" t="n">
-        <v>0.8596836411217954</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="B11" s="20" t="inlineStr">
-        <is>
-          <t>Custo do capital próprio (Ke = Rf + βL·ERP)</t>
-        </is>
-      </c>
-      <c r="C11" s="6" t="n">
-        <v>0.1651778548785257</v>
-      </c>
-    </row>
-    <row r="13" ht="22" customHeight="1">
-      <c r="B13" s="28" t="inlineStr">
-        <is>
-          <t>2. Custo da dívida (Kd)</t>
-        </is>
+      <c r="C11" s="33" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="I11" s="26" t="inlineStr">
+        <is>
+          <t>farma/consumo defensivo</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="30" t="inlineStr">
+        <is>
+          <t>Alíquota p/ realavancagem (estatutária)</t>
+        </is>
+      </c>
+      <c r="C12" s="31" t="n">
+        <v>0.34</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>Beta realavancado (βL=βu·(1+(1-t)·D/E))</t>
+        </is>
+      </c>
+      <c r="C13" s="34" t="n">
+        <v>0.9275522388059702</v>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="29" t="inlineStr">
-        <is>
-          <t>Custo da dívida pré-impostos (Kd)</t>
-        </is>
-      </c>
-      <c r="C14" s="30" t="n">
+      <c r="B14" s="18" t="inlineStr">
+        <is>
+          <t>Custo do capital próprio (Ke=Rf+βL·ERP)</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>0.1699286567164179</v>
+      </c>
+    </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="B15" s="29" t="inlineStr">
+        <is>
+          <t>3. Custo da dívida (Kd)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="30" t="inlineStr">
+        <is>
+          <t>Kd pré-impostos</t>
+        </is>
+      </c>
+      <c r="C16" s="31" t="n">
         <v>0.135</v>
       </c>
-      <c r="D14" s="25" t="inlineStr">
-        <is>
-          <t>CDI + spread debêntures CIMED</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>Custo da dívida após impostos (Kd·(1-t))</t>
-        </is>
-      </c>
-      <c r="C15" s="34" t="n">
-        <v>0.10125</v>
-      </c>
-    </row>
-    <row r="17" ht="22" customHeight="1">
-      <c r="B17" s="28" t="inlineStr">
-        <is>
-          <t>3. Estrutura de capital (alvo, a valor de mercado)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
+      <c r="I16" s="26" t="inlineStr">
+        <is>
+          <t>CDI + spread debêntures</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="22" customHeight="1">
       <c r="B18" s="29" t="inlineStr">
         <is>
-          <t>Capital próprio / Valor (E/V)</t>
-        </is>
-      </c>
-      <c r="C18" s="30" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="D18" s="25" t="inlineStr">
-        <is>
-          <t>≈ pós-IPO (desalavancagem)</t>
+          <t>4. WACC por ano (varia com a alíquota efetiva)</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="B19" s="29" t="inlineStr">
-        <is>
-          <t>Dívida / Valor (D/V)</t>
-        </is>
-      </c>
-      <c r="C19" s="30" t="n">
-        <v>0.33</v>
-      </c>
-    </row>
-    <row r="21" ht="22" customHeight="1">
-      <c r="B21" s="28" t="inlineStr">
-        <is>
-          <t>4. WACC</t>
-        </is>
+      <c r="B19" s="16" t="inlineStr">
+        <is>
+          <t>Ano</t>
+        </is>
+      </c>
+      <c r="C19" s="17" t="inlineStr">
+        <is>
+          <t>2026E</t>
+        </is>
+      </c>
+      <c r="D19" s="17" t="inlineStr">
+        <is>
+          <t>2027E</t>
+        </is>
+      </c>
+      <c r="E19" s="17" t="inlineStr">
+        <is>
+          <t>2028E</t>
+        </is>
+      </c>
+      <c r="F19" s="17" t="inlineStr">
+        <is>
+          <t>2029E</t>
+        </is>
+      </c>
+      <c r="G19" s="17" t="inlineStr">
+        <is>
+          <t>2030E</t>
+        </is>
+      </c>
+      <c r="H19" s="35" t="inlineStr">
+        <is>
+          <t>Perpet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="20" t="inlineStr">
+        <is>
+          <t>Alíquota efetiva de imposto (t)</t>
+        </is>
+      </c>
+      <c r="C20" s="36">
+        <f>Impostos!C19</f>
+        <v>0.107578</v>
+        <v/>
+      </c>
+      <c r="D20" s="36">
+        <f>Impostos!D19</f>
+        <v>0.12107</v>
+        <v/>
+      </c>
+      <c r="E20" s="36">
+        <f>Impostos!E19</f>
+        <v>0.128614</v>
+        <v/>
+      </c>
+      <c r="F20" s="36">
+        <f>Impostos!F19</f>
+        <v>0.135243</v>
+        <v/>
+      </c>
+      <c r="G20" s="36">
+        <f>Impostos!G19</f>
+        <v>0.138265</v>
+        <v/>
+      </c>
+      <c r="H20" s="36">
+        <f>Impostos!H19</f>
+        <v>0.197522</v>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="37" t="inlineStr">
+        <is>
+          <t>Kd após impostos = Kd·(1−t)</t>
+        </is>
+      </c>
+      <c r="C21" s="38">
+        <f>$C$16*(1-C20)</f>
+        <v>0.120477</v>
+        <v/>
+      </c>
+      <c r="D21" s="38">
+        <f>$C$16*(1-D20)</f>
+        <v>0.118656</v>
+        <v/>
+      </c>
+      <c r="E21" s="38">
+        <f>$C$16*(1-E20)</f>
+        <v>0.117637</v>
+        <v/>
+      </c>
+      <c r="F21" s="38">
+        <f>$C$16*(1-F20)</f>
+        <v>0.116742</v>
+        <v/>
+      </c>
+      <c r="G21" s="38">
+        <f>$C$16*(1-G20)</f>
+        <v>0.116334</v>
+        <v/>
+      </c>
+      <c r="H21" s="38">
+        <f>$C$16*(1-H20)</f>
+        <v>0.108335</v>
+        <v/>
       </c>
     </row>
     <row r="22">
-      <c r="B22" s="35" t="inlineStr">
-        <is>
-          <t>WACC = Ke·(E/V) + Kd·(1-t)·(D/V)</t>
-        </is>
-      </c>
-      <c r="C22" s="36" t="n">
-        <v>0.1440816627686122</v>
+      <c r="B22" s="39" t="inlineStr">
+        <is>
+          <t>WACC = Ke·(E/V) + Kd·(1−t)·(D/V)</t>
+        </is>
+      </c>
+      <c r="C22" s="40">
+        <f>$C$14*$C$5+C21*$C$6</f>
+        <v>0.15361</v>
+        <v/>
+      </c>
+      <c r="D22" s="40">
+        <f>$C$14*$C$5+D21*$C$6</f>
+        <v>0.153009</v>
+        <v/>
+      </c>
+      <c r="E22" s="40">
+        <f>$C$14*$C$5+E21*$C$6</f>
+        <v>0.152672</v>
+        <v/>
+      </c>
+      <c r="F22" s="40">
+        <f>$C$14*$C$5+F21*$C$6</f>
+        <v>0.152377</v>
+        <v/>
+      </c>
+      <c r="G22" s="40">
+        <f>$C$14*$C$5+G21*$C$6</f>
+        <v>0.152242</v>
+        <v/>
+      </c>
+      <c r="H22" s="40">
+        <f>$C$14*$C$5+H21*$C$6</f>
+        <v>0.149603</v>
+        <v/>
       </c>
     </row>
     <row r="24">
-      <c r="B24" s="12" t="inlineStr">
-        <is>
-          <t>Notas: WACC em termos nominais (BRL), coerente com projeções nominais. Rf reflete a NTN-B longa; o juro real brasileiro está historicamente alto (NTN-B real ~9,5% em 2026), por isso usa-se nível normalizado de longo prazo. ERP da FGV/Ceqef (8,19%) entra como teto na sensibilidade. βu de ~0,63 reflete o caráter defensivo de saúde/consumo. Resultado: WACC ≈ 14,4%, dentro do intervalo de mercado para mid-caps brasileiras (13–16%).</t>
+      <c r="B24" s="13" t="inlineStr">
+        <is>
+          <t>A taxa de desconto NÃO é constante: nos primeiros anos a alíquota efetiva é baixa (prejuízo fiscal + crédito presumido de ICMS), o que reduz o benefício fiscal da dívida e ELEVA o WACC; conforme o prejuízo fiscal é consumido e a alíquota normaliza, o benefício fiscal cresce e o WACC CAI. Ke mantido constante (estrutura de capital alvo estável). Cenário SEM reforma tributária: o crédito presumido de ICMS persiste indefinidamente.</t>
         </is>
       </c>
     </row>
@@ -1609,12 +1632,12 @@
     <row r="27"/>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="B24:D27"/>
+    <mergeCell ref="B18:H18"/>
+    <mergeCell ref="B8:D8"/>
     <mergeCell ref="B4:D4"/>
-    <mergeCell ref="B17:D17"/>
-    <mergeCell ref="B13:D13"/>
-    <mergeCell ref="B21:D21"/>
-    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="B2:H2"/>
+    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="B24:H27"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1626,61 +1649,508 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:D32"/>
+  <dimension ref="B2:I23"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="42" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="26" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="2" ht="26" customHeight="1">
+      <c r="B2" s="28" t="inlineStr">
+        <is>
+          <t>Imposto de Renda com Prejuízo Fiscal (cenário SEM reforma tributária)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1">
+      <c r="B4" s="29" t="inlineStr">
+        <is>
+          <t>Parâmetros (do RI e legislação)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="30" t="inlineStr">
+        <is>
+          <t>Alíquota IRPJ (25%) + CSLL (9%)</t>
+        </is>
+      </c>
+      <c r="C5" s="31" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="I5" s="26" t="inlineStr">
+        <is>
+          <t>nota 10 das DFs</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="30" t="inlineStr">
+        <is>
+          <t>Limite de compensação por ano (trava)</t>
+        </is>
+      </c>
+      <c r="C6" s="31" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="I6" s="26" t="inlineStr">
+        <is>
+          <t>30% do lucro tributável</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="30" t="inlineStr">
+        <is>
+          <t>Subvenção crédito presumido ICMS (% receita)</t>
+        </is>
+      </c>
+      <c r="C7" s="41" t="n">
+        <v>0.07123900781562895</v>
+      </c>
+      <c r="I7" s="26" t="inlineStr">
+        <is>
+          <t>R$74,3mi÷34%÷receita 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="39" t="inlineStr">
+        <is>
+          <t>Estoque de prejuízo fiscal inicial (2025)</t>
+        </is>
+      </c>
+      <c r="C8" s="42" t="n">
+        <v>754.9764705882353</v>
+      </c>
+      <c r="I8" s="26" t="inlineStr">
+        <is>
+          <t>DTA R$256,7mi ÷ 34%</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="B10" s="29" t="inlineStr">
+        <is>
+          <t>Cálculo do imposto e da alíquota efetiva</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="16" t="inlineStr">
+        <is>
+          <t>Ano</t>
+        </is>
+      </c>
+      <c r="C11" s="17" t="inlineStr">
+        <is>
+          <t>2026E</t>
+        </is>
+      </c>
+      <c r="D11" s="17" t="inlineStr">
+        <is>
+          <t>2027E</t>
+        </is>
+      </c>
+      <c r="E11" s="17" t="inlineStr">
+        <is>
+          <t>2028E</t>
+        </is>
+      </c>
+      <c r="F11" s="17" t="inlineStr">
+        <is>
+          <t>2029E</t>
+        </is>
+      </c>
+      <c r="G11" s="17" t="inlineStr">
+        <is>
+          <t>2030E</t>
+        </is>
+      </c>
+      <c r="H11" s="35" t="inlineStr">
+        <is>
+          <t>Perpet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="37" t="inlineStr">
+        <is>
+          <t>EBIT (lucro operacional)</t>
+        </is>
+      </c>
+      <c r="C12" s="43">
+        <f>Projecoes!C11</f>
+        <v>446.641686</v>
+        <v/>
+      </c>
+      <c r="D12" s="43">
+        <f>Projecoes!D11</f>
+        <v>552.976765</v>
+        <v/>
+      </c>
+      <c r="E12" s="43">
+        <f>Projecoes!E11</f>
+        <v>650.224403</v>
+        <v/>
+      </c>
+      <c r="F12" s="43">
+        <f>Projecoes!F11</f>
+        <v>747.548313</v>
+        <v/>
+      </c>
+      <c r="G12" s="43">
+        <f>Projecoes!G11</f>
+        <v>820.264377</v>
+        <v/>
+      </c>
+      <c r="H12" s="43">
+        <f>Projecoes!G11*(1+Premissas!C15)</f>
+        <v>861.277595</v>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="37" t="inlineStr">
+        <is>
+          <t>(-) Subvenção (crédito presumido ICMS)</t>
+        </is>
+      </c>
+      <c r="C13" s="21">
+        <f>-$C$7*Projecoes!C7</f>
+        <v>-244.756235</v>
+        <v/>
+      </c>
+      <c r="D13" s="21">
+        <f>-$C$7*Projecoes!D7</f>
+        <v>-271.679421</v>
+        <v/>
+      </c>
+      <c r="E13" s="21">
+        <f>-$C$7*Projecoes!E7</f>
+        <v>-298.847363</v>
+        <v/>
+      </c>
+      <c r="F13" s="21">
+        <f>-$C$7*Projecoes!F7</f>
+        <v>-322.755152</v>
+        <v/>
+      </c>
+      <c r="G13" s="21">
+        <f>-$C$7*Projecoes!G7</f>
+        <v>-343.734237</v>
+        <v/>
+      </c>
+      <c r="H13" s="21">
+        <f>-$C$7*Projecoes!G7*(1+Premissas!C15)</f>
+        <v>-360.920949</v>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="22">
+        <f> Lucro tributável antes da compensação</f>
+        <v/>
+      </c>
+      <c r="C14" s="23">
+        <f>MAX(C12+C13,0)</f>
+        <v>201.885451</v>
+        <v/>
+      </c>
+      <c r="D14" s="23">
+        <f>MAX(D12+D13,0)</f>
+        <v>281.297344</v>
+        <v/>
+      </c>
+      <c r="E14" s="23">
+        <f>MAX(E12+E13,0)</f>
+        <v>351.377039</v>
+        <v/>
+      </c>
+      <c r="F14" s="23">
+        <f>MAX(F12+F13,0)</f>
+        <v>424.793161</v>
+        <v/>
+      </c>
+      <c r="G14" s="23">
+        <f>MAX(G12+G13,0)</f>
+        <v>476.530139</v>
+        <v/>
+      </c>
+      <c r="H14" s="23">
+        <f>MAX(H12+H13,0)</f>
+        <v>500.356646</v>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="37" t="inlineStr">
+        <is>
+          <t>Saldo de prejuízo fiscal (início do ano)</t>
+        </is>
+      </c>
+      <c r="C15" s="21">
+        <f>C8</f>
+        <v>754.976471</v>
+        <v/>
+      </c>
+      <c r="D15" s="21">
+        <f>C17</f>
+        <v>694.410835</v>
+        <v/>
+      </c>
+      <c r="E15" s="21">
+        <f>D17</f>
+        <v>610.021632</v>
+        <v/>
+      </c>
+      <c r="F15" s="21">
+        <f>E17</f>
+        <v>504.60852</v>
+        <v/>
+      </c>
+      <c r="G15" s="21">
+        <f>F17</f>
+        <v>377.170572</v>
+        <v/>
+      </c>
+      <c r="H15" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="37" t="inlineStr">
+        <is>
+          <t>(-) Compensação de prejuízo (≤30%)</t>
+        </is>
+      </c>
+      <c r="C16" s="21">
+        <f>-MIN($C$6*C14,C15)</f>
+        <v>-60.565635</v>
+        <v/>
+      </c>
+      <c r="D16" s="21">
+        <f>-MIN($C$6*D14,D15)</f>
+        <v>-84.389203</v>
+        <v/>
+      </c>
+      <c r="E16" s="21">
+        <f>-MIN($C$6*E14,E15)</f>
+        <v>-105.413112</v>
+        <v/>
+      </c>
+      <c r="F16" s="21">
+        <f>-MIN($C$6*F14,F15)</f>
+        <v>-127.437948</v>
+        <v/>
+      </c>
+      <c r="G16" s="21">
+        <f>-MIN($C$6*G14,G15)</f>
+        <v>-142.959042</v>
+        <v/>
+      </c>
+      <c r="H16" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="37" t="inlineStr">
+        <is>
+          <t>Saldo de prejuízo fiscal (fim do ano)</t>
+        </is>
+      </c>
+      <c r="C17" s="21">
+        <f>C15+C16</f>
+        <v>694.410835</v>
+        <v/>
+      </c>
+      <c r="D17" s="21">
+        <f>D15+D16</f>
+        <v>610.021632</v>
+        <v/>
+      </c>
+      <c r="E17" s="21">
+        <f>E15+E16</f>
+        <v>504.60852</v>
+        <v/>
+      </c>
+      <c r="F17" s="21">
+        <f>F15+F16</f>
+        <v>377.170572</v>
+        <v/>
+      </c>
+      <c r="G17" s="21">
+        <f>G15+G16</f>
+        <v>234.21153</v>
+        <v/>
+      </c>
+      <c r="H17" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="44" t="inlineStr">
+        <is>
+          <t>Imposto corrente (34% × base após comp.)</t>
+        </is>
+      </c>
+      <c r="C18" s="45">
+        <f>$C$5*(C14+C16)</f>
+        <v>48.048737</v>
+        <v/>
+      </c>
+      <c r="D18" s="45">
+        <f>$C$5*(D14+D16)</f>
+        <v>66.948768</v>
+        <v/>
+      </c>
+      <c r="E18" s="45">
+        <f>$C$5*(E14+E16)</f>
+        <v>83.627735</v>
+        <v/>
+      </c>
+      <c r="F18" s="45">
+        <f>$C$5*(F14+F16)</f>
+        <v>101.100772</v>
+        <v/>
+      </c>
+      <c r="G18" s="45">
+        <f>$C$5*(G14+G16)</f>
+        <v>113.414173</v>
+        <v/>
+      </c>
+      <c r="H18" s="45">
+        <f>$C$5*H14</f>
+        <v>170.12126</v>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="18" t="inlineStr">
+        <is>
+          <t>Alíquota efetiva (imposto ÷ EBIT)</t>
+        </is>
+      </c>
+      <c r="C19" s="8">
+        <f>C18/C12</f>
+        <v>0.107578</v>
+        <v/>
+      </c>
+      <c r="D19" s="8">
+        <f>D18/D12</f>
+        <v>0.12107</v>
+        <v/>
+      </c>
+      <c r="E19" s="8">
+        <f>E18/E12</f>
+        <v>0.128614</v>
+        <v/>
+      </c>
+      <c r="F19" s="8">
+        <f>F18/F12</f>
+        <v>0.135243</v>
+        <v/>
+      </c>
+      <c r="G19" s="8">
+        <f>G18/G12</f>
+        <v>0.138265</v>
+        <v/>
+      </c>
+      <c r="H19" s="8">
+        <f>H18/H12</f>
+        <v>0.197522</v>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="13" t="inlineStr">
+        <is>
+          <t>Memória: base tributável ≈ EBIT − subvenção de ICMS (excluída da base, pois o crédito presumido persiste sem a reforma). A compensação de prejuízo fiscal é limitada a 30% da base por ano (trava brasileira). A alíquota efetiva sobe de ~11% para ~14% à medida que o prejuízo de R$755mi é consumido; na perpetuidade assume-se prejuízo esgotado (~20%).</t>
+        </is>
+      </c>
+    </row>
+    <row r="22"/>
+    <row r="23"/>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="B21:H23"/>
+    <mergeCell ref="B2:H2"/>
+    <mergeCell ref="B10:H10"/>
+    <mergeCell ref="B4:D4"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B2:D31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
     <col width="42" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="38" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="2" ht="26" customHeight="1">
-      <c r="B2" s="27" t="inlineStr">
+      <c r="B2" s="28" t="inlineStr">
         <is>
           <t>Premissas, Dados-base e Avaliação por Múltiplos</t>
         </is>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
-      <c r="B4" s="28" t="inlineStr">
-        <is>
-          <t>1. Dados-base 2025A (consolidado, R$ milhões)</t>
+      <c r="B4" s="29" t="inlineStr">
+        <is>
+          <t>1. Dados-base 2025A (R$ milhões)</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="18" t="inlineStr">
+      <c r="B5" s="20" t="inlineStr">
         <is>
           <t>Receita líquida 2025</t>
         </is>
       </c>
-      <c r="C5" s="19" t="n">
+      <c r="C5" s="21" t="n">
         <v>3067.594</v>
       </c>
-      <c r="D5" s="25" t="inlineStr">
+      <c r="D5" s="26" t="inlineStr">
         <is>
           <t>DF Cimed &amp; Co 2025</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="18" t="inlineStr">
+      <c r="B6" s="20" t="inlineStr">
         <is>
           <t>EBIT 2025</t>
         </is>
       </c>
-      <c r="C6" s="19" t="n">
+      <c r="C6" s="21" t="n">
         <v>358.827</v>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="18" t="inlineStr">
-        <is>
-          <t>Depreciação &amp; amortização 2025</t>
-        </is>
-      </c>
-      <c r="C7" s="19" t="n">
+      <c r="B7" s="20" t="inlineStr">
+        <is>
+          <t>D&amp;A 2025</t>
+        </is>
+      </c>
+      <c r="C7" s="21" t="n">
         <v>121.334</v>
       </c>
     </row>
@@ -1690,158 +2160,148 @@
           <t>EBITDA 2025</t>
         </is>
       </c>
-      <c r="C8" s="22" t="n">
+      <c r="C8" s="23" t="n">
         <v>480.161</v>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="18" t="inlineStr">
+      <c r="B9" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">  margem EBITDA 2025</t>
         </is>
       </c>
-      <c r="C9" s="26" t="n">
+      <c r="C9" s="27" t="n">
         <v>0.1565269067549356</v>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="18" t="inlineStr">
-        <is>
-          <t>Lucro líquido 2025</t>
-        </is>
-      </c>
-      <c r="C10" s="19" t="n">
-        <v>196.709</v>
+      <c r="B10" s="20" t="inlineStr">
+        <is>
+          <t>Custo das mercadorias vendidas 2025</t>
+        </is>
+      </c>
+      <c r="C10" s="21" t="n">
+        <v>1684.485</v>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1">
-      <c r="B12" s="28" t="inlineStr">
+      <c r="B12" s="29" t="inlineStr">
         <is>
           <t>2. Premissas gerais</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="29" t="inlineStr">
-        <is>
-          <t>Depreciação &amp; amortização (% receita)</t>
-        </is>
-      </c>
-      <c r="C13" s="30" t="n">
+      <c r="B13" s="30" t="inlineStr">
+        <is>
+          <t>D&amp;A (% receita)</t>
+        </is>
+      </c>
+      <c r="C13" s="31" t="n">
         <v>0.04</v>
       </c>
-      <c r="D13" s="25" t="inlineStr">
-        <is>
-          <t>~3,96% em 2025</t>
-        </is>
-      </c>
     </row>
     <row r="14">
-      <c r="B14" s="29" t="inlineStr">
-        <is>
-          <t>Alíquota efetiva de impostos</t>
-        </is>
-      </c>
-      <c r="C14" s="30" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="D14" s="25" t="inlineStr">
-        <is>
-          <t>ef. negativa em 2025; sobe c/ fim do ICMS (reforma tributária)</t>
+      <c r="B14" s="30" t="inlineStr">
+        <is>
+          <t>Crescimento na perpetuidade (g)</t>
+        </is>
+      </c>
+      <c r="C14" s="31" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D14" s="26" t="inlineStr">
+        <is>
+          <t>~inflação LP + real</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="29" t="inlineStr">
-        <is>
-          <t>Crescimento na perpetuidade (g)</t>
-        </is>
-      </c>
-      <c r="C15" s="30" t="n">
+      <c r="B15" s="30" t="inlineStr">
+        <is>
+          <t>Crescimento na perpetuidade (ref. p/ termo)</t>
+        </is>
+      </c>
+      <c r="C15" s="31" t="n">
         <v>0.05</v>
       </c>
-      <c r="D15" s="25" t="inlineStr">
-        <is>
-          <t>~inflação LP (4-4,5%) + real</t>
+      <c r="D15" s="26" t="inlineStr">
+        <is>
+          <t>usado nas abas Impostos/DCF</t>
         </is>
       </c>
     </row>
     <row r="17" ht="22" customHeight="1">
-      <c r="B17" s="28" t="inlineStr">
+      <c r="B17" s="29" t="inlineStr">
         <is>
           <t>3. Ponte para Equity — dívida líquida 2025</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="18" t="inlineStr">
-        <is>
-          <t>Empréstimos, financiamentos e debêntures</t>
-        </is>
-      </c>
-      <c r="C18" s="19" t="n">
+      <c r="B18" s="20" t="inlineStr">
+        <is>
+          <t>Empréstimos, financ. e debêntures</t>
+        </is>
+      </c>
+      <c r="C18" s="21" t="n">
         <v>1633.539</v>
       </c>
-      <c r="D18" s="25" t="inlineStr">
-        <is>
-          <t>circ.+não circ.</t>
-        </is>
-      </c>
     </row>
     <row r="19">
-      <c r="B19" s="18" t="inlineStr">
-        <is>
-          <t>(+) Passivo de arrendamento (leasing)</t>
-        </is>
-      </c>
-      <c r="C19" s="19" t="n">
+      <c r="B19" s="20" t="inlineStr">
+        <is>
+          <t>(+) Arrendamento (leasing)</t>
+        </is>
+      </c>
+      <c r="C19" s="21" t="n">
         <v>157.884</v>
       </c>
     </row>
     <row r="20">
       <c r="B20" s="4">
-        <f> Dívida bruta total</f>
-        <v/>
-      </c>
-      <c r="C20" s="22" t="n">
+        <f> Dívida bruta</f>
+        <v/>
+      </c>
+      <c r="C20" s="23" t="n">
         <v>1791.423</v>
       </c>
     </row>
     <row r="21">
-      <c r="B21" s="18" t="inlineStr">
-        <is>
-          <t>(-) Caixa e equivalentes + TVM</t>
-        </is>
-      </c>
-      <c r="C21" s="19" t="n">
+      <c r="B21" s="20" t="inlineStr">
+        <is>
+          <t>(-) Caixa + TVM</t>
+        </is>
+      </c>
+      <c r="C21" s="21" t="n">
         <v>438.377</v>
       </c>
     </row>
     <row r="22">
-      <c r="B22" s="37">
+      <c r="B22" s="44">
         <f> Dívida líquida</f>
         <v/>
       </c>
-      <c r="C22" s="38" t="n">
+      <c r="C22" s="46" t="n">
         <v>1353.046</v>
       </c>
-      <c r="D22" s="25" t="inlineStr">
-        <is>
-          <t>ND/EBITDA = 2,8x ✓ (covenant)</t>
+      <c r="D22" s="26" t="inlineStr">
+        <is>
+          <t>ND/EBITDA=2,8x</t>
         </is>
       </c>
     </row>
     <row r="24" ht="22" customHeight="1">
-      <c r="B24" s="28" t="inlineStr">
-        <is>
-          <t>4. Avaliação por múltiplos de comparáveis (mercado)</t>
+      <c r="B24" s="29" t="inlineStr">
+        <is>
+          <t>4. Avaliação por múltiplos (cross-check de mercado)</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="B25" s="16" t="inlineStr">
         <is>
-          <t>Comparável listada (B3)</t>
+          <t>Comparável (B3)</t>
         </is>
       </c>
       <c r="C25" s="17" t="inlineStr">
@@ -1851,93 +2311,75 @@
       </c>
       <c r="D25" s="16" t="inlineStr">
         <is>
-          <t>Referência</t>
+          <t>Ref.</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="B26" s="18" t="inlineStr">
+      <c r="B26" s="20" t="inlineStr">
         <is>
           <t>Hypera (HYPE3)</t>
         </is>
       </c>
-      <c r="C26" s="39" t="n">
+      <c r="C26" s="47" t="n">
         <v>7.56</v>
       </c>
-      <c r="D26" s="25" t="inlineStr">
+      <c r="D26" s="26" t="inlineStr">
         <is>
           <t>mar/26; EV R$22,7bi</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="B27" s="18" t="inlineStr">
+      <c r="B27" s="20" t="inlineStr">
         <is>
           <t>Blau (BLAU3)</t>
         </is>
       </c>
-      <c r="C27" s="39" t="n">
+      <c r="C27" s="47" t="n">
         <v>6.5</v>
       </c>
-      <c r="D27" s="25" t="inlineStr">
-        <is>
-          <t>caixa líq.; alta margem</t>
+      <c r="D27" s="26" t="inlineStr">
+        <is>
+          <t>caixa líq.</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="B28" s="18" t="inlineStr">
-        <is>
-          <t>Prêmio cresc. / (-) desconto IPO &amp; alavancagem</t>
-        </is>
-      </c>
-      <c r="C28" s="39" t="n"/>
-      <c r="D28" s="25" t="inlineStr">
-        <is>
-          <t>líquido ≈ neutro</t>
-        </is>
+      <c r="B28" s="39" t="inlineStr">
+        <is>
+          <t>EV/EBITDA selecionado (forward 2026E)</t>
+        </is>
+      </c>
+      <c r="C28" s="48" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="29">
-      <c r="B29" s="35" t="inlineStr">
-        <is>
-          <t>EV/EBITDA selecionado (forward, 2026E)</t>
-        </is>
-      </c>
-      <c r="C29" s="40" t="n">
-        <v>7</v>
-      </c>
-      <c r="D29" s="25" t="inlineStr">
-        <is>
-          <t>≈ setor; leve desconto vs. Hypera</t>
-        </is>
+      <c r="B29" s="24">
+        <f> Enterprise Value (múltiplos)</f>
+        <v/>
+      </c>
+      <c r="C29" s="25" t="n">
+        <v>4088.489283200001</v>
       </c>
     </row>
     <row r="30">
-      <c r="B30" s="23">
-        <f> Enterprise Value (mercado)</f>
-        <v/>
-      </c>
-      <c r="C30" s="24" t="n">
-        <v>4088.489283200001</v>
+      <c r="B30" s="20" t="inlineStr">
+        <is>
+          <t>(-) Dívida líquida</t>
+        </is>
+      </c>
+      <c r="C30" s="21" t="n">
+        <v>-1353.046</v>
       </c>
     </row>
     <row r="31">
-      <c r="B31" s="18" t="inlineStr">
-        <is>
-          <t>(-) Dívida líquida</t>
-        </is>
-      </c>
-      <c r="C31" s="19" t="n">
-        <v>-1353.046</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="B32" s="23">
-        <f> Equity Value (mercado)</f>
-        <v/>
-      </c>
-      <c r="C32" s="24" t="n">
+      <c r="B31" s="24">
+        <f> Equity Value (múltiplos)</f>
+        <v/>
+      </c>
+      <c r="C31" s="25" t="n">
         <v>2735.4432832</v>
       </c>
     </row>
@@ -1953,30 +2395,29 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:I22"/>
+  <dimension ref="B2:H32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="42" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="34" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="2" ht="26" customHeight="1">
-      <c r="B2" s="27" t="inlineStr">
-        <is>
-          <t>Capital de Giro — Histórico e Projeção (R$ milhões)</t>
+      <c r="B2" s="28" t="inlineStr">
+        <is>
+          <t>Capital de Giro — Dias de Giro (memória de cálculo) — R$ milhões</t>
         </is>
       </c>
     </row>
@@ -1996,288 +2437,549 @@
           <t>2025</t>
         </is>
       </c>
+      <c r="H4" s="16" t="inlineStr">
+        <is>
+          <t>Fórmula</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="B5" s="18" t="inlineStr">
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>Receita líquida</t>
+        </is>
+      </c>
+      <c r="C5" s="43" t="n">
+        <v>2726.887</v>
+      </c>
+      <c r="D5" s="43" t="n">
+        <v>3067.594</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="20" t="inlineStr">
+        <is>
+          <t>Custo das mercadorias vendidas (CMV)</t>
+        </is>
+      </c>
+      <c r="C6" s="43" t="n">
+        <v>1402.853</v>
+      </c>
+      <c r="D6" s="43" t="n">
+        <v>1684.485</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="20" t="inlineStr">
         <is>
           <t>Contas a receber</t>
         </is>
       </c>
-      <c r="C5" s="19" t="n">
+      <c r="C7" s="43" t="n">
         <v>757.47</v>
       </c>
-      <c r="D5" s="19" t="n">
+      <c r="D7" s="43" t="n">
         <v>1106.327</v>
       </c>
     </row>
-    <row r="6">
-      <c r="B6" s="18" t="inlineStr">
-        <is>
-          <t>(+) Estoques</t>
-        </is>
-      </c>
-      <c r="C6" s="19" t="n">
+    <row r="8">
+      <c r="B8" s="20" t="inlineStr">
+        <is>
+          <t>Estoques</t>
+        </is>
+      </c>
+      <c r="C8" s="43" t="n">
         <v>507.999</v>
       </c>
-      <c r="D6" s="19" t="n">
+      <c r="D8" s="43" t="n">
         <v>699.5069999999999</v>
       </c>
     </row>
-    <row r="7">
-      <c r="B7" s="18" t="inlineStr">
-        <is>
-          <t>(-) Fornecedores</t>
-        </is>
-      </c>
-      <c r="C7" s="19" t="n">
-        <v>-623.978</v>
-      </c>
-      <c r="D7" s="19" t="n">
-        <v>-677.3920000000001</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="B8" s="20">
-        <f> Capital de giro (líquido)</f>
-        <v/>
-      </c>
-      <c r="C8" s="21" t="n">
+    <row r="9">
+      <c r="B9" s="20" t="inlineStr">
+        <is>
+          <t>Fornecedores</t>
+        </is>
+      </c>
+      <c r="C9" s="43" t="n">
+        <v>623.978</v>
+      </c>
+      <c r="D9" s="43" t="n">
+        <v>677.3920000000001</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="18">
+        <f> Capital de giro (AR+Estoq−Forn)</f>
+        <v/>
+      </c>
+      <c r="C10" s="5" t="n">
         <v>641.4910000000001</v>
       </c>
-      <c r="D8" s="21" t="n">
+      <c r="D10" s="5" t="n">
         <v>1128.442</v>
       </c>
-    </row>
-    <row r="9">
-      <c r="B9" s="18" t="inlineStr">
+      <c r="H10" s="26">
+        <f> linha7 + linha8 − linha9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">  % da receita líquida</t>
         </is>
       </c>
-      <c r="C9" s="26" t="n">
+      <c r="C11" s="27" t="n">
         <v>0.2352466383828886</v>
       </c>
-      <c r="D9" s="26" t="n">
+      <c r="D11" s="27" t="n">
         <v>0.3678589800345156</v>
       </c>
-    </row>
-    <row r="10">
-      <c r="B10" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Prazo médio receb. (DSO)</t>
-        </is>
-      </c>
-      <c r="C10" s="41" t="n">
+      <c r="H11" s="26">
+        <f> CG ÷ Receita</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  DSO — prazo médio recebimento</t>
+        </is>
+      </c>
+      <c r="C12" s="49" t="n">
         <v>101.3890747948118</v>
       </c>
-      <c r="D10" s="41" t="n">
+      <c r="D12" s="49" t="n">
         <v>131.6371576551525</v>
       </c>
-    </row>
-    <row r="11">
-      <c r="B11" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Prazo médio estoques (DIO)</t>
-        </is>
-      </c>
-      <c r="C11" s="41" t="n">
+      <c r="H12" s="26">
+        <f> AR ÷ Receita × 365</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  DIO — prazo médio estoques</t>
+        </is>
+      </c>
+      <c r="C13" s="49" t="n">
         <v>132.1732462346376</v>
       </c>
-      <c r="D11" s="41" t="n">
+      <c r="D13" s="49" t="n">
         <v>151.5715812251222</v>
       </c>
-    </row>
-    <row r="12">
-      <c r="B12" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Prazo médio fornec. (DPO)</t>
-        </is>
-      </c>
-      <c r="C12" s="41" t="n">
+      <c r="H13" s="26">
+        <f> Estoque ÷ CMV × 365</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  DPO — prazo médio fornecedores</t>
+        </is>
+      </c>
+      <c r="C14" s="49" t="n">
         <v>162.3491342286041</v>
       </c>
-      <c r="D12" s="41" t="n">
+      <c r="D14" s="49" t="n">
         <v>146.7796270076611</v>
       </c>
-    </row>
-    <row r="13">
-      <c r="B13" s="4" t="inlineStr">
+      <c r="H14" s="26">
+        <f> Forn. ÷ CMV × 365</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">  Ciclo de conversão de caixa</t>
         </is>
       </c>
-      <c r="C13" s="42" t="n">
+      <c r="C15" s="50" t="n">
         <v>71.21318680084528</v>
       </c>
-      <c r="D13" s="42" t="n">
+      <c r="D15" s="50" t="n">
         <v>136.4291118726136</v>
       </c>
-    </row>
-    <row r="16">
-      <c r="B16" s="16" t="inlineStr">
-        <is>
-          <t>Projeção</t>
-        </is>
-      </c>
-      <c r="C16" s="17" t="inlineStr">
+      <c r="H15" s="26">
+        <f> DSO + DIO − DPO</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="16" t="inlineStr">
+        <is>
+          <t>Projeção — premissas de dias de giro</t>
+        </is>
+      </c>
+      <c r="C17" s="17" t="inlineStr">
         <is>
           <t>2026E</t>
         </is>
       </c>
-      <c r="D16" s="17" t="inlineStr">
+      <c r="D17" s="17" t="inlineStr">
         <is>
           <t>2027E</t>
         </is>
       </c>
-      <c r="E16" s="17" t="inlineStr">
+      <c r="E17" s="17" t="inlineStr">
         <is>
           <t>2028E</t>
         </is>
       </c>
-      <c r="F16" s="17" t="inlineStr">
+      <c r="F17" s="17" t="inlineStr">
         <is>
           <t>2029E</t>
         </is>
       </c>
-      <c r="G16" s="17" t="inlineStr">
+      <c r="G17" s="17" t="inlineStr">
         <is>
           <t>2030E</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="B17" s="18" t="inlineStr">
+    <row r="18">
+      <c r="B18" s="30" t="inlineStr">
+        <is>
+          <t>DSO — recebimento (dias)</t>
+        </is>
+      </c>
+      <c r="C18" s="51" t="n">
+        <v>128</v>
+      </c>
+      <c r="D18" s="51" t="n">
+        <v>124</v>
+      </c>
+      <c r="E18" s="51" t="n">
+        <v>120</v>
+      </c>
+      <c r="F18" s="51" t="n">
+        <v>117</v>
+      </c>
+      <c r="G18" s="51" t="n">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="30" t="inlineStr">
+        <is>
+          <t>DIO — estoques (dias)</t>
+        </is>
+      </c>
+      <c r="C19" s="51" t="n">
+        <v>145</v>
+      </c>
+      <c r="D19" s="51" t="n">
+        <v>138</v>
+      </c>
+      <c r="E19" s="51" t="n">
+        <v>132</v>
+      </c>
+      <c r="F19" s="51" t="n">
+        <v>128</v>
+      </c>
+      <c r="G19" s="51" t="n">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="30" t="inlineStr">
+        <is>
+          <t>DPO — fornecedores (dias)</t>
+        </is>
+      </c>
+      <c r="C20" s="51" t="n">
+        <v>148</v>
+      </c>
+      <c r="D20" s="51" t="n">
+        <v>150</v>
+      </c>
+      <c r="E20" s="51" t="n">
+        <v>150</v>
+      </c>
+      <c r="F20" s="51" t="n">
+        <v>150</v>
+      </c>
+      <c r="G20" s="51" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="20" t="inlineStr">
         <is>
           <t>Receita líquida</t>
         </is>
       </c>
-      <c r="C17" s="43">
+      <c r="C21" s="52">
         <f>Projecoes!C7</f>
         <v>3435.70528</v>
         <v/>
       </c>
-      <c r="D17" s="43">
+      <c r="D21" s="52">
         <f>Projecoes!D7</f>
         <v>3813.632861</v>
         <v/>
       </c>
-      <c r="E17" s="43">
+      <c r="E21" s="52">
         <f>Projecoes!E7</f>
         <v>4194.996147</v>
         <v/>
       </c>
-      <c r="F17" s="43">
+      <c r="F21" s="52">
         <f>Projecoes!F7</f>
         <v>4530.595839</v>
         <v/>
       </c>
-      <c r="G17" s="43">
+      <c r="G21" s="52">
         <f>Projecoes!G7</f>
         <v>4825.084568</v>
         <v/>
       </c>
     </row>
-    <row r="18">
-      <c r="B18" s="44" t="inlineStr">
-        <is>
-          <t>Capital de giro (% da receita)</t>
-        </is>
-      </c>
-      <c r="C18" s="30" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="D18" s="30" t="n">
-        <v>0.34</v>
-      </c>
-      <c r="E18" s="30" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="F18" s="30" t="n">
-        <v>0.325</v>
-      </c>
-      <c r="G18" s="30" t="n">
-        <v>0.32</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="B19" s="20" t="inlineStr">
-        <is>
-          <t>Capital de giro (líquido)</t>
-        </is>
-      </c>
-      <c r="C19" s="5">
-        <f>C17*C18</f>
-        <v>1202.496848</v>
-        <v/>
-      </c>
-      <c r="D19" s="5">
-        <f>D17*D18</f>
-        <v>1296.635173</v>
-        <v/>
-      </c>
-      <c r="E19" s="5">
-        <f>E17*E18</f>
-        <v>1384.348728</v>
-        <v/>
-      </c>
-      <c r="F19" s="5">
-        <f>F17*F18</f>
-        <v>1472.443648</v>
-        <v/>
-      </c>
-      <c r="G19" s="5">
-        <f>G17*G18</f>
-        <v>1544.027062</v>
-        <v/>
-      </c>
-    </row>
-    <row r="20">
-      <c r="B20" s="23">
+    <row r="22">
+      <c r="B22" s="37" t="inlineStr">
+        <is>
+          <t>CMV (= % CMV × receita)</t>
+        </is>
+      </c>
+      <c r="C22" s="43">
+        <f>0.54*C21</f>
+        <v>1855.280851</v>
+        <v/>
+      </c>
+      <c r="D22" s="43">
+        <f>0.53*D21</f>
+        <v>2021.225416</v>
+        <v/>
+      </c>
+      <c r="E22" s="43">
+        <f>0.52*E21</f>
+        <v>2181.397996</v>
+        <v/>
+      </c>
+      <c r="F22" s="43">
+        <f>0.515*F21</f>
+        <v>2333.256857</v>
+        <v/>
+      </c>
+      <c r="G22" s="43">
+        <f>0.51*G21</f>
+        <v>2460.79313</v>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="37" t="inlineStr">
+        <is>
+          <t>Contas a receber (=DSO÷365×Receita)</t>
+        </is>
+      </c>
+      <c r="C23" s="43">
+        <f>C18/365*C21</f>
+        <v>1204.850071</v>
+        <v/>
+      </c>
+      <c r="D23" s="43">
+        <f>D18/365*D21</f>
+        <v>1295.590342</v>
+        <v/>
+      </c>
+      <c r="E23" s="43">
+        <f>E18/365*E21</f>
+        <v>1379.176815</v>
+        <v/>
+      </c>
+      <c r="F23" s="43">
+        <f>F18/365*F21</f>
+        <v>1452.273187</v>
+        <v/>
+      </c>
+      <c r="G23" s="43">
+        <f>G18/365*G21</f>
+        <v>1520.232124</v>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="37" t="inlineStr">
+        <is>
+          <t>(+) Estoques (=DIO÷365×CMV)</t>
+        </is>
+      </c>
+      <c r="C24" s="43">
+        <f>C19/365*C22</f>
+        <v>737.029379</v>
+        <v/>
+      </c>
+      <c r="D24" s="43">
+        <f>D19/365*D22</f>
+        <v>764.189335</v>
+        <v/>
+      </c>
+      <c r="E24" s="43">
+        <f>E19/365*E22</f>
+        <v>788.889138</v>
+        <v/>
+      </c>
+      <c r="F24" s="43">
+        <f>F19/365*F22</f>
+        <v>818.238021</v>
+        <v/>
+      </c>
+      <c r="G24" s="43">
+        <f>G19/365*G22</f>
+        <v>842.737373</v>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="37" t="inlineStr">
+        <is>
+          <t>(-) Fornecedores (=DPO÷365×CMV)</t>
+        </is>
+      </c>
+      <c r="C25" s="43">
+        <f>-C20/365*C22</f>
+        <v>-752.278263</v>
+        <v/>
+      </c>
+      <c r="D25" s="43">
+        <f>-D20/365*D22</f>
+        <v>-830.640582</v>
+        <v/>
+      </c>
+      <c r="E25" s="43">
+        <f>-E20/365*E22</f>
+        <v>-896.46493</v>
+        <v/>
+      </c>
+      <c r="F25" s="43">
+        <f>-F20/365*F22</f>
+        <v>-958.872681</v>
+        <v/>
+      </c>
+      <c r="G25" s="43">
+        <f>-G20/365*G22</f>
+        <v>-1011.284848</v>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="18">
+        <f> Capital de giro líquido</f>
+        <v/>
+      </c>
+      <c r="C26" s="5">
+        <f>C23+C24+C25</f>
+        <v>1189.601187</v>
+        <v/>
+      </c>
+      <c r="D26" s="5">
+        <f>D23+D24+D25</f>
+        <v>1229.139095</v>
+        <v/>
+      </c>
+      <c r="E26" s="5">
+        <f>E23+E24+E25</f>
+        <v>1271.601024</v>
+        <v/>
+      </c>
+      <c r="F26" s="5">
+        <f>F23+F24+F25</f>
+        <v>1311.638527</v>
+        <v/>
+      </c>
+      <c r="G26" s="5">
+        <f>G23+G24+G25</f>
+        <v>1351.68465</v>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="37" t="inlineStr">
+        <is>
+          <t>Ciclo de conversão de caixa (DSO+DIO−DPO)</t>
+        </is>
+      </c>
+      <c r="C27" s="49">
+        <f>C18+C19-C20</f>
+        <v>125.0</v>
+        <v/>
+      </c>
+      <c r="D27" s="49">
+        <f>D18+D19-D20</f>
+        <v>112.0</v>
+        <v/>
+      </c>
+      <c r="E27" s="49">
+        <f>E18+E19-E20</f>
+        <v>102.0</v>
+        <v/>
+      </c>
+      <c r="F27" s="49">
+        <f>F18+F19-F20</f>
+        <v>95.0</v>
+        <v/>
+      </c>
+      <c r="G27" s="49">
+        <f>G18+G19-G20</f>
+        <v>90.0</v>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" s="24">
         <f> Variação do capital de giro (ΔWC)</f>
         <v/>
       </c>
-      <c r="C20" s="8">
-        <f>C19-D8</f>
-        <v>74.054848</v>
-        <v/>
-      </c>
-      <c r="D20" s="8">
-        <f>D19-C19</f>
-        <v>94.138325</v>
-        <v/>
-      </c>
-      <c r="E20" s="8">
-        <f>E19-D19</f>
-        <v>87.713556</v>
-        <v/>
-      </c>
-      <c r="F20" s="8">
-        <f>F19-E19</f>
-        <v>88.094919</v>
-        <v/>
-      </c>
-      <c r="G20" s="8">
-        <f>G19-F19</f>
-        <v>71.583414</v>
-        <v/>
-      </c>
-    </row>
-    <row r="22">
-      <c r="B22" s="15" t="inlineStr">
-        <is>
-          <t>Premissa: normalização gradual do ciclo de caixa (36,8% → 32% da receita), revertendo parte do estouro de 2025.</t>
-        </is>
-      </c>
-    </row>
+      <c r="C28" s="7">
+        <f>C26-D10</f>
+        <v>61.159187</v>
+        <v/>
+      </c>
+      <c r="D28" s="7">
+        <f>D26-C26</f>
+        <v>39.537908</v>
+        <v/>
+      </c>
+      <c r="E28" s="7">
+        <f>E26-D26</f>
+        <v>42.461929</v>
+        <v/>
+      </c>
+      <c r="F28" s="7">
+        <f>F26-E26</f>
+        <v>40.037503</v>
+        <v/>
+      </c>
+      <c r="G28" s="7">
+        <f>G26-F26</f>
+        <v>40.046123</v>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="13" t="inlineStr">
+        <is>
+          <t>Em 2025 o ciclo de caixa saltou de 71 para 136 dias (estoques +38%, recebíveis +46%), consumindo ~R$487mi — origem do FCO negativo. A projeção assume melhora gradual de eficiência (DSO 132→115, DIO 152→125, DPO ~150), reduzindo o ΔWC. ΔWC positivo consome caixa no FCFF.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31"/>
+    <row r="32"/>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="B2:I2"/>
+  <mergeCells count="2">
+    <mergeCell ref="B2:G2"/>
+    <mergeCell ref="B30:G32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2296,9 +2998,9 @@
   </cols>
   <sheetData>
     <row r="2" ht="26" customHeight="1">
-      <c r="B2" s="27" t="inlineStr">
-        <is>
-          <t>Projeção de Fluxo de Caixa Livre Desalavancado (FCFF) — R$ milhões</t>
+      <c r="B2" s="28" t="inlineStr">
+        <is>
+          <t>Projeção — FCFF Desalavancado (R$ milhões)</t>
         </is>
       </c>
     </row>
@@ -2335,24 +3037,24 @@
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="44" t="inlineStr">
+      <c r="B6" s="37" t="inlineStr">
         <is>
           <t>Crescimento da receita (%)</t>
         </is>
       </c>
-      <c r="C6" s="30" t="n">
+      <c r="C6" s="31" t="n">
         <v>0.12</v>
       </c>
-      <c r="D6" s="30" t="n">
+      <c r="D6" s="31" t="n">
         <v>0.11</v>
       </c>
-      <c r="E6" s="30" t="n">
+      <c r="E6" s="31" t="n">
         <v>0.1</v>
       </c>
-      <c r="F6" s="30" t="n">
+      <c r="F6" s="31" t="n">
         <v>0.08</v>
       </c>
-      <c r="G6" s="30" t="n">
+      <c r="G6" s="31" t="n">
         <v>0.065</v>
       </c>
     </row>
@@ -2362,56 +3064,56 @@
           <t>Receita líquida</t>
         </is>
       </c>
-      <c r="C7" s="45">
+      <c r="C7" s="9">
         <f>Premissas!$C$5*(1+C6)</f>
         <v>3435.70528</v>
         <v/>
       </c>
-      <c r="D7" s="45">
+      <c r="D7" s="9">
         <f>C7*(1+D6)</f>
         <v>3813.632861</v>
         <v/>
       </c>
-      <c r="E7" s="45">
+      <c r="E7" s="9">
         <f>D7*(1+E6)</f>
         <v>4194.996147</v>
         <v/>
       </c>
-      <c r="F7" s="45">
+      <c r="F7" s="9">
         <f>E7*(1+F6)</f>
         <v>4530.595839</v>
         <v/>
       </c>
-      <c r="G7" s="45">
+      <c r="G7" s="9">
         <f>F7*(1+G6)</f>
         <v>4825.084568</v>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="44" t="inlineStr">
+      <c r="B8" s="37" t="inlineStr">
         <is>
           <t>Margem EBITDA (%)</t>
         </is>
       </c>
-      <c r="C8" s="30" t="n">
+      <c r="C8" s="31" t="n">
         <v>0.17</v>
       </c>
-      <c r="D8" s="30" t="n">
+      <c r="D8" s="31" t="n">
         <v>0.185</v>
       </c>
-      <c r="E8" s="30" t="n">
+      <c r="E8" s="31" t="n">
         <v>0.195</v>
       </c>
-      <c r="F8" s="30" t="n">
+      <c r="F8" s="31" t="n">
         <v>0.205</v>
       </c>
-      <c r="G8" s="30" t="n">
+      <c r="G8" s="31" t="n">
         <v>0.21</v>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="20" t="inlineStr">
+      <c r="B9" s="18" t="inlineStr">
         <is>
           <t>EBITDA</t>
         </is>
@@ -2443,277 +3145,277 @@
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="44" t="inlineStr">
+      <c r="B10" s="37" t="inlineStr">
         <is>
           <t>(-) Depreciação &amp; amortização</t>
         </is>
       </c>
-      <c r="C10" s="19">
+      <c r="C10" s="21">
         <f>-C7*Premissas!$C$13</f>
         <v>-137.428211</v>
         <v/>
       </c>
-      <c r="D10" s="19">
+      <c r="D10" s="21">
         <f>-D7*Premissas!$C$13</f>
         <v>-152.545314</v>
         <v/>
       </c>
-      <c r="E10" s="19">
+      <c r="E10" s="21">
         <f>-E7*Premissas!$C$13</f>
         <v>-167.799846</v>
         <v/>
       </c>
-      <c r="F10" s="19">
+      <c r="F10" s="21">
         <f>-F7*Premissas!$C$13</f>
         <v>-181.223834</v>
         <v/>
       </c>
-      <c r="G10" s="19">
+      <c r="G10" s="21">
         <f>-G7*Premissas!$C$13</f>
         <v>-193.003383</v>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="10">
+      <c r="B11" s="22">
         <f> EBIT</f>
         <v/>
       </c>
-      <c r="C11" s="22">
+      <c r="C11" s="23">
         <f>C9+C10</f>
         <v>446.641686</v>
         <v/>
       </c>
-      <c r="D11" s="22">
+      <c r="D11" s="23">
         <f>D9+D10</f>
         <v>552.976765</v>
         <v/>
       </c>
-      <c r="E11" s="22">
+      <c r="E11" s="23">
         <f>E9+E10</f>
         <v>650.224403</v>
         <v/>
       </c>
-      <c r="F11" s="22">
+      <c r="F11" s="23">
         <f>F9+F10</f>
         <v>747.548313</v>
         <v/>
       </c>
-      <c r="G11" s="22">
+      <c r="G11" s="23">
         <f>G9+G10</f>
         <v>820.264377</v>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="44" t="inlineStr">
-        <is>
-          <t>(-) Impostos sobre EBIT</t>
-        </is>
-      </c>
-      <c r="C12" s="19">
-        <f>-C11*Premissas!$C$14</f>
-        <v>-111.660422</v>
-        <v/>
-      </c>
-      <c r="D12" s="19">
-        <f>-D11*Premissas!$C$14</f>
-        <v>-138.244191</v>
-        <v/>
-      </c>
-      <c r="E12" s="19">
-        <f>-E11*Premissas!$C$14</f>
-        <v>-162.556101</v>
-        <v/>
-      </c>
-      <c r="F12" s="19">
-        <f>-F11*Premissas!$C$14</f>
-        <v>-186.887078</v>
-        <v/>
-      </c>
-      <c r="G12" s="19">
-        <f>-G11*Premissas!$C$14</f>
-        <v>-205.066094</v>
+      <c r="B12" s="37" t="inlineStr">
+        <is>
+          <t>(-) Imposto corrente (com prej. fiscal)</t>
+        </is>
+      </c>
+      <c r="C12" s="21">
+        <f>-Impostos!C18</f>
+        <v>-48.048737</v>
+        <v/>
+      </c>
+      <c r="D12" s="21">
+        <f>-Impostos!D18</f>
+        <v>-66.948768</v>
+        <v/>
+      </c>
+      <c r="E12" s="21">
+        <f>-Impostos!E18</f>
+        <v>-83.627735</v>
+        <v/>
+      </c>
+      <c r="F12" s="21">
+        <f>-Impostos!F18</f>
+        <v>-101.100772</v>
+        <v/>
+      </c>
+      <c r="G12" s="21">
+        <f>-Impostos!G18</f>
+        <v>-113.414173</v>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="10">
-        <f> NOPAT</f>
-        <v/>
-      </c>
-      <c r="C13" s="22">
+      <c r="B13" s="22">
+        <f> NOPAT (após imposto caixa)</f>
+        <v/>
+      </c>
+      <c r="C13" s="23">
         <f>C11+C12</f>
-        <v>334.981265</v>
-        <v/>
-      </c>
-      <c r="D13" s="22">
+        <v>398.592949</v>
+        <v/>
+      </c>
+      <c r="D13" s="23">
         <f>D11+D12</f>
-        <v>414.732574</v>
-        <v/>
-      </c>
-      <c r="E13" s="22">
+        <v>486.027997</v>
+        <v/>
+      </c>
+      <c r="E13" s="23">
         <f>E11+E12</f>
-        <v>487.668302</v>
-        <v/>
-      </c>
-      <c r="F13" s="22">
+        <v>566.596667</v>
+        <v/>
+      </c>
+      <c r="F13" s="23">
         <f>F11+F12</f>
-        <v>560.661235</v>
-        <v/>
-      </c>
-      <c r="G13" s="22">
+        <v>646.447541</v>
+        <v/>
+      </c>
+      <c r="G13" s="23">
         <f>G11+G12</f>
-        <v>615.198282</v>
+        <v>706.850203</v>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="44" t="inlineStr">
+      <c r="B14" s="37" t="inlineStr">
         <is>
           <t>(+) Depreciação &amp; amortização</t>
         </is>
       </c>
-      <c r="C14" s="19">
+      <c r="C14" s="21">
         <f>-C10</f>
         <v>137.428211</v>
         <v/>
       </c>
-      <c r="D14" s="19">
+      <c r="D14" s="21">
         <f>-D10</f>
         <v>152.545314</v>
         <v/>
       </c>
-      <c r="E14" s="19">
+      <c r="E14" s="21">
         <f>-E10</f>
         <v>167.799846</v>
         <v/>
       </c>
-      <c r="F14" s="19">
+      <c r="F14" s="21">
         <f>-F10</f>
         <v>181.223834</v>
         <v/>
       </c>
-      <c r="G14" s="19">
+      <c r="G14" s="21">
         <f>-G10</f>
         <v>193.003383</v>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="44" t="inlineStr">
+      <c r="B15" s="37" t="inlineStr">
         <is>
           <t>Capex (% receita)</t>
         </is>
       </c>
-      <c r="C15" s="30" t="n">
+      <c r="C15" s="31" t="n">
         <v>0.06</v>
       </c>
-      <c r="D15" s="30" t="n">
+      <c r="D15" s="31" t="n">
         <v>0.055</v>
       </c>
-      <c r="E15" s="30" t="n">
+      <c r="E15" s="31" t="n">
         <v>0.05</v>
       </c>
-      <c r="F15" s="30" t="n">
+      <c r="F15" s="31" t="n">
         <v>0.047</v>
       </c>
-      <c r="G15" s="30" t="n">
+      <c r="G15" s="31" t="n">
         <v>0.045</v>
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="44" t="inlineStr">
+      <c r="B16" s="37" t="inlineStr">
         <is>
           <t>(-) Capex</t>
         </is>
       </c>
-      <c r="C16" s="19">
+      <c r="C16" s="21">
         <f>-C7*C15</f>
         <v>-206.142317</v>
         <v/>
       </c>
-      <c r="D16" s="19">
+      <c r="D16" s="21">
         <f>-D7*D15</f>
         <v>-209.749807</v>
         <v/>
       </c>
-      <c r="E16" s="19">
+      <c r="E16" s="21">
         <f>-E7*E15</f>
         <v>-209.749807</v>
         <v/>
       </c>
-      <c r="F16" s="19">
+      <c r="F16" s="21">
         <f>-F7*F15</f>
         <v>-212.938004</v>
         <v/>
       </c>
-      <c r="G16" s="19">
+      <c r="G16" s="21">
         <f>-G7*G15</f>
         <v>-217.128806</v>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="B17" s="44" t="inlineStr">
+      <c r="B17" s="37" t="inlineStr">
         <is>
           <t>(-) Variação de capital de giro</t>
         </is>
       </c>
-      <c r="C17" s="19">
-        <f>-Capital_de_Giro!C20</f>
-        <v>-74.054848</v>
-        <v/>
-      </c>
-      <c r="D17" s="19">
-        <f>-Capital_de_Giro!D20</f>
-        <v>-94.138325</v>
-        <v/>
-      </c>
-      <c r="E17" s="19">
-        <f>-Capital_de_Giro!E20</f>
-        <v>-87.713556</v>
-        <v/>
-      </c>
-      <c r="F17" s="19">
-        <f>-Capital_de_Giro!F20</f>
-        <v>-88.094919</v>
-        <v/>
-      </c>
-      <c r="G17" s="19">
-        <f>-Capital_de_Giro!G20</f>
-        <v>-71.583414</v>
+      <c r="C17" s="21">
+        <f>-Capital_de_Giro!C28</f>
+        <v>-61.159187</v>
+        <v/>
+      </c>
+      <c r="D17" s="21">
+        <f>-Capital_de_Giro!D28</f>
+        <v>-39.537908</v>
+        <v/>
+      </c>
+      <c r="E17" s="21">
+        <f>-Capital_de_Giro!E28</f>
+        <v>-42.461929</v>
+        <v/>
+      </c>
+      <c r="F17" s="21">
+        <f>-Capital_de_Giro!F28</f>
+        <v>-40.037503</v>
+        <v/>
+      </c>
+      <c r="G17" s="21">
+        <f>-Capital_de_Giro!G28</f>
+        <v>-40.046123</v>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="23">
-        <f> Fluxo de Caixa Livre (FCFF)</f>
-        <v/>
-      </c>
-      <c r="C18" s="8">
+      <c r="B18" s="24">
+        <f> FCFF</f>
+        <v/>
+      </c>
+      <c r="C18" s="7">
         <f>C13+C14+C16+C17</f>
-        <v>192.212311</v>
-        <v/>
-      </c>
-      <c r="D18" s="8">
+        <v>268.719656</v>
+        <v/>
+      </c>
+      <c r="D18" s="7">
         <f>D13+D14+D16+D17</f>
-        <v>263.389756</v>
-        <v/>
-      </c>
-      <c r="E18" s="8">
+        <v>389.285596</v>
+        <v/>
+      </c>
+      <c r="E18" s="7">
         <f>E13+E14+E16+E17</f>
-        <v>358.004785</v>
-        <v/>
-      </c>
-      <c r="F18" s="8">
+        <v>482.184777</v>
+        <v/>
+      </c>
+      <c r="F18" s="7">
         <f>F13+F14+F16+F17</f>
-        <v>440.852145</v>
-        <v/>
-      </c>
-      <c r="G18" s="8">
+        <v>574.695867</v>
+        <v/>
+      </c>
+      <c r="G18" s="7">
         <f>G13+G14+G16+G17</f>
-        <v>519.489445</v>
+        <v>642.678658</v>
         <v/>
       </c>
     </row>
@@ -2725,7 +3427,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2744,9 +3446,9 @@
   </cols>
   <sheetData>
     <row r="2" ht="26" customHeight="1">
-      <c r="B2" s="27" t="inlineStr">
-        <is>
-          <t>Fluxo de Caixa Descontado — Conclusão (R$ milhões)</t>
+      <c r="B2" s="28" t="inlineStr">
+        <is>
+          <t>DCF — Desconto com WACC Variável e Conclusão (R$ milhões)</t>
         </is>
       </c>
     </row>
@@ -2783,120 +3485,130 @@
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="44" t="inlineStr">
-        <is>
-          <t>Período de desconto (t)</t>
-        </is>
-      </c>
-      <c r="C5" s="46" t="n">
-        <v>1</v>
-      </c>
-      <c r="D5" s="46" t="n">
-        <v>2</v>
-      </c>
-      <c r="E5" s="46" t="n">
-        <v>3</v>
-      </c>
-      <c r="F5" s="46" t="n">
-        <v>4</v>
-      </c>
-      <c r="G5" s="46" t="n">
-        <v>5</v>
+      <c r="B5" s="37" t="inlineStr">
+        <is>
+          <t>FCFF</t>
+        </is>
+      </c>
+      <c r="C5" s="43">
+        <f>Projecoes!C18</f>
+        <v>268.719656</v>
+        <v/>
+      </c>
+      <c r="D5" s="43">
+        <f>Projecoes!D18</f>
+        <v>389.285596</v>
+        <v/>
+      </c>
+      <c r="E5" s="43">
+        <f>Projecoes!E18</f>
+        <v>482.184777</v>
+        <v/>
+      </c>
+      <c r="F5" s="43">
+        <f>Projecoes!F18</f>
+        <v>574.695867</v>
+        <v/>
+      </c>
+      <c r="G5" s="43">
+        <f>Projecoes!G18</f>
+        <v>642.678658</v>
+        <v/>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="44" t="inlineStr">
-        <is>
-          <t>FCFF</t>
-        </is>
-      </c>
-      <c r="C6" s="47">
-        <f>Projecoes!C18</f>
-        <v>192.212311</v>
-        <v/>
-      </c>
-      <c r="D6" s="47">
-        <f>Projecoes!D18</f>
-        <v>263.389756</v>
-        <v/>
-      </c>
-      <c r="E6" s="47">
-        <f>Projecoes!E18</f>
-        <v>358.004785</v>
-        <v/>
-      </c>
-      <c r="F6" s="47">
-        <f>Projecoes!F18</f>
-        <v>440.852145</v>
-        <v/>
-      </c>
-      <c r="G6" s="47">
-        <f>Projecoes!G18</f>
-        <v>519.489445</v>
+      <c r="B6" s="37" t="inlineStr">
+        <is>
+          <t>WACC do ano</t>
+        </is>
+      </c>
+      <c r="C6" s="38">
+        <f>WACC!C22</f>
+        <v>0.15361</v>
+        <v/>
+      </c>
+      <c r="D6" s="38">
+        <f>WACC!D22</f>
+        <v>0.153009</v>
+        <v/>
+      </c>
+      <c r="E6" s="38">
+        <f>WACC!E22</f>
+        <v>0.152672</v>
+        <v/>
+      </c>
+      <c r="F6" s="38">
+        <f>WACC!F22</f>
+        <v>0.152377</v>
+        <v/>
+      </c>
+      <c r="G6" s="38">
+        <f>WACC!G22</f>
+        <v>0.152242</v>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="44" t="inlineStr">
-        <is>
-          <t>Fator de desconto @ WACC</t>
-        </is>
-      </c>
-      <c r="C7" s="48">
-        <f>1/(1+WACC!$C$22)^C5</f>
-        <v>0.874063</v>
-        <v/>
-      </c>
-      <c r="D7" s="48">
-        <f>1/(1+WACC!$C$22)^D5</f>
-        <v>0.763987</v>
-        <v/>
-      </c>
-      <c r="E7" s="48">
-        <f>1/(1+WACC!$C$22)^E5</f>
-        <v>0.667773</v>
-        <v/>
-      </c>
-      <c r="F7" s="48">
-        <f>1/(1+WACC!$C$22)^F5</f>
-        <v>0.583676</v>
-        <v/>
-      </c>
-      <c r="G7" s="48">
-        <f>1/(1+WACC!$C$22)^G5</f>
-        <v>0.51017</v>
+      <c r="B7" s="37" t="inlineStr">
+        <is>
+          <t>Fator de desconto (acumulado)</t>
+        </is>
+      </c>
+      <c r="C7" s="53">
+        <f>1/(1+C6)</f>
+        <v>0.866844</v>
+        <v/>
+      </c>
+      <c r="D7" s="53">
+        <f>C7/(1+D6)</f>
+        <v>0.751811</v>
+        <v/>
+      </c>
+      <c r="E7" s="53">
+        <f>D7/(1+E6)</f>
+        <v>0.652233</v>
+        <v/>
+      </c>
+      <c r="F7" s="53">
+        <f>E7/(1+F6)</f>
+        <v>0.565989</v>
+        <v/>
+      </c>
+      <c r="G7" s="53">
+        <f>F7/(1+G6)</f>
+        <v>0.491207</v>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="23" t="inlineStr">
+      <c r="B8" s="24" t="inlineStr">
         <is>
           <t>FCFF a valor presente</t>
         </is>
       </c>
-      <c r="C8" s="24">
-        <f>C6*C7</f>
-        <v>168.005762</v>
-        <v/>
-      </c>
-      <c r="D8" s="24">
-        <f>D6*D7</f>
-        <v>201.226341</v>
-        <v/>
-      </c>
-      <c r="E8" s="24">
-        <f>E6*E7</f>
-        <v>239.065968</v>
-        <v/>
-      </c>
-      <c r="F8" s="24">
-        <f>F6*F7</f>
-        <v>257.314855</v>
-        <v/>
-      </c>
-      <c r="G8" s="24">
-        <f>G6*G7</f>
-        <v>265.027905</v>
+      <c r="C8" s="25">
+        <f>C5*C7</f>
+        <v>232.938123</v>
+        <v/>
+      </c>
+      <c r="D8" s="25">
+        <f>D5*D7</f>
+        <v>292.669149</v>
+        <v/>
+      </c>
+      <c r="E8" s="25">
+        <f>E5*E7</f>
+        <v>314.496769</v>
+        <v/>
+      </c>
+      <c r="F8" s="25">
+        <f>F5*F7</f>
+        <v>325.271596</v>
+        <v/>
+      </c>
+      <c r="G8" s="25">
+        <f>G5*G7</f>
+        <v>315.687992</v>
         <v/>
       </c>
     </row>
@@ -2906,117 +3618,117 @@
           <t>Soma do VP dos FCFF (2026–2030)</t>
         </is>
       </c>
-      <c r="C11" s="22">
+      <c r="C11" s="23">
         <f>SUM(C8:G8)</f>
-        <v>1130.640831</v>
+        <v>1481.06363</v>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="18" t="inlineStr">
-        <is>
-          <t>FCFF normalizado (terminal × (1+g))</t>
-        </is>
-      </c>
-      <c r="C13" s="19">
-        <f>G6*(1+Premissas!C15)</f>
-        <v>545.463918</v>
+      <c r="B13" s="20" t="inlineStr">
+        <is>
+          <t>FCFF terminal (2030 × (1+g))</t>
+        </is>
+      </c>
+      <c r="C13" s="21">
+        <f>G5*(1+Premissas!C14)</f>
+        <v>674.812591</v>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>Valor Terminal (Gordon) = FCFFn/(WACC−g)</t>
-        </is>
-      </c>
-      <c r="C14" s="49">
-        <f>C13/(WACC!C22-Premissas!C15)</f>
-        <v>5797.770804</v>
+      <c r="B14" s="20" t="inlineStr">
+        <is>
+          <t>WACC na perpetuidade</t>
+        </is>
+      </c>
+      <c r="C14" s="38">
+        <f>WACC!H22</f>
+        <v>0.149603</v>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="18" t="inlineStr">
-        <is>
-          <t>Fator de desconto do ano terminal</t>
-        </is>
-      </c>
-      <c r="C15" s="48">
-        <f>G7</f>
-        <v>0.51017</v>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>Valor Terminal = FCFFt/(WACC−g)</t>
+        </is>
+      </c>
+      <c r="C15" s="54">
+        <f>C13/(C14-Premissas!C14)</f>
+        <v>6775.050255</v>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="23" t="inlineStr">
+      <c r="B16" s="24" t="inlineStr">
         <is>
           <t>Valor Terminal a valor presente</t>
         </is>
       </c>
-      <c r="C16" s="24">
-        <f>C14*C15</f>
-        <v>2957.848452</v>
+      <c r="C16" s="25">
+        <f>C15*G7</f>
+        <v>3327.949338</v>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="18" t="inlineStr">
-        <is>
-          <t>VP dos fluxos explícitos</t>
-        </is>
-      </c>
-      <c r="C18" s="19">
+      <c r="B18" s="20" t="inlineStr">
+        <is>
+          <t>VP fluxos explícitos</t>
+        </is>
+      </c>
+      <c r="C18" s="21">
         <f>C11</f>
-        <v>1130.640831</v>
+        <v>1481.06363</v>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="B19" s="20" t="inlineStr">
+      <c r="B19" s="18" t="inlineStr">
         <is>
           <t>ENTERPRISE VALUE (EV)</t>
         </is>
       </c>
       <c r="C19" s="5">
         <f>C18+C16</f>
-        <v>4088.489283</v>
+        <v>4809.012968</v>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="B20" s="18" t="inlineStr">
+      <c r="B20" s="20" t="inlineStr">
         <is>
           <t>% do EV no Valor Terminal</t>
         </is>
       </c>
-      <c r="C20" s="26">
+      <c r="C20" s="27">
         <f>C16/C19</f>
-        <v>0.723458</v>
+        <v>0.692023</v>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="B22" s="18" t="inlineStr">
+      <c r="B22" s="20" t="inlineStr">
         <is>
           <t>(-) Dívida líquida (2025)</t>
         </is>
       </c>
-      <c r="C22" s="19">
+      <c r="C22" s="21">
         <f>-Premissas!C22</f>
         <v>-1353.046</v>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="B23" s="23" t="inlineStr">
+      <c r="B23" s="24" t="inlineStr">
         <is>
           <t>EQUITY VALUE (DCF)</t>
         </is>
       </c>
-      <c r="C23" s="8">
+      <c r="C23" s="7">
         <f>C19+C22</f>
-        <v>2735.443283</v>
+        <v>3455.966968</v>
         <v/>
       </c>
     </row>

--- a/CIMED_Valuation_DCF.xlsx
+++ b/CIMED_Valuation_DCF.xlsx
@@ -740,7 +740,7 @@
       </c>
       <c r="C6" s="5">
         <f>DCF!C19</f>
-        <v>4809.012968</v>
+        <v>4115.654188</v>
         <v/>
       </c>
       <c r="E6" s="4" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="F6" s="6">
         <f>WACC!C22</f>
-        <v>0.15361</v>
+        <v>0.169177</v>
         <v/>
       </c>
     </row>
@@ -772,7 +772,7 @@
       </c>
       <c r="F7" s="6">
         <f>WACC!H22</f>
-        <v>0.149603</v>
+        <v>0.165022</v>
         <v/>
       </c>
     </row>
@@ -783,7 +783,7 @@
       </c>
       <c r="C8" s="7">
         <f>DCF!C23</f>
-        <v>3455.966968</v>
+        <v>2762.608188</v>
         <v/>
       </c>
       <c r="E8" s="4" t="inlineStr">
@@ -834,12 +834,12 @@
     <row r="11">
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Faixa de valor (múltiplos ↔ DCF)</t>
+          <t>DCF vs. múltiplos (validação)</t>
         </is>
       </c>
       <c r="C11" s="10" t="inlineStr">
         <is>
-          <t>R$ 2,7 – R$ 3,5 bi</t>
+          <t>DCF ≈ 7,0x ✓</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="F11" s="11">
         <f>DCF!C19/Projecoes!C9</f>
-        <v>8.233626</v>
+        <v>7.04651</v>
         <v/>
       </c>
     </row>
@@ -873,14 +873,14 @@
       </c>
       <c r="C13" s="12">
         <f>DCF!C23/1000</f>
-        <v>3.455967</v>
+        <v>2.762608</v>
         <v/>
       </c>
     </row>
     <row r="14">
       <c r="E14" s="13" t="inlineStr">
         <is>
-          <t>O DCF intrínseco (~R$3,5bi) supera o valor por múltiplos (~R$2,7bi) porque o múltiplo simples não captura o ativo fiscal: prejuízo fiscal de R$755mi + crédito presumido de ICMS mantêm o imposto caixa baixo por vários anos (cenário SEM reforma). O EV/EBITDA implícito do DCF (~8,2x) fica acima da Hypera (7,56x) — o prêmio é o valor do escudo fiscal. A taxa de desconto varia no tempo (aba WACC). Faixa razoável de IPO: R$2,7–3,5bi conforme a durabilidade dos benefícios fiscais. Células amarelas = inputs.</t>
+          <t>Premissas de mercado verdadeiras (não calibradas a alvo): Rf NTN-B ~11,5%, ERP FGV 8,19%, Kd 14%, βu 0,70 -&gt; WACC ~16,5-16,9% que VARIA no tempo conforme o escudo fiscal da dívida (aba WACC). O imposto reflete o uso do prejuízo fiscal de R$755mi + crédito presumido de ICMS (cenário SEM reforma). Resultado: Equity ~R$2,8bi. O cross-check por múltiplos (EV/EBITDA implícito 7,05x ≈ Hypera 7,56x) CONFIRMA as premissas, em vez de impô-las. Células amarelas = inputs editáveis.</t>
         </is>
       </c>
     </row>
@@ -1375,11 +1375,11 @@
         </is>
       </c>
       <c r="C9" s="31" t="n">
-        <v>0.105</v>
+        <v>0.115</v>
       </c>
       <c r="I9" s="26" t="inlineStr">
         <is>
-          <t>NTN-B 10a nominal</t>
+          <t>NTN-B longa: real ~6,7% + inflação ~4,5%</t>
         </is>
       </c>
     </row>
@@ -1390,11 +1390,11 @@
         </is>
       </c>
       <c r="C10" s="31" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.0819</v>
       </c>
       <c r="I10" s="26" t="inlineStr">
         <is>
-          <t>FGV/Ceqef 8,19% = teto</t>
+          <t>FGV/Ceqef (fev/2026)</t>
         </is>
       </c>
     </row>
@@ -1440,7 +1440,7 @@
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>0.1699286567164179</v>
+        <v>0.190966528358209</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
@@ -1457,11 +1457,11 @@
         </is>
       </c>
       <c r="C16" s="31" t="n">
-        <v>0.135</v>
+        <v>0.14</v>
       </c>
       <c r="I16" s="26" t="inlineStr">
         <is>
-          <t>CDI + spread debêntures</t>
+          <t>CDI ~13% + spread (debêntures CIMED)</t>
         </is>
       </c>
     </row>
@@ -1554,32 +1554,32 @@
       </c>
       <c r="C21" s="38">
         <f>$C$16*(1-C20)</f>
-        <v>0.120477</v>
+        <v>0.124939</v>
         <v/>
       </c>
       <c r="D21" s="38">
         <f>$C$16*(1-D20)</f>
-        <v>0.118656</v>
+        <v>0.12305</v>
         <v/>
       </c>
       <c r="E21" s="38">
         <f>$C$16*(1-E20)</f>
-        <v>0.117637</v>
+        <v>0.121994</v>
         <v/>
       </c>
       <c r="F21" s="38">
         <f>$C$16*(1-F20)</f>
-        <v>0.116742</v>
+        <v>0.121066</v>
         <v/>
       </c>
       <c r="G21" s="38">
         <f>$C$16*(1-G20)</f>
-        <v>0.116334</v>
+        <v>0.120643</v>
         <v/>
       </c>
       <c r="H21" s="38">
         <f>$C$16*(1-H20)</f>
-        <v>0.108335</v>
+        <v>0.112347</v>
         <v/>
       </c>
     </row>
@@ -1591,39 +1591,39 @@
       </c>
       <c r="C22" s="40">
         <f>$C$14*$C$5+C21*$C$6</f>
-        <v>0.15361</v>
+        <v>0.169177</v>
         <v/>
       </c>
       <c r="D22" s="40">
         <f>$C$14*$C$5+D21*$C$6</f>
-        <v>0.153009</v>
+        <v>0.168554</v>
         <v/>
       </c>
       <c r="E22" s="40">
         <f>$C$14*$C$5+E21*$C$6</f>
-        <v>0.152672</v>
+        <v>0.168206</v>
         <v/>
       </c>
       <c r="F22" s="40">
         <f>$C$14*$C$5+F21*$C$6</f>
-        <v>0.152377</v>
+        <v>0.167899</v>
         <v/>
       </c>
       <c r="G22" s="40">
         <f>$C$14*$C$5+G21*$C$6</f>
-        <v>0.152242</v>
+        <v>0.16776</v>
         <v/>
       </c>
       <c r="H22" s="40">
         <f>$C$14*$C$5+H21*$C$6</f>
-        <v>0.149603</v>
+        <v>0.165022</v>
         <v/>
       </c>
     </row>
     <row r="24">
       <c r="B24" s="13" t="inlineStr">
         <is>
-          <t>A taxa de desconto NÃO é constante: nos primeiros anos a alíquota efetiva é baixa (prejuízo fiscal + crédito presumido de ICMS), o que reduz o benefício fiscal da dívida e ELEVA o WACC; conforme o prejuízo fiscal é consumido e a alíquota normaliza, o benefício fiscal cresce e o WACC CAI. Ke mantido constante (estrutura de capital alvo estável). Cenário SEM reforma tributária: o crédito presumido de ICMS persiste indefinidamente.</t>
+          <t>Parâmetros de mercado (Rf NTN-B, ERP FGV/Ceqef, Kd das debêntures). A taxa de desconto NÃO é constante: nos primeiros anos a alíquota efetiva é baixa (prejuízo fiscal + crédito presumido de ICMS), o que reduz o benefício fiscal da dívida e ELEVA o WACC; conforme o prejuízo fiscal é consumido e a alíquota normaliza, o benefício fiscal cresce e o WACC CAI. Ke mantido constante (estrutura de capital alvo estável). Cenário SEM reforma tributária: o crédito presumido de ICMS persiste indefinidamente.</t>
         </is>
       </c>
     </row>
@@ -3524,27 +3524,27 @@
       </c>
       <c r="C6" s="38">
         <f>WACC!C22</f>
-        <v>0.15361</v>
+        <v>0.169177</v>
         <v/>
       </c>
       <c r="D6" s="38">
         <f>WACC!D22</f>
-        <v>0.153009</v>
+        <v>0.168554</v>
         <v/>
       </c>
       <c r="E6" s="38">
         <f>WACC!E22</f>
-        <v>0.152672</v>
+        <v>0.168206</v>
         <v/>
       </c>
       <c r="F6" s="38">
         <f>WACC!F22</f>
-        <v>0.152377</v>
+        <v>0.167899</v>
         <v/>
       </c>
       <c r="G6" s="38">
         <f>WACC!G22</f>
-        <v>0.152242</v>
+        <v>0.16776</v>
         <v/>
       </c>
     </row>
@@ -3556,27 +3556,27 @@
       </c>
       <c r="C7" s="53">
         <f>1/(1+C6)</f>
-        <v>0.866844</v>
+        <v>0.855302</v>
         <v/>
       </c>
       <c r="D7" s="53">
         <f>C7/(1+D6)</f>
-        <v>0.751811</v>
+        <v>0.731932</v>
         <v/>
       </c>
       <c r="E7" s="53">
         <f>D7/(1+E6)</f>
-        <v>0.652233</v>
+        <v>0.626544</v>
         <v/>
       </c>
       <c r="F7" s="53">
         <f>E7/(1+F6)</f>
-        <v>0.565989</v>
+        <v>0.536471</v>
         <v/>
       </c>
       <c r="G7" s="53">
         <f>F7/(1+G6)</f>
-        <v>0.491207</v>
+        <v>0.459402</v>
         <v/>
       </c>
     </row>
@@ -3588,27 +3588,27 @@
       </c>
       <c r="C8" s="25">
         <f>C5*C7</f>
-        <v>232.938123</v>
+        <v>229.836497</v>
         <v/>
       </c>
       <c r="D8" s="25">
         <f>D5*D7</f>
-        <v>292.669149</v>
+        <v>284.930573</v>
         <v/>
       </c>
       <c r="E8" s="25">
         <f>E5*E7</f>
-        <v>314.496769</v>
+        <v>302.109874</v>
         <v/>
       </c>
       <c r="F8" s="25">
         <f>F5*F7</f>
-        <v>325.271596</v>
+        <v>308.307496</v>
         <v/>
       </c>
       <c r="G8" s="25">
         <f>G5*G7</f>
-        <v>315.687992</v>
+        <v>295.247616</v>
         <v/>
       </c>
     </row>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="C11" s="23">
         <f>SUM(C8:G8)</f>
-        <v>1481.06363</v>
+        <v>1420.432056</v>
         <v/>
       </c>
     </row>
@@ -3644,7 +3644,7 @@
       </c>
       <c r="C14" s="38">
         <f>WACC!H22</f>
-        <v>0.149603</v>
+        <v>0.165022</v>
         <v/>
       </c>
     </row>
@@ -3656,7 +3656,7 @@
       </c>
       <c r="C15" s="54">
         <f>C13/(C14-Premissas!C14)</f>
-        <v>6775.050255</v>
+        <v>5866.810249</v>
         <v/>
       </c>
     </row>
@@ -3668,7 +3668,7 @@
       </c>
       <c r="C16" s="25">
         <f>C15*G7</f>
-        <v>3327.949338</v>
+        <v>2695.222131</v>
         <v/>
       </c>
     </row>
@@ -3680,7 +3680,7 @@
       </c>
       <c r="C18" s="21">
         <f>C11</f>
-        <v>1481.06363</v>
+        <v>1420.432056</v>
         <v/>
       </c>
     </row>
@@ -3692,7 +3692,7 @@
       </c>
       <c r="C19" s="5">
         <f>C18+C16</f>
-        <v>4809.012968</v>
+        <v>4115.654188</v>
         <v/>
       </c>
     </row>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C20" s="27">
         <f>C16/C19</f>
-        <v>0.692023</v>
+        <v>0.654871</v>
         <v/>
       </c>
     </row>
@@ -3728,7 +3728,7 @@
       </c>
       <c r="C23" s="7">
         <f>C19+C22</f>
-        <v>3455.966968</v>
+        <v>2762.608188</v>
         <v/>
       </c>
     </row>

--- a/CIMED_Valuation_DCF.xlsx
+++ b/CIMED_Valuation_DCF.xlsx
@@ -15,6 +15,7 @@
     <sheet name="Capital_de_Giro" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="Projecoes" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="DCF" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Sensibilidade" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,13 +24,14 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="6">
+  <numFmts count="7">
     <numFmt numFmtId="164" formatCode="#,##0.0"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
     <numFmt numFmtId="166" formatCode="0.0&quot;x&quot;"/>
     <numFmt numFmtId="167" formatCode="0&quot;d&quot;"/>
     <numFmt numFmtId="168" formatCode="0.000"/>
     <numFmt numFmtId="169" formatCode="&quot;R$ &quot;#,##0.00&quot; bi&quot;"/>
+    <numFmt numFmtId="170" formatCode="&quot;R$ &quot;0.00&quot; bi&quot;"/>
   </numFmts>
   <fonts count="11">
     <font>
@@ -165,7 +167,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="65">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -327,6 +329,36 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
@@ -3738,4 +3770,433 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B2:H34"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="2" ht="26" customHeight="1">
+      <c r="B2" s="28" t="inlineStr">
+        <is>
+          <t>Análise de Sensibilidade — Equity Value (R$ milhões)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1">
+      <c r="B4" s="29" t="inlineStr">
+        <is>
+          <t>1. Equity Value por Ke (custo do capital próprio) × g (perpetuidade)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="55" t="inlineStr">
+        <is>
+          <t>Ke ↓  /  g →</t>
+        </is>
+      </c>
+      <c r="C5" s="56" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="D5" s="56" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="E5" s="56" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F5" s="56" t="n">
+        <v>0.055</v>
+      </c>
+      <c r="G5" s="56" t="n">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="56" t="n">
+        <v>0.181</v>
+      </c>
+      <c r="C6" s="43" t="n">
+        <v>2763</v>
+      </c>
+      <c r="D6" s="43" t="n">
+        <v>2894</v>
+      </c>
+      <c r="E6" s="57" t="n">
+        <v>3037</v>
+      </c>
+      <c r="F6" s="57" t="n">
+        <v>3195</v>
+      </c>
+      <c r="G6" s="57" t="n">
+        <v>3368</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="56" t="n">
+        <v>0.186</v>
+      </c>
+      <c r="C7" s="43" t="n">
+        <v>2639</v>
+      </c>
+      <c r="D7" s="43" t="n">
+        <v>2762</v>
+      </c>
+      <c r="E7" s="43" t="n">
+        <v>2895</v>
+      </c>
+      <c r="F7" s="57" t="n">
+        <v>3041</v>
+      </c>
+      <c r="G7" s="57" t="n">
+        <v>3202</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="56" t="n">
+        <v>0.191</v>
+      </c>
+      <c r="C8" s="58" t="n">
+        <v>2523</v>
+      </c>
+      <c r="D8" s="43" t="n">
+        <v>2637</v>
+      </c>
+      <c r="E8" s="43" t="n">
+        <v>2762</v>
+      </c>
+      <c r="F8" s="43" t="n">
+        <v>2898</v>
+      </c>
+      <c r="G8" s="57" t="n">
+        <v>3046</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="56" t="n">
+        <v>0.196</v>
+      </c>
+      <c r="C9" s="58" t="n">
+        <v>2412</v>
+      </c>
+      <c r="D9" s="58" t="n">
+        <v>2519</v>
+      </c>
+      <c r="E9" s="43" t="n">
+        <v>2636</v>
+      </c>
+      <c r="F9" s="43" t="n">
+        <v>2762</v>
+      </c>
+      <c r="G9" s="43" t="n">
+        <v>2901</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="56" t="n">
+        <v>0.201</v>
+      </c>
+      <c r="C10" s="58" t="n">
+        <v>2307</v>
+      </c>
+      <c r="D10" s="58" t="n">
+        <v>2408</v>
+      </c>
+      <c r="E10" s="58" t="n">
+        <v>2517</v>
+      </c>
+      <c r="F10" s="43" t="n">
+        <v>2635</v>
+      </c>
+      <c r="G10" s="43" t="n">
+        <v>2764</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="56" t="n">
+        <v>0.206</v>
+      </c>
+      <c r="C11" s="58" t="n">
+        <v>2208</v>
+      </c>
+      <c r="D11" s="58" t="n">
+        <v>2302</v>
+      </c>
+      <c r="E11" s="58" t="n">
+        <v>2404</v>
+      </c>
+      <c r="F11" s="58" t="n">
+        <v>2515</v>
+      </c>
+      <c r="G11" s="43" t="n">
+        <v>2635</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="15" t="inlineStr">
+        <is>
+          <t>Caso-base: Ke 19,1% · g 5,0%  →  WACC ~16,5-16,9%</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="22" customHeight="1">
+      <c r="B14" s="29" t="inlineStr">
+        <is>
+          <t>2. Equity Value por Beta desalavancado (βu) × Prêmio de risco (ERP)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="55" t="inlineStr">
+        <is>
+          <t>βu ↓  /  ERP →</t>
+        </is>
+      </c>
+      <c r="C15" s="59" t="n">
+        <v>0.07190000000000001</v>
+      </c>
+      <c r="D15" s="59" t="n">
+        <v>0.0769</v>
+      </c>
+      <c r="E15" s="59" t="n">
+        <v>0.0819</v>
+      </c>
+      <c r="F15" s="59" t="n">
+        <v>0.08690000000000001</v>
+      </c>
+      <c r="G15" s="59" t="n">
+        <v>0.0919</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="60" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="C16" s="57" t="n">
+        <v>3312</v>
+      </c>
+      <c r="D16" s="57" t="n">
+        <v>3184</v>
+      </c>
+      <c r="E16" s="57" t="n">
+        <v>3064</v>
+      </c>
+      <c r="F16" s="43" t="n">
+        <v>2949</v>
+      </c>
+      <c r="G16" s="43" t="n">
+        <v>2839</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="60" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="C17" s="57" t="n">
+        <v>3160</v>
+      </c>
+      <c r="D17" s="57" t="n">
+        <v>3031</v>
+      </c>
+      <c r="E17" s="43" t="n">
+        <v>2908</v>
+      </c>
+      <c r="F17" s="43" t="n">
+        <v>2792</v>
+      </c>
+      <c r="G17" s="43" t="n">
+        <v>2681</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="60" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="C18" s="57" t="n">
+        <v>3017</v>
+      </c>
+      <c r="D18" s="43" t="n">
+        <v>2886</v>
+      </c>
+      <c r="E18" s="61" t="n">
+        <v>2763</v>
+      </c>
+      <c r="F18" s="43" t="n">
+        <v>2645</v>
+      </c>
+      <c r="G18" s="58" t="n">
+        <v>2534</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="60" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="C19" s="43" t="n">
+        <v>2883</v>
+      </c>
+      <c r="D19" s="43" t="n">
+        <v>2751</v>
+      </c>
+      <c r="E19" s="43" t="n">
+        <v>2626</v>
+      </c>
+      <c r="F19" s="58" t="n">
+        <v>2508</v>
+      </c>
+      <c r="G19" s="58" t="n">
+        <v>2397</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="60" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="C20" s="43" t="n">
+        <v>2756</v>
+      </c>
+      <c r="D20" s="43" t="n">
+        <v>2623</v>
+      </c>
+      <c r="E20" s="58" t="n">
+        <v>2498</v>
+      </c>
+      <c r="F20" s="58" t="n">
+        <v>2380</v>
+      </c>
+      <c r="G20" s="58" t="n">
+        <v>2268</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="60" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="C21" s="43" t="n">
+        <v>2636</v>
+      </c>
+      <c r="D21" s="58" t="n">
+        <v>2503</v>
+      </c>
+      <c r="E21" s="58" t="n">
+        <v>2377</v>
+      </c>
+      <c r="F21" s="58" t="n">
+        <v>2259</v>
+      </c>
+      <c r="G21" s="58" t="n">
+        <v>2148</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="15" t="inlineStr">
+        <is>
+          <t>Caso-base: βu 0,70 · ERP 8,19% (FGV)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="22" customHeight="1">
+      <c r="B24" s="29" t="inlineStr">
+        <is>
+          <t>3. Leitura por múltiplo (EV/EBITDA 2026E implícito)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="20" t="inlineStr">
+        <is>
+          <t>Equity Value (R$ bi)</t>
+        </is>
+      </c>
+      <c r="C25" s="20" t="inlineStr">
+        <is>
+          <t>EV/EBITDA 2026E</t>
+        </is>
+      </c>
+      <c r="D25" s="20" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="62" t="n">
+        <v>2.207502451089324</v>
+      </c>
+      <c r="C26" s="63" t="n">
+        <v>6.096099911534498</v>
+      </c>
+      <c r="D26" s="37" t="inlineStr">
+        <is>
+          <t>conservador</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="64" t="n">
+        <v>2.762608187746837</v>
+      </c>
+      <c r="C27" s="48" t="n">
+        <v>7.046509680876312</v>
+      </c>
+      <c r="D27" s="30" t="inlineStr">
+        <is>
+          <t>caso-base</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" s="62" t="n">
+        <v>3.36779389895011</v>
+      </c>
+      <c r="C28" s="63" t="n">
+        <v>8.082662568895435</v>
+      </c>
+      <c r="D28" s="37" t="inlineStr">
+        <is>
+          <t>otimista</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="15" t="inlineStr">
+        <is>
+          <t>Referência de mercado: Hypera 7,56x · Blau ~6,5x (mar/2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="13" t="inlineStr">
+        <is>
+          <t>Verde = acima do caso-base (+8%); laranja = abaixo (-8%); amarelo = caso-base. O valuation é mais sensível ao Ke (taxa de desconto) e ao ERP do que a g, dado o peso do valor terminal. Mesmo no cenário otimista o EV/EBITDA implícito permanece coerente com o setor (Hypera 7,56x), reforçando a robustez das premissas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33"/>
+    <row r="34"/>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="B14:H14"/>
+    <mergeCell ref="B4:H4"/>
+    <mergeCell ref="B24:H24"/>
+    <mergeCell ref="B2:H2"/>
+    <mergeCell ref="B32:H34"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>